--- a/Data/Rules/Fluff & Tuff Rules Matrix.xlsx
+++ b/Data/Rules/Fluff & Tuff Rules Matrix.xlsx
@@ -1165,103 +1165,103 @@
         <v>1</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL2" t="b">
         <v>1</v>
@@ -1284,22 +1284,22 @@
         <v>226</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -1308,25 +1308,25 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
       </c>
       <c r="O3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="b">
         <v>0</v>
       </c>
       <c r="R3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S3">
         <v>4</v>
@@ -1335,46 +1335,46 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC3" t="b">
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="b">
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="b">
         <v>0</v>
@@ -1383,7 +1383,7 @@
         <v>2</v>
       </c>
       <c r="AK3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL3" t="b">
         <v>1</v>
@@ -1406,22 +1406,22 @@
         <v>226</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" t="b">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" t="b">
         <v>0</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -1430,25 +1430,25 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
       </c>
       <c r="O4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="b">
         <v>0</v>
       </c>
       <c r="R4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S4">
         <v>4</v>
@@ -1457,46 +1457,46 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC4" t="b">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         <v>2</v>
       </c>
       <c r="AK4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL4" t="b">
         <v>1</v>
@@ -1528,22 +1528,22 @@
         <v>226</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H5" t="b">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J5">
         <v>4</v>
@@ -1552,25 +1552,25 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
       </c>
       <c r="O5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="b">
         <v>0</v>
       </c>
       <c r="R5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S5">
         <v>4</v>
@@ -1579,46 +1579,46 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
       </c>
       <c r="AA5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="b">
         <v>0</v>
       </c>
       <c r="AD5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="b">
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -1627,7 +1627,7 @@
         <v>2</v>
       </c>
       <c r="AK5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL5" t="b">
         <v>1</v>
@@ -1650,22 +1650,22 @@
         <v>226</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="b">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>4</v>
@@ -1674,25 +1674,25 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
       </c>
       <c r="O6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="b">
         <v>0</v>
       </c>
       <c r="R6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6">
         <v>4</v>
@@ -1701,46 +1701,46 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="b">
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="b">
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -1749,7 +1749,7 @@
         <v>2</v>
       </c>
       <c r="AK6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL6" t="b">
         <v>1</v>
@@ -1772,22 +1772,22 @@
         <v>226</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" t="b">
         <v>0</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -1796,25 +1796,25 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
       </c>
       <c r="O7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="b">
         <v>0</v>
       </c>
       <c r="R7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S7">
         <v>4</v>
@@ -1823,46 +1823,46 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W7" t="b">
         <v>0</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="b">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="b">
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>2</v>
       </c>
       <c r="AK7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL7" t="b">
         <v>1</v>
@@ -1894,22 +1894,22 @@
         <v>226</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" t="b">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -1918,25 +1918,25 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
       </c>
       <c r="O8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="b">
         <v>0</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8">
         <v>4</v>
@@ -1945,46 +1945,46 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC8" t="b">
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="b">
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>2</v>
       </c>
       <c r="AK8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="b">
         <v>1</v>
@@ -2260,22 +2260,22 @@
         <v>226</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
       </c>
       <c r="F11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" t="b">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -2284,25 +2284,25 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
       </c>
       <c r="O11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="b">
         <v>0</v>
       </c>
       <c r="R11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S11">
         <v>4</v>
@@ -2311,46 +2311,46 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W11" t="b">
         <v>0</v>
       </c>
       <c r="X11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="b">
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="b">
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="b">
         <v>0</v>
@@ -2359,7 +2359,7 @@
         <v>2</v>
       </c>
       <c r="AK11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL11" t="b">
         <v>1</v>
@@ -2385,103 +2385,103 @@
         <v>1</v>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="b">
         <v>1</v>
@@ -2507,103 +2507,103 @@
         <v>1</v>
       </c>
       <c r="E13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="b">
         <v>1</v>
@@ -2626,22 +2626,22 @@
         <v>226</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E14" t="b">
         <v>0</v>
       </c>
       <c r="F14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -2650,25 +2650,25 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
       </c>
       <c r="O14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="b">
         <v>0</v>
       </c>
       <c r="R14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S14">
         <v>4</v>
@@ -2677,46 +2677,46 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W14" t="b">
         <v>0</v>
       </c>
       <c r="X14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
       </c>
       <c r="AA14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC14" t="b">
         <v>0</v>
       </c>
       <c r="AD14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="b">
         <v>0</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI14" t="b">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         <v>2</v>
       </c>
       <c r="AK14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="b">
         <v>1</v>
@@ -3236,22 +3236,22 @@
         <v>226</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H19" t="b">
         <v>0</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J19">
         <v>4</v>
@@ -3260,25 +3260,25 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
       </c>
       <c r="O19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="b">
         <v>0</v>
       </c>
       <c r="R19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S19">
         <v>4</v>
@@ -3287,46 +3287,46 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W19" t="b">
         <v>0</v>
       </c>
       <c r="X19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="b">
         <v>0</v>
       </c>
       <c r="AA19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC19" t="b">
         <v>0</v>
       </c>
       <c r="AD19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF19" t="b">
         <v>0</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="b">
         <v>0</v>
@@ -3335,7 +3335,7 @@
         <v>2</v>
       </c>
       <c r="AK19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL19" t="b">
         <v>1</v>
@@ -3358,22 +3358,22 @@
         <v>226</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
       </c>
       <c r="F20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" t="b">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -3382,25 +3382,25 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
       </c>
       <c r="O20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="b">
         <v>0</v>
       </c>
       <c r="R20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S20">
         <v>4</v>
@@ -3409,46 +3409,46 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W20" t="b">
         <v>0</v>
       </c>
       <c r="X20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="b">
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC20" t="b">
         <v>0</v>
       </c>
       <c r="AD20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="b">
         <v>0</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI20" t="b">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>2</v>
       </c>
       <c r="AK20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL20" t="b">
         <v>1</v>
@@ -3480,22 +3480,22 @@
         <v>226</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -3504,25 +3504,25 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
       </c>
       <c r="O21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="b">
         <v>0</v>
       </c>
       <c r="R21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S21">
         <v>4</v>
@@ -3531,46 +3531,46 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W21" t="b">
         <v>0</v>
       </c>
       <c r="X21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="b">
         <v>0</v>
       </c>
       <c r="AA21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC21" t="b">
         <v>0</v>
       </c>
       <c r="AD21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="b">
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3579,7 +3579,7 @@
         <v>2</v>
       </c>
       <c r="AK21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL21" t="b">
         <v>1</v>
@@ -3724,22 +3724,22 @@
         <v>226</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" t="b">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" t="b">
         <v>0</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J23">
         <v>4</v>
@@ -3748,25 +3748,25 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
       </c>
       <c r="O23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="b">
         <v>0</v>
       </c>
       <c r="R23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S23">
         <v>4</v>
@@ -3775,46 +3775,46 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W23" t="b">
         <v>0</v>
       </c>
       <c r="X23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="b">
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC23" t="b">
         <v>0</v>
       </c>
       <c r="AD23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="b">
         <v>0</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI23" t="b">
         <v>0</v>
@@ -3823,7 +3823,7 @@
         <v>2</v>
       </c>
       <c r="AK23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL23" t="b">
         <v>1</v>
@@ -3846,22 +3846,22 @@
         <v>226</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24" t="b">
         <v>0</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>4</v>
@@ -3870,25 +3870,25 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
       </c>
       <c r="O24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="b">
         <v>0</v>
       </c>
       <c r="R24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S24">
         <v>4</v>
@@ -3897,46 +3897,46 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W24" t="b">
         <v>0</v>
       </c>
       <c r="X24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="b">
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC24" t="b">
         <v>0</v>
       </c>
       <c r="AD24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="b">
         <v>0</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI24" t="b">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>2</v>
       </c>
       <c r="AK24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL24" t="b">
         <v>1</v>
@@ -4090,22 +4090,22 @@
         <v>226</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
       </c>
       <c r="I26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J26">
         <v>4</v>
@@ -4114,25 +4114,25 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
       </c>
       <c r="O26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="b">
         <v>0</v>
       </c>
       <c r="R26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S26">
         <v>4</v>
@@ -4141,46 +4141,46 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W26" t="b">
         <v>0</v>
       </c>
       <c r="X26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="b">
         <v>0</v>
       </c>
       <c r="AA26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="b">
         <v>0</v>
       </c>
       <c r="AD26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="b">
         <v>0</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
@@ -4189,7 +4189,7 @@
         <v>2</v>
       </c>
       <c r="AK26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL26" t="b">
         <v>1</v>
@@ -4212,22 +4212,22 @@
         <v>226</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
       </c>
       <c r="F27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" t="b">
         <v>0</v>
       </c>
       <c r="I27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J27">
         <v>4</v>
@@ -4236,25 +4236,25 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
       </c>
       <c r="O27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="b">
         <v>0</v>
       </c>
       <c r="R27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S27">
         <v>4</v>
@@ -4263,46 +4263,46 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W27" t="b">
         <v>0</v>
       </c>
       <c r="X27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="b">
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="b">
         <v>0</v>
       </c>
       <c r="AD27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="b">
         <v>0</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI27" t="b">
         <v>0</v>
@@ -4311,7 +4311,7 @@
         <v>2</v>
       </c>
       <c r="AK27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL27" t="b">
         <v>1</v>
@@ -4334,22 +4334,22 @@
         <v>226</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" t="b">
         <v>0</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28">
         <v>4</v>
@@ -4358,25 +4358,25 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
       </c>
       <c r="O28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="b">
         <v>0</v>
       </c>
       <c r="R28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S28">
         <v>4</v>
@@ -4385,46 +4385,46 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W28" t="b">
         <v>0</v>
       </c>
       <c r="X28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="b">
         <v>0</v>
       </c>
       <c r="AA28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="b">
         <v>0</v>
       </c>
       <c r="AD28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="b">
         <v>0</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4433,7 +4433,7 @@
         <v>2</v>
       </c>
       <c r="AK28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL28" t="b">
         <v>1</v>
@@ -4700,22 +4700,22 @@
         <v>226</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
       </c>
       <c r="F31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" t="b">
         <v>0</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J31">
         <v>4</v>
@@ -4724,25 +4724,25 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
       </c>
       <c r="O31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="b">
         <v>0</v>
       </c>
       <c r="R31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S31">
         <v>4</v>
@@ -4751,46 +4751,46 @@
         <v>0</v>
       </c>
       <c r="U31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W31" t="b">
         <v>0</v>
       </c>
       <c r="X31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z31" t="b">
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="b">
         <v>0</v>
       </c>
       <c r="AD31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="b">
         <v>0</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI31" t="b">
         <v>0</v>
@@ -4799,7 +4799,7 @@
         <v>2</v>
       </c>
       <c r="AK31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL31" t="b">
         <v>1</v>
@@ -4822,22 +4822,22 @@
         <v>226</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E32" t="b">
         <v>0</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H32" t="b">
         <v>0</v>
       </c>
       <c r="I32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J32">
         <v>4</v>
@@ -4846,25 +4846,25 @@
         <v>0</v>
       </c>
       <c r="L32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
       </c>
       <c r="O32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="b">
         <v>0</v>
       </c>
       <c r="R32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S32">
         <v>4</v>
@@ -4873,46 +4873,46 @@
         <v>0</v>
       </c>
       <c r="U32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W32" t="b">
         <v>0</v>
       </c>
       <c r="X32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z32" t="b">
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="b">
         <v>0</v>
       </c>
       <c r="AD32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="b">
         <v>0</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI32" t="b">
         <v>0</v>
@@ -4921,7 +4921,7 @@
         <v>2</v>
       </c>
       <c r="AK32">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL32" t="b">
         <v>1</v>
@@ -4944,22 +4944,22 @@
         <v>226</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
       </c>
       <c r="F33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H33" t="b">
         <v>0</v>
       </c>
       <c r="I33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33">
         <v>4</v>
@@ -4968,25 +4968,25 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
       </c>
       <c r="O33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="b">
         <v>0</v>
       </c>
       <c r="R33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S33">
         <v>4</v>
@@ -4995,46 +4995,46 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W33" t="b">
         <v>0</v>
       </c>
       <c r="X33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="b">
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="b">
         <v>0</v>
       </c>
       <c r="AD33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF33" t="b">
         <v>0</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
@@ -5043,7 +5043,7 @@
         <v>2</v>
       </c>
       <c r="AK33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL33" t="b">
         <v>1</v>
@@ -5066,22 +5066,22 @@
         <v>226</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34" t="b">
         <v>0</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J34">
         <v>4</v>
@@ -5090,25 +5090,25 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
       </c>
       <c r="O34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q34" t="b">
         <v>0</v>
       </c>
       <c r="R34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S34">
         <v>4</v>
@@ -5117,46 +5117,46 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W34" t="b">
         <v>0</v>
       </c>
       <c r="X34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="b">
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="b">
         <v>0</v>
       </c>
       <c r="AD34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF34" t="b">
         <v>0</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI34" t="b">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>2</v>
       </c>
       <c r="AK34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL34" t="b">
         <v>1</v>
@@ -5188,22 +5188,22 @@
         <v>226</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
       </c>
       <c r="F35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35" t="b">
         <v>0</v>
       </c>
       <c r="I35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J35">
         <v>4</v>
@@ -5212,25 +5212,25 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
       </c>
       <c r="O35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="b">
         <v>0</v>
       </c>
       <c r="R35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S35">
         <v>4</v>
@@ -5239,46 +5239,46 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W35" t="b">
         <v>0</v>
       </c>
       <c r="X35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="b">
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC35" t="b">
         <v>0</v>
       </c>
       <c r="AD35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="b">
         <v>0</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
@@ -5287,7 +5287,7 @@
         <v>2</v>
       </c>
       <c r="AK35">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL35" t="b">
         <v>1</v>
@@ -5310,22 +5310,22 @@
         <v>226</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H36" t="b">
         <v>0</v>
       </c>
       <c r="I36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J36">
         <v>4</v>
@@ -5334,25 +5334,25 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
       </c>
       <c r="O36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="b">
         <v>0</v>
       </c>
       <c r="R36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S36">
         <v>4</v>
@@ -5361,46 +5361,46 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W36" t="b">
         <v>0</v>
       </c>
       <c r="X36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="b">
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC36" t="b">
         <v>0</v>
       </c>
       <c r="AD36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="b">
         <v>0</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
@@ -5409,7 +5409,7 @@
         <v>2</v>
       </c>
       <c r="AK36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL36" t="b">
         <v>1</v>
@@ -5432,22 +5432,22 @@
         <v>226</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
       </c>
       <c r="F37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37" t="b">
         <v>0</v>
       </c>
       <c r="I37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J37">
         <v>4</v>
@@ -5456,25 +5456,25 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
       </c>
       <c r="O37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="b">
         <v>0</v>
       </c>
       <c r="R37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S37">
         <v>4</v>
@@ -5483,46 +5483,46 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W37" t="b">
         <v>0</v>
       </c>
       <c r="X37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="b">
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC37" t="b">
         <v>0</v>
       </c>
       <c r="AD37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF37" t="b">
         <v>0</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>2</v>
       </c>
       <c r="AK37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL37" t="b">
         <v>1</v>
@@ -5554,22 +5554,22 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H38" t="b">
         <v>0</v>
       </c>
       <c r="I38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J38">
         <v>4</v>
@@ -5578,25 +5578,25 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
       </c>
       <c r="O38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="b">
         <v>0</v>
       </c>
       <c r="R38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S38">
         <v>4</v>
@@ -5605,46 +5605,46 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W38" t="b">
         <v>0</v>
       </c>
       <c r="X38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z38" t="b">
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC38" t="b">
         <v>0</v>
       </c>
       <c r="AD38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF38" t="b">
         <v>0</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5653,7 +5653,7 @@
         <v>2</v>
       </c>
       <c r="AK38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL38" t="b">
         <v>1</v>
@@ -5798,22 +5798,22 @@
         <v>226</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H40" t="b">
         <v>0</v>
       </c>
       <c r="I40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J40">
         <v>4</v>
@@ -5822,25 +5822,25 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
       </c>
       <c r="O40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="b">
         <v>0</v>
       </c>
       <c r="R40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S40">
         <v>4</v>
@@ -5849,46 +5849,46 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W40" t="b">
         <v>0</v>
       </c>
       <c r="X40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="b">
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="b">
         <v>0</v>
       </c>
       <c r="AD40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="b">
         <v>0</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
@@ -5897,7 +5897,7 @@
         <v>2</v>
       </c>
       <c r="AK40">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL40" t="b">
         <v>1</v>
@@ -5920,22 +5920,22 @@
         <v>226</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
       </c>
       <c r="F41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H41" t="b">
         <v>0</v>
       </c>
       <c r="I41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J41">
         <v>4</v>
@@ -5944,25 +5944,25 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
       </c>
       <c r="O41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="b">
         <v>0</v>
       </c>
       <c r="R41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S41">
         <v>4</v>
@@ -5971,46 +5971,46 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W41" t="b">
         <v>0</v>
       </c>
       <c r="X41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="b">
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC41" t="b">
         <v>0</v>
       </c>
       <c r="AD41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF41" t="b">
         <v>0</v>
       </c>
       <c r="AG41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -6019,7 +6019,7 @@
         <v>2</v>
       </c>
       <c r="AK41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL41" t="b">
         <v>1</v>
@@ -6045,103 +6045,103 @@
         <v>1</v>
       </c>
       <c r="E42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="b">
         <v>1</v>
@@ -6164,22 +6164,22 @@
         <v>226</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H43" t="b">
         <v>0</v>
       </c>
       <c r="I43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J43">
         <v>4</v>
@@ -6188,25 +6188,25 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
       </c>
       <c r="O43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q43" t="b">
         <v>0</v>
       </c>
       <c r="R43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S43">
         <v>4</v>
@@ -6215,46 +6215,46 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W43" t="b">
         <v>0</v>
       </c>
       <c r="X43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="b">
         <v>0</v>
       </c>
       <c r="AA43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC43" t="b">
         <v>0</v>
       </c>
       <c r="AD43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF43" t="b">
         <v>0</v>
       </c>
       <c r="AG43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6263,7 +6263,7 @@
         <v>2</v>
       </c>
       <c r="AK43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL43" t="b">
         <v>1</v>
@@ -6286,22 +6286,22 @@
         <v>226</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
       </c>
       <c r="F44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H44" t="b">
         <v>0</v>
       </c>
       <c r="I44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J44">
         <v>4</v>
@@ -6310,25 +6310,25 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
       </c>
       <c r="O44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="b">
         <v>0</v>
       </c>
       <c r="R44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S44">
         <v>4</v>
@@ -6337,46 +6337,46 @@
         <v>0</v>
       </c>
       <c r="U44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W44" t="b">
         <v>0</v>
       </c>
       <c r="X44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="b">
         <v>0</v>
       </c>
       <c r="AA44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC44" t="b">
         <v>0</v>
       </c>
       <c r="AD44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF44" t="b">
         <v>0</v>
       </c>
       <c r="AG44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6385,7 +6385,7 @@
         <v>2</v>
       </c>
       <c r="AK44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL44" t="b">
         <v>1</v>
@@ -6530,22 +6530,22 @@
         <v>226</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
       </c>
       <c r="F46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" t="b">
         <v>0</v>
       </c>
       <c r="I46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J46">
         <v>4</v>
@@ -6554,25 +6554,25 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
       </c>
       <c r="O46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="b">
         <v>0</v>
       </c>
       <c r="R46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S46">
         <v>4</v>
@@ -6581,46 +6581,46 @@
         <v>0</v>
       </c>
       <c r="U46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W46" t="b">
         <v>0</v>
       </c>
       <c r="X46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="b">
         <v>0</v>
       </c>
       <c r="AA46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC46" t="b">
         <v>0</v>
       </c>
       <c r="AD46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF46" t="b">
         <v>0</v>
       </c>
       <c r="AG46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6629,7 +6629,7 @@
         <v>2</v>
       </c>
       <c r="AK46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL46" t="b">
         <v>1</v>
@@ -6652,22 +6652,22 @@
         <v>226</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
       </c>
       <c r="F47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H47" t="b">
         <v>0</v>
       </c>
       <c r="I47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J47">
         <v>4</v>
@@ -6676,25 +6676,25 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
       </c>
       <c r="O47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="b">
         <v>0</v>
       </c>
       <c r="R47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S47">
         <v>4</v>
@@ -6703,46 +6703,46 @@
         <v>0</v>
       </c>
       <c r="U47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W47" t="b">
         <v>0</v>
       </c>
       <c r="X47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z47" t="b">
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC47" t="b">
         <v>0</v>
       </c>
       <c r="AD47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF47" t="b">
         <v>0</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -6751,7 +6751,7 @@
         <v>2</v>
       </c>
       <c r="AK47">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL47" t="b">
         <v>1</v>
@@ -6777,103 +6777,103 @@
         <v>1</v>
       </c>
       <c r="E48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK48">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="b">
         <v>1</v>
@@ -7018,22 +7018,22 @@
         <v>226</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H50" t="b">
         <v>0</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J50">
         <v>4</v>
@@ -7042,25 +7042,25 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N50" t="b">
         <v>0</v>
       </c>
       <c r="O50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="b">
         <v>0</v>
       </c>
       <c r="R50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S50">
         <v>4</v>
@@ -7069,46 +7069,46 @@
         <v>0</v>
       </c>
       <c r="U50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W50" t="b">
         <v>0</v>
       </c>
       <c r="X50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z50" t="b">
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC50" t="b">
         <v>0</v>
       </c>
       <c r="AD50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF50" t="b">
         <v>0</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -7117,7 +7117,7 @@
         <v>2</v>
       </c>
       <c r="AK50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL50" t="b">
         <v>1</v>
@@ -7140,22 +7140,22 @@
         <v>226</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
       </c>
       <c r="F51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H51" t="b">
         <v>0</v>
       </c>
       <c r="I51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J51">
         <v>4</v>
@@ -7164,25 +7164,25 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N51" t="b">
         <v>0</v>
       </c>
       <c r="O51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="b">
         <v>0</v>
       </c>
       <c r="R51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S51">
         <v>4</v>
@@ -7191,46 +7191,46 @@
         <v>0</v>
       </c>
       <c r="U51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W51" t="b">
         <v>0</v>
       </c>
       <c r="X51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z51" t="b">
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC51" t="b">
         <v>0</v>
       </c>
       <c r="AD51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF51" t="b">
         <v>0</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7239,7 +7239,7 @@
         <v>2</v>
       </c>
       <c r="AK51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL51" t="b">
         <v>1</v>
@@ -7262,22 +7262,22 @@
         <v>226</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
       </c>
       <c r="F52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H52" t="b">
         <v>0</v>
       </c>
       <c r="I52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J52">
         <v>4</v>
@@ -7286,25 +7286,25 @@
         <v>0</v>
       </c>
       <c r="L52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N52" t="b">
         <v>0</v>
       </c>
       <c r="O52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q52" t="b">
         <v>0</v>
       </c>
       <c r="R52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S52">
         <v>4</v>
@@ -7313,46 +7313,46 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W52" t="b">
         <v>0</v>
       </c>
       <c r="X52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z52" t="b">
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC52" t="b">
         <v>0</v>
       </c>
       <c r="AD52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF52" t="b">
         <v>0</v>
       </c>
       <c r="AG52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI52" t="b">
         <v>0</v>
@@ -7361,7 +7361,7 @@
         <v>2</v>
       </c>
       <c r="AK52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL52" t="b">
         <v>1</v>
@@ -7384,22 +7384,22 @@
         <v>226</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H53" t="b">
         <v>0</v>
       </c>
       <c r="I53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J53">
         <v>4</v>
@@ -7408,25 +7408,25 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N53" t="b">
         <v>0</v>
       </c>
       <c r="O53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="b">
         <v>0</v>
       </c>
       <c r="R53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S53">
         <v>4</v>
@@ -7435,46 +7435,46 @@
         <v>0</v>
       </c>
       <c r="U53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W53" t="b">
         <v>0</v>
       </c>
       <c r="X53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z53" t="b">
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC53" t="b">
         <v>0</v>
       </c>
       <c r="AD53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF53" t="b">
         <v>0</v>
       </c>
       <c r="AG53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI53" t="b">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>2</v>
       </c>
       <c r="AK53">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL53" t="b">
         <v>1</v>
@@ -7506,22 +7506,22 @@
         <v>226</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
       </c>
       <c r="F54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" t="b">
         <v>0</v>
       </c>
       <c r="I54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J54">
         <v>4</v>
@@ -7530,25 +7530,25 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
       </c>
       <c r="O54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="b">
         <v>0</v>
       </c>
       <c r="R54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S54">
         <v>4</v>
@@ -7557,46 +7557,46 @@
         <v>0</v>
       </c>
       <c r="U54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W54" t="b">
         <v>0</v>
       </c>
       <c r="X54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z54" t="b">
         <v>0</v>
       </c>
       <c r="AA54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC54" t="b">
         <v>0</v>
       </c>
       <c r="AD54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF54" t="b">
         <v>0</v>
       </c>
       <c r="AG54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI54" t="b">
         <v>0</v>
@@ -7605,7 +7605,7 @@
         <v>2</v>
       </c>
       <c r="AK54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL54" t="b">
         <v>1</v>
@@ -7628,22 +7628,22 @@
         <v>226</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H55" t="b">
         <v>0</v>
       </c>
       <c r="I55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J55">
         <v>4</v>
@@ -7652,25 +7652,25 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
       </c>
       <c r="O55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="b">
         <v>0</v>
       </c>
       <c r="R55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S55">
         <v>4</v>
@@ -7679,46 +7679,46 @@
         <v>0</v>
       </c>
       <c r="U55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W55" t="b">
         <v>0</v>
       </c>
       <c r="X55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z55" t="b">
         <v>0</v>
       </c>
       <c r="AA55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC55" t="b">
         <v>0</v>
       </c>
       <c r="AD55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF55" t="b">
         <v>0</v>
       </c>
       <c r="AG55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI55" t="b">
         <v>0</v>
@@ -7727,7 +7727,7 @@
         <v>2</v>
       </c>
       <c r="AK55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL55" t="b">
         <v>1</v>
@@ -7750,22 +7750,22 @@
         <v>226</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H56" t="b">
         <v>0</v>
       </c>
       <c r="I56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J56">
         <v>4</v>
@@ -7774,25 +7774,25 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N56" t="b">
         <v>0</v>
       </c>
       <c r="O56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="b">
         <v>0</v>
       </c>
       <c r="R56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S56">
         <v>4</v>
@@ -7801,46 +7801,46 @@
         <v>0</v>
       </c>
       <c r="U56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W56" t="b">
         <v>0</v>
       </c>
       <c r="X56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z56" t="b">
         <v>0</v>
       </c>
       <c r="AA56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC56" t="b">
         <v>0</v>
       </c>
       <c r="AD56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF56" t="b">
         <v>0</v>
       </c>
       <c r="AG56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI56" t="b">
         <v>0</v>
@@ -7849,7 +7849,7 @@
         <v>2</v>
       </c>
       <c r="AK56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL56" t="b">
         <v>1</v>
@@ -7872,22 +7872,22 @@
         <v>226</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
       </c>
       <c r="F57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H57" t="b">
         <v>0</v>
       </c>
       <c r="I57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J57">
         <v>4</v>
@@ -7896,25 +7896,25 @@
         <v>0</v>
       </c>
       <c r="L57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N57" t="b">
         <v>0</v>
       </c>
       <c r="O57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q57" t="b">
         <v>0</v>
       </c>
       <c r="R57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S57">
         <v>4</v>
@@ -7923,46 +7923,46 @@
         <v>0</v>
       </c>
       <c r="U57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W57" t="b">
         <v>0</v>
       </c>
       <c r="X57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z57" t="b">
         <v>0</v>
       </c>
       <c r="AA57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC57" t="b">
         <v>0</v>
       </c>
       <c r="AD57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF57" t="b">
         <v>0</v>
       </c>
       <c r="AG57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI57" t="b">
         <v>0</v>
@@ -7971,7 +7971,7 @@
         <v>2</v>
       </c>
       <c r="AK57">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL57" t="b">
         <v>1</v>
@@ -7994,22 +7994,22 @@
         <v>226</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H58" t="b">
         <v>0</v>
       </c>
       <c r="I58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J58">
         <v>4</v>
@@ -8018,25 +8018,25 @@
         <v>0</v>
       </c>
       <c r="L58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
       </c>
       <c r="O58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q58" t="b">
         <v>0</v>
       </c>
       <c r="R58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S58">
         <v>4</v>
@@ -8045,46 +8045,46 @@
         <v>0</v>
       </c>
       <c r="U58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W58" t="b">
         <v>0</v>
       </c>
       <c r="X58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z58" t="b">
         <v>0</v>
       </c>
       <c r="AA58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC58" t="b">
         <v>0</v>
       </c>
       <c r="AD58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF58" t="b">
         <v>0</v>
       </c>
       <c r="AG58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI58" t="b">
         <v>0</v>
@@ -8093,7 +8093,7 @@
         <v>2</v>
       </c>
       <c r="AK58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL58" t="b">
         <v>1</v>
@@ -8116,22 +8116,22 @@
         <v>226</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
       </c>
       <c r="F59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H59" t="b">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J59">
         <v>4</v>
@@ -8140,25 +8140,25 @@
         <v>0</v>
       </c>
       <c r="L59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
       </c>
       <c r="O59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q59" t="b">
         <v>0</v>
       </c>
       <c r="R59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S59">
         <v>4</v>
@@ -8167,46 +8167,46 @@
         <v>0</v>
       </c>
       <c r="U59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W59" t="b">
         <v>0</v>
       </c>
       <c r="X59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z59" t="b">
         <v>0</v>
       </c>
       <c r="AA59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC59" t="b">
         <v>0</v>
       </c>
       <c r="AD59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF59" t="b">
         <v>0</v>
       </c>
       <c r="AG59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI59" t="b">
         <v>0</v>
@@ -8215,7 +8215,7 @@
         <v>2</v>
       </c>
       <c r="AK59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL59" t="b">
         <v>1</v>
@@ -8238,22 +8238,22 @@
         <v>226</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
       </c>
       <c r="F60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H60" t="b">
         <v>0</v>
       </c>
       <c r="I60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J60">
         <v>4</v>
@@ -8262,25 +8262,25 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
       </c>
       <c r="O60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="b">
         <v>0</v>
       </c>
       <c r="R60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S60">
         <v>4</v>
@@ -8289,46 +8289,46 @@
         <v>0</v>
       </c>
       <c r="U60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W60" t="b">
         <v>0</v>
       </c>
       <c r="X60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z60" t="b">
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC60" t="b">
         <v>0</v>
       </c>
       <c r="AD60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF60" t="b">
         <v>0</v>
       </c>
       <c r="AG60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI60" t="b">
         <v>0</v>
@@ -8337,7 +8337,7 @@
         <v>2</v>
       </c>
       <c r="AK60">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL60" t="b">
         <v>1</v>
@@ -8360,22 +8360,22 @@
         <v>226</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
       </c>
       <c r="F61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H61" t="b">
         <v>0</v>
       </c>
       <c r="I61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J61">
         <v>4</v>
@@ -8384,25 +8384,25 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
       </c>
       <c r="O61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q61" t="b">
         <v>0</v>
       </c>
       <c r="R61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S61">
         <v>4</v>
@@ -8411,46 +8411,46 @@
         <v>0</v>
       </c>
       <c r="U61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W61" t="b">
         <v>0</v>
       </c>
       <c r="X61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z61" t="b">
         <v>0</v>
       </c>
       <c r="AA61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC61" t="b">
         <v>0</v>
       </c>
       <c r="AD61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF61" t="b">
         <v>0</v>
       </c>
       <c r="AG61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI61" t="b">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         <v>2</v>
       </c>
       <c r="AK61">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL61" t="b">
         <v>1</v>
@@ -8482,22 +8482,22 @@
         <v>226</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H62" t="b">
         <v>0</v>
       </c>
       <c r="I62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J62">
         <v>4</v>
@@ -8506,25 +8506,25 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N62" t="b">
         <v>0</v>
       </c>
       <c r="O62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="b">
         <v>0</v>
       </c>
       <c r="R62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S62">
         <v>4</v>
@@ -8533,46 +8533,46 @@
         <v>0</v>
       </c>
       <c r="U62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W62" t="b">
         <v>0</v>
       </c>
       <c r="X62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z62" t="b">
         <v>0</v>
       </c>
       <c r="AA62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC62" t="b">
         <v>0</v>
       </c>
       <c r="AD62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF62" t="b">
         <v>0</v>
       </c>
       <c r="AG62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI62" t="b">
         <v>0</v>
@@ -8581,7 +8581,7 @@
         <v>2</v>
       </c>
       <c r="AK62">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL62" t="b">
         <v>1</v>
@@ -8604,22 +8604,22 @@
         <v>226</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H63" t="b">
         <v>0</v>
       </c>
       <c r="I63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J63">
         <v>4</v>
@@ -8628,25 +8628,25 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
       </c>
       <c r="O63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q63" t="b">
         <v>0</v>
       </c>
       <c r="R63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S63">
         <v>4</v>
@@ -8655,46 +8655,46 @@
         <v>0</v>
       </c>
       <c r="U63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W63" t="b">
         <v>0</v>
       </c>
       <c r="X63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z63" t="b">
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC63" t="b">
         <v>0</v>
       </c>
       <c r="AD63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF63" t="b">
         <v>0</v>
       </c>
       <c r="AG63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI63" t="b">
         <v>0</v>
@@ -8703,7 +8703,7 @@
         <v>2</v>
       </c>
       <c r="AK63">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL63" t="b">
         <v>1</v>
@@ -8848,22 +8848,22 @@
         <v>226</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
       </c>
       <c r="F65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H65" t="b">
         <v>0</v>
       </c>
       <c r="I65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J65">
         <v>4</v>
@@ -8872,25 +8872,25 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
       </c>
       <c r="O65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="b">
         <v>0</v>
       </c>
       <c r="R65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S65">
         <v>4</v>
@@ -8899,46 +8899,46 @@
         <v>0</v>
       </c>
       <c r="U65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W65" t="b">
         <v>0</v>
       </c>
       <c r="X65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z65" t="b">
         <v>0</v>
       </c>
       <c r="AA65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC65" t="b">
         <v>0</v>
       </c>
       <c r="AD65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF65" t="b">
         <v>0</v>
       </c>
       <c r="AG65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI65" t="b">
         <v>0</v>
@@ -8947,7 +8947,7 @@
         <v>2</v>
       </c>
       <c r="AK65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL65" t="b">
         <v>1</v>
@@ -8970,22 +8970,22 @@
         <v>226</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H66" t="b">
         <v>0</v>
       </c>
       <c r="I66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J66">
         <v>4</v>
@@ -8994,25 +8994,25 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
       </c>
       <c r="O66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="b">
         <v>0</v>
       </c>
       <c r="R66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S66">
         <v>4</v>
@@ -9021,46 +9021,46 @@
         <v>0</v>
       </c>
       <c r="U66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W66" t="b">
         <v>0</v>
       </c>
       <c r="X66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z66" t="b">
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC66" t="b">
         <v>0</v>
       </c>
       <c r="AD66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF66" t="b">
         <v>0</v>
       </c>
       <c r="AG66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI66" t="b">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>2</v>
       </c>
       <c r="AK66">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL66" t="b">
         <v>1</v>
@@ -9095,103 +9095,103 @@
         <v>1</v>
       </c>
       <c r="E67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J67">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S67">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL67" t="b">
         <v>1</v>
@@ -9458,22 +9458,22 @@
         <v>226</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E70" t="b">
         <v>0</v>
       </c>
       <c r="F70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H70" t="b">
         <v>0</v>
       </c>
       <c r="I70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J70">
         <v>4</v>
@@ -9482,25 +9482,25 @@
         <v>0</v>
       </c>
       <c r="L70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N70" t="b">
         <v>0</v>
       </c>
       <c r="O70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q70" t="b">
         <v>0</v>
       </c>
       <c r="R70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S70">
         <v>4</v>
@@ -9509,46 +9509,46 @@
         <v>0</v>
       </c>
       <c r="U70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W70" t="b">
         <v>0</v>
       </c>
       <c r="X70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z70" t="b">
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC70" t="b">
         <v>0</v>
       </c>
       <c r="AD70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF70" t="b">
         <v>0</v>
       </c>
       <c r="AG70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI70" t="b">
         <v>0</v>
@@ -9557,7 +9557,7 @@
         <v>2</v>
       </c>
       <c r="AK70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL70" t="b">
         <v>1</v>
@@ -9580,22 +9580,22 @@
         <v>226</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E71" t="b">
         <v>0</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H71" t="b">
         <v>0</v>
       </c>
       <c r="I71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J71">
         <v>4</v>
@@ -9604,25 +9604,25 @@
         <v>0</v>
       </c>
       <c r="L71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N71" t="b">
         <v>0</v>
       </c>
       <c r="O71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q71" t="b">
         <v>0</v>
       </c>
       <c r="R71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S71">
         <v>4</v>
@@ -9631,46 +9631,46 @@
         <v>0</v>
       </c>
       <c r="U71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W71" t="b">
         <v>0</v>
       </c>
       <c r="X71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z71" t="b">
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC71" t="b">
         <v>0</v>
       </c>
       <c r="AD71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF71" t="b">
         <v>0</v>
       </c>
       <c r="AG71">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI71" t="b">
         <v>0</v>
@@ -9679,7 +9679,7 @@
         <v>2</v>
       </c>
       <c r="AK71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL71" t="b">
         <v>1</v>
@@ -9702,22 +9702,22 @@
         <v>226</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" t="b">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H72" t="b">
         <v>0</v>
       </c>
       <c r="I72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J72">
         <v>4</v>
@@ -9726,25 +9726,25 @@
         <v>0</v>
       </c>
       <c r="L72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N72" t="b">
         <v>0</v>
       </c>
       <c r="O72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q72" t="b">
         <v>0</v>
       </c>
       <c r="R72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S72">
         <v>4</v>
@@ -9753,46 +9753,46 @@
         <v>0</v>
       </c>
       <c r="U72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W72" t="b">
         <v>0</v>
       </c>
       <c r="X72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z72" t="b">
         <v>0</v>
       </c>
       <c r="AA72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC72" t="b">
         <v>0</v>
       </c>
       <c r="AD72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF72" t="b">
         <v>0</v>
       </c>
       <c r="AG72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI72" t="b">
         <v>0</v>
@@ -9801,7 +9801,7 @@
         <v>2</v>
       </c>
       <c r="AK72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL72" t="b">
         <v>1</v>
@@ -9946,22 +9946,22 @@
         <v>226</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E74" t="b">
         <v>0</v>
       </c>
       <c r="F74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H74" t="b">
         <v>0</v>
       </c>
       <c r="I74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J74">
         <v>4</v>
@@ -9970,25 +9970,25 @@
         <v>0</v>
       </c>
       <c r="L74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N74" t="b">
         <v>0</v>
       </c>
       <c r="O74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q74" t="b">
         <v>0</v>
       </c>
       <c r="R74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S74">
         <v>4</v>
@@ -9997,46 +9997,46 @@
         <v>0</v>
       </c>
       <c r="U74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W74" t="b">
         <v>0</v>
       </c>
       <c r="X74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z74" t="b">
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC74" t="b">
         <v>0</v>
       </c>
       <c r="AD74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF74" t="b">
         <v>0</v>
       </c>
       <c r="AG74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI74" t="b">
         <v>0</v>
@@ -10045,7 +10045,7 @@
         <v>2</v>
       </c>
       <c r="AK74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL74" t="b">
         <v>1</v>
@@ -10068,22 +10068,22 @@
         <v>226</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E75" t="b">
         <v>0</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H75" t="b">
         <v>0</v>
       </c>
       <c r="I75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J75">
         <v>4</v>
@@ -10092,25 +10092,25 @@
         <v>0</v>
       </c>
       <c r="L75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N75" t="b">
         <v>0</v>
       </c>
       <c r="O75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q75" t="b">
         <v>0</v>
       </c>
       <c r="R75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S75">
         <v>4</v>
@@ -10119,46 +10119,46 @@
         <v>0</v>
       </c>
       <c r="U75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W75" t="b">
         <v>0</v>
       </c>
       <c r="X75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z75" t="b">
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC75" t="b">
         <v>0</v>
       </c>
       <c r="AD75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF75" t="b">
         <v>0</v>
       </c>
       <c r="AG75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI75" t="b">
         <v>0</v>
@@ -10167,7 +10167,7 @@
         <v>2</v>
       </c>
       <c r="AK75">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL75" t="b">
         <v>1</v>
@@ -10190,22 +10190,22 @@
         <v>226</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E76" t="b">
         <v>0</v>
       </c>
       <c r="F76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H76" t="b">
         <v>0</v>
       </c>
       <c r="I76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J76">
         <v>4</v>
@@ -10214,25 +10214,25 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N76" t="b">
         <v>0</v>
       </c>
       <c r="O76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q76" t="b">
         <v>0</v>
       </c>
       <c r="R76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S76">
         <v>4</v>
@@ -10241,46 +10241,46 @@
         <v>0</v>
       </c>
       <c r="U76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W76" t="b">
         <v>0</v>
       </c>
       <c r="X76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z76" t="b">
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC76" t="b">
         <v>0</v>
       </c>
       <c r="AD76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF76" t="b">
         <v>0</v>
       </c>
       <c r="AG76">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI76" t="b">
         <v>0</v>
@@ -10289,7 +10289,7 @@
         <v>2</v>
       </c>
       <c r="AK76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL76" t="b">
         <v>1</v>
@@ -10312,22 +10312,22 @@
         <v>226</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77" t="b">
         <v>0</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H77" t="b">
         <v>0</v>
       </c>
       <c r="I77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J77">
         <v>4</v>
@@ -10336,25 +10336,25 @@
         <v>0</v>
       </c>
       <c r="L77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N77" t="b">
         <v>0</v>
       </c>
       <c r="O77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q77" t="b">
         <v>0</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S77">
         <v>4</v>
@@ -10363,46 +10363,46 @@
         <v>0</v>
       </c>
       <c r="U77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W77" t="b">
         <v>0</v>
       </c>
       <c r="X77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z77" t="b">
         <v>0</v>
       </c>
       <c r="AA77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC77" t="b">
         <v>0</v>
       </c>
       <c r="AD77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF77" t="b">
         <v>0</v>
       </c>
       <c r="AG77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI77" t="b">
         <v>0</v>
@@ -10411,7 +10411,7 @@
         <v>2</v>
       </c>
       <c r="AK77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL77" t="b">
         <v>1</v>
@@ -10434,22 +10434,22 @@
         <v>226</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E78" t="b">
         <v>0</v>
       </c>
       <c r="F78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H78" t="b">
         <v>0</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J78">
         <v>4</v>
@@ -10458,25 +10458,25 @@
         <v>0</v>
       </c>
       <c r="L78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N78" t="b">
         <v>0</v>
       </c>
       <c r="O78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q78" t="b">
         <v>0</v>
       </c>
       <c r="R78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S78">
         <v>4</v>
@@ -10485,46 +10485,46 @@
         <v>0</v>
       </c>
       <c r="U78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W78" t="b">
         <v>0</v>
       </c>
       <c r="X78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z78" t="b">
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC78" t="b">
         <v>0</v>
       </c>
       <c r="AD78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF78" t="b">
         <v>0</v>
       </c>
       <c r="AG78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI78" t="b">
         <v>0</v>
@@ -10533,7 +10533,7 @@
         <v>2</v>
       </c>
       <c r="AK78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL78" t="b">
         <v>1</v>
@@ -10556,22 +10556,22 @@
         <v>226</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E79" t="b">
         <v>0</v>
       </c>
       <c r="F79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H79" t="b">
         <v>0</v>
       </c>
       <c r="I79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J79">
         <v>4</v>
@@ -10580,25 +10580,25 @@
         <v>0</v>
       </c>
       <c r="L79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N79" t="b">
         <v>0</v>
       </c>
       <c r="O79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q79" t="b">
         <v>0</v>
       </c>
       <c r="R79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S79">
         <v>4</v>
@@ -10607,46 +10607,46 @@
         <v>0</v>
       </c>
       <c r="U79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W79" t="b">
         <v>0</v>
       </c>
       <c r="X79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z79" t="b">
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC79" t="b">
         <v>0</v>
       </c>
       <c r="AD79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF79" t="b">
         <v>0</v>
       </c>
       <c r="AG79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI79" t="b">
         <v>0</v>
@@ -10655,7 +10655,7 @@
         <v>2</v>
       </c>
       <c r="AK79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL79" t="b">
         <v>1</v>
@@ -10678,22 +10678,22 @@
         <v>226</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E80" t="b">
         <v>0</v>
       </c>
       <c r="F80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H80" t="b">
         <v>0</v>
       </c>
       <c r="I80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J80">
         <v>4</v>
@@ -10702,25 +10702,25 @@
         <v>0</v>
       </c>
       <c r="L80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N80" t="b">
         <v>0</v>
       </c>
       <c r="O80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q80" t="b">
         <v>0</v>
       </c>
       <c r="R80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S80">
         <v>4</v>
@@ -10729,46 +10729,46 @@
         <v>0</v>
       </c>
       <c r="U80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W80" t="b">
         <v>0</v>
       </c>
       <c r="X80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z80" t="b">
         <v>0</v>
       </c>
       <c r="AA80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC80" t="b">
         <v>0</v>
       </c>
       <c r="AD80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF80" t="b">
         <v>0</v>
       </c>
       <c r="AG80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI80" t="b">
         <v>0</v>
@@ -10777,7 +10777,7 @@
         <v>2</v>
       </c>
       <c r="AK80">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL80" t="b">
         <v>1</v>
@@ -10922,22 +10922,22 @@
         <v>226</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E82" t="b">
         <v>0</v>
       </c>
       <c r="F82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H82" t="b">
         <v>0</v>
       </c>
       <c r="I82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J82">
         <v>4</v>
@@ -10946,25 +10946,25 @@
         <v>0</v>
       </c>
       <c r="L82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N82" t="b">
         <v>0</v>
       </c>
       <c r="O82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q82" t="b">
         <v>0</v>
       </c>
       <c r="R82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S82">
         <v>4</v>
@@ -10973,46 +10973,46 @@
         <v>0</v>
       </c>
       <c r="U82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W82" t="b">
         <v>0</v>
       </c>
       <c r="X82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z82" t="b">
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC82" t="b">
         <v>0</v>
       </c>
       <c r="AD82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF82" t="b">
         <v>0</v>
       </c>
       <c r="AG82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI82" t="b">
         <v>0</v>
@@ -11021,7 +11021,7 @@
         <v>2</v>
       </c>
       <c r="AK82">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL82" t="b">
         <v>1</v>
@@ -11044,22 +11044,22 @@
         <v>226</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E83" t="b">
         <v>0</v>
       </c>
       <c r="F83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H83" t="b">
         <v>0</v>
       </c>
       <c r="I83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J83">
         <v>4</v>
@@ -11068,25 +11068,25 @@
         <v>0</v>
       </c>
       <c r="L83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N83" t="b">
         <v>0</v>
       </c>
       <c r="O83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q83" t="b">
         <v>0</v>
       </c>
       <c r="R83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S83">
         <v>4</v>
@@ -11095,46 +11095,46 @@
         <v>0</v>
       </c>
       <c r="U83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W83" t="b">
         <v>0</v>
       </c>
       <c r="X83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z83" t="b">
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC83" t="b">
         <v>0</v>
       </c>
       <c r="AD83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF83" t="b">
         <v>0</v>
       </c>
       <c r="AG83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI83" t="b">
         <v>0</v>
@@ -11143,7 +11143,7 @@
         <v>2</v>
       </c>
       <c r="AK83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL83" t="b">
         <v>1</v>
@@ -11288,22 +11288,22 @@
         <v>226</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E85" t="b">
         <v>0</v>
       </c>
       <c r="F85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H85" t="b">
         <v>0</v>
       </c>
       <c r="I85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J85">
         <v>4</v>
@@ -11312,25 +11312,25 @@
         <v>0</v>
       </c>
       <c r="L85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N85" t="b">
         <v>0</v>
       </c>
       <c r="O85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q85" t="b">
         <v>0</v>
       </c>
       <c r="R85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S85">
         <v>4</v>
@@ -11339,46 +11339,46 @@
         <v>0</v>
       </c>
       <c r="U85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W85" t="b">
         <v>0</v>
       </c>
       <c r="X85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z85" t="b">
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC85" t="b">
         <v>0</v>
       </c>
       <c r="AD85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF85" t="b">
         <v>0</v>
       </c>
       <c r="AG85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI85" t="b">
         <v>0</v>
@@ -11387,7 +11387,7 @@
         <v>2</v>
       </c>
       <c r="AK85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL85" t="b">
         <v>1</v>
@@ -11410,22 +11410,22 @@
         <v>226</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" t="b">
         <v>0</v>
       </c>
       <c r="F86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H86" t="b">
         <v>0</v>
       </c>
       <c r="I86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J86">
         <v>4</v>
@@ -11434,25 +11434,25 @@
         <v>0</v>
       </c>
       <c r="L86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N86" t="b">
         <v>0</v>
       </c>
       <c r="O86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q86" t="b">
         <v>0</v>
       </c>
       <c r="R86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S86">
         <v>4</v>
@@ -11461,46 +11461,46 @@
         <v>0</v>
       </c>
       <c r="U86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W86" t="b">
         <v>0</v>
       </c>
       <c r="X86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z86" t="b">
         <v>0</v>
       </c>
       <c r="AA86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC86" t="b">
         <v>0</v>
       </c>
       <c r="AD86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF86" t="b">
         <v>0</v>
       </c>
       <c r="AG86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI86" t="b">
         <v>0</v>
@@ -11509,7 +11509,7 @@
         <v>2</v>
       </c>
       <c r="AK86">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL86" t="b">
         <v>1</v>
@@ -11532,22 +11532,22 @@
         <v>226</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E87" t="b">
         <v>0</v>
       </c>
       <c r="F87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H87" t="b">
         <v>0</v>
       </c>
       <c r="I87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J87">
         <v>4</v>
@@ -11556,25 +11556,25 @@
         <v>0</v>
       </c>
       <c r="L87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N87" t="b">
         <v>0</v>
       </c>
       <c r="O87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q87" t="b">
         <v>0</v>
       </c>
       <c r="R87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S87">
         <v>4</v>
@@ -11583,46 +11583,46 @@
         <v>0</v>
       </c>
       <c r="U87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W87" t="b">
         <v>0</v>
       </c>
       <c r="X87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z87" t="b">
         <v>0</v>
       </c>
       <c r="AA87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC87" t="b">
         <v>0</v>
       </c>
       <c r="AD87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF87" t="b">
         <v>0</v>
       </c>
       <c r="AG87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI87" t="b">
         <v>0</v>
@@ -11631,7 +11631,7 @@
         <v>2</v>
       </c>
       <c r="AK87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL87" t="b">
         <v>1</v>
@@ -11654,22 +11654,22 @@
         <v>226</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E88" t="b">
         <v>0</v>
       </c>
       <c r="F88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H88" t="b">
         <v>0</v>
       </c>
       <c r="I88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J88">
         <v>4</v>
@@ -11678,25 +11678,25 @@
         <v>0</v>
       </c>
       <c r="L88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N88" t="b">
         <v>0</v>
       </c>
       <c r="O88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q88" t="b">
         <v>0</v>
       </c>
       <c r="R88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S88">
         <v>4</v>
@@ -11705,46 +11705,46 @@
         <v>0</v>
       </c>
       <c r="U88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W88" t="b">
         <v>0</v>
       </c>
       <c r="X88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z88" t="b">
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC88" t="b">
         <v>0</v>
       </c>
       <c r="AD88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF88" t="b">
         <v>0</v>
       </c>
       <c r="AG88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI88" t="b">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         <v>2</v>
       </c>
       <c r="AK88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL88" t="b">
         <v>1</v>
@@ -11776,22 +11776,22 @@
         <v>226</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E89" t="b">
         <v>0</v>
       </c>
       <c r="F89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H89" t="b">
         <v>0</v>
       </c>
       <c r="I89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J89">
         <v>4</v>
@@ -11800,25 +11800,25 @@
         <v>0</v>
       </c>
       <c r="L89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N89" t="b">
         <v>0</v>
       </c>
       <c r="O89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q89" t="b">
         <v>0</v>
       </c>
       <c r="R89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S89">
         <v>4</v>
@@ -11827,46 +11827,46 @@
         <v>0</v>
       </c>
       <c r="U89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W89" t="b">
         <v>0</v>
       </c>
       <c r="X89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z89" t="b">
         <v>0</v>
       </c>
       <c r="AA89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC89" t="b">
         <v>0</v>
       </c>
       <c r="AD89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF89" t="b">
         <v>0</v>
       </c>
       <c r="AG89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI89" t="b">
         <v>0</v>
@@ -11875,7 +11875,7 @@
         <v>2</v>
       </c>
       <c r="AK89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL89" t="b">
         <v>1</v>
@@ -11901,103 +11901,103 @@
         <v>1</v>
       </c>
       <c r="E90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J90">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S90">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL90" t="b">
         <v>1</v>
@@ -12020,22 +12020,22 @@
         <v>226</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E91" t="b">
         <v>0</v>
       </c>
       <c r="F91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H91" t="b">
         <v>0</v>
       </c>
       <c r="I91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J91">
         <v>4</v>
@@ -12044,25 +12044,25 @@
         <v>0</v>
       </c>
       <c r="L91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N91" t="b">
         <v>0</v>
       </c>
       <c r="O91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q91" t="b">
         <v>0</v>
       </c>
       <c r="R91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S91">
         <v>4</v>
@@ -12071,46 +12071,46 @@
         <v>0</v>
       </c>
       <c r="U91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W91" t="b">
         <v>0</v>
       </c>
       <c r="X91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z91" t="b">
         <v>0</v>
       </c>
       <c r="AA91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC91" t="b">
         <v>0</v>
       </c>
       <c r="AD91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF91" t="b">
         <v>0</v>
       </c>
       <c r="AG91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI91" t="b">
         <v>0</v>
@@ -12119,7 +12119,7 @@
         <v>2</v>
       </c>
       <c r="AK91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL91" t="b">
         <v>1</v>
@@ -12142,22 +12142,22 @@
         <v>226</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E92" t="b">
         <v>0</v>
       </c>
       <c r="F92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H92" t="b">
         <v>0</v>
       </c>
       <c r="I92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J92">
         <v>4</v>
@@ -12166,25 +12166,25 @@
         <v>0</v>
       </c>
       <c r="L92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N92" t="b">
         <v>0</v>
       </c>
       <c r="O92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q92" t="b">
         <v>0</v>
       </c>
       <c r="R92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S92">
         <v>4</v>
@@ -12193,46 +12193,46 @@
         <v>0</v>
       </c>
       <c r="U92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W92" t="b">
         <v>0</v>
       </c>
       <c r="X92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z92" t="b">
         <v>0</v>
       </c>
       <c r="AA92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC92" t="b">
         <v>0</v>
       </c>
       <c r="AD92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF92" t="b">
         <v>0</v>
       </c>
       <c r="AG92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI92" t="b">
         <v>0</v>
@@ -12241,7 +12241,7 @@
         <v>2</v>
       </c>
       <c r="AK92">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL92" t="b">
         <v>1</v>
@@ -12267,103 +12267,103 @@
         <v>1</v>
       </c>
       <c r="E93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J93">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S93">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL93" t="b">
         <v>1</v>
@@ -12389,103 +12389,103 @@
         <v>1</v>
       </c>
       <c r="E94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J94">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S94">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL94" t="b">
         <v>1</v>

--- a/Data/Rules/Fluff & Tuff Rules Matrix.xlsx
+++ b/Data/Rules/Fluff & Tuff Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="177">
   <si>
     <t>SKU</t>
   </si>
@@ -136,9 +136,6 @@
     <t>HQ_Max</t>
   </si>
   <si>
-    <t>15556</t>
-  </si>
-  <si>
     <t>10189</t>
   </si>
   <si>
@@ -157,36 +154,12 @@
     <t>28653</t>
   </si>
   <si>
-    <t>28635</t>
-  </si>
-  <si>
-    <t>28633</t>
-  </si>
-  <si>
     <t>10877</t>
   </si>
   <si>
-    <t>10635</t>
-  </si>
-  <si>
-    <t>28636</t>
-  </si>
-  <si>
     <t>10232</t>
   </si>
   <si>
-    <t>28637</t>
-  </si>
-  <si>
-    <t>16642</t>
-  </si>
-  <si>
-    <t>28638</t>
-  </si>
-  <si>
-    <t>28183</t>
-  </si>
-  <si>
     <t>11062</t>
   </si>
   <si>
@@ -196,18 +169,12 @@
     <t>10096</t>
   </si>
   <si>
-    <t>28180</t>
-  </si>
-  <si>
     <t>28792</t>
   </si>
   <si>
     <t>30555</t>
   </si>
   <si>
-    <t>10833</t>
-  </si>
-  <si>
     <t>10245</t>
   </si>
   <si>
@@ -217,12 +184,6 @@
     <t>30556</t>
   </si>
   <si>
-    <t>28179</t>
-  </si>
-  <si>
-    <t>27119</t>
-  </si>
-  <si>
     <t>10285</t>
   </si>
   <si>
@@ -247,27 +208,18 @@
     <t>10016</t>
   </si>
   <si>
-    <t>10876</t>
-  </si>
-  <si>
     <t>11051</t>
   </si>
   <si>
     <t>10885</t>
   </si>
   <si>
-    <t>26662</t>
-  </si>
-  <si>
     <t>29955</t>
   </si>
   <si>
     <t>10953</t>
   </si>
   <si>
-    <t>28632</t>
-  </si>
-  <si>
     <t>10338</t>
   </si>
   <si>
@@ -277,9 +229,6 @@
     <t>17048</t>
   </si>
   <si>
-    <t>10535</t>
-  </si>
-  <si>
     <t>10286</t>
   </si>
   <si>
@@ -322,24 +271,12 @@
     <t>28795</t>
   </si>
   <si>
-    <t>28631</t>
-  </si>
-  <si>
     <t>28796</t>
   </si>
   <si>
     <t>10313</t>
   </si>
   <si>
-    <t>10185</t>
-  </si>
-  <si>
-    <t>28634</t>
-  </si>
-  <si>
-    <t>28184</t>
-  </si>
-  <si>
     <t>11065</t>
   </si>
   <si>
@@ -349,9 +286,6 @@
     <t>10874</t>
   </si>
   <si>
-    <t>10796</t>
-  </si>
-  <si>
     <t>11059</t>
   </si>
   <si>
@@ -361,9 +295,6 @@
     <t>10945</t>
   </si>
   <si>
-    <t>15227</t>
-  </si>
-  <si>
     <t>29956</t>
   </si>
   <si>
@@ -373,18 +304,12 @@
     <t>11462</t>
   </si>
   <si>
-    <t>28182</t>
-  </si>
-  <si>
     <t>10188</t>
   </si>
   <si>
     <t>26309</t>
   </si>
   <si>
-    <t>26661</t>
-  </si>
-  <si>
     <t>29957</t>
   </si>
   <si>
@@ -400,22 +325,19 @@
     <t>16596</t>
   </si>
   <si>
-    <t>15321</t>
-  </si>
-  <si>
     <t>28760</t>
   </si>
   <si>
     <t>11068</t>
   </si>
   <si>
-    <t>16062</t>
-  </si>
-  <si>
-    <t>10576</t>
-  </si>
-  <si>
-    <t>F&amp;T Ally Starfish 9" SM</t>
+    <t>5655311</t>
+  </si>
+  <si>
+    <t>8585052</t>
+  </si>
+  <si>
+    <t>5852101</t>
   </si>
   <si>
     <t>F&amp;T Anderson Fox</t>
@@ -436,36 +358,12 @@
     <t>F&amp;T Beach Ball Mini</t>
   </si>
   <si>
-    <t>F&amp;T Belle Unicorn HOL</t>
-  </si>
-  <si>
-    <t>F&amp;T Betty Gingerbread Girl LG HOL</t>
-  </si>
-  <si>
     <t>F&amp;T Big Daddy Gator</t>
   </si>
   <si>
-    <t>F&amp;T Bleu Narwhal</t>
-  </si>
-  <si>
-    <t>F&amp;T Brody Dragon HOL</t>
-  </si>
-  <si>
     <t>F&amp;T Burt Lake Trout</t>
   </si>
   <si>
-    <t>F&amp;T Candy Cane MD HOL 25</t>
-  </si>
-  <si>
-    <t>F&amp;T Candy Cane Med HOL</t>
-  </si>
-  <si>
-    <t>F&amp;T Candy Cane XL HOL 25</t>
-  </si>
-  <si>
-    <t>F&amp;T Candy Cane XS HOL</t>
-  </si>
-  <si>
     <t>F&amp;T Cedar Salmon</t>
   </si>
   <si>
@@ -475,18 +373,12 @@
     <t>F&amp;T Charlie Triceratops</t>
   </si>
   <si>
-    <t>F&amp;T Christmas Tree HOL</t>
-  </si>
-  <si>
     <t>F&amp;T Cici Tropical Fish</t>
   </si>
   <si>
     <t>F&amp;T Claude Squid Squeakerless</t>
   </si>
   <si>
-    <t>F&amp;T Clement Mouse HOL</t>
-  </si>
-  <si>
     <t>F&amp;T Cubby Bear</t>
   </si>
   <si>
@@ -496,12 +388,6 @@
     <t>F&amp;T Dottie Pufferfish</t>
   </si>
   <si>
-    <t>F&amp;T Eddie Sloth HOL</t>
-  </si>
-  <si>
-    <t>F&amp;T Emily Brontosaurus VDC</t>
-  </si>
-  <si>
     <t>F&amp;T Esmerelda Turtle</t>
   </si>
   <si>
@@ -526,27 +412,18 @@
     <t>F&amp;T Harry Otter</t>
   </si>
   <si>
-    <t>F&amp;T Hendrix the Fox VDC</t>
-  </si>
-  <si>
     <t>F&amp;T Ike Pheasant</t>
   </si>
   <si>
     <t>F&amp;T Inca Alpaca</t>
   </si>
   <si>
-    <t>F&amp;T Jan Bear HOL</t>
-  </si>
-  <si>
     <t>F&amp;T Jasper Fox</t>
   </si>
   <si>
     <t>F&amp;T Jessica Bunny</t>
   </si>
   <si>
-    <t>F&amp;T Judy Gingerbread Girl SM HOL</t>
-  </si>
-  <si>
     <t>F&amp;T Katie Caterpillar</t>
   </si>
   <si>
@@ -556,9 +433,6 @@
     <t>F&amp;T Leopard Bone SM</t>
   </si>
   <si>
-    <t>F&amp;T Lobo Wolf Pup DC</t>
-  </si>
-  <si>
     <t>F&amp;T Lola Flamingo</t>
   </si>
   <si>
@@ -601,24 +475,12 @@
     <t>F&amp;T Phyllis Crab</t>
   </si>
   <si>
-    <t>F&amp;T Pops Koala HOL</t>
-  </si>
-  <si>
     <t>F&amp;T Rachel Lobster Mini</t>
   </si>
   <si>
     <t>F&amp;T Red Squirrel</t>
   </si>
   <si>
-    <t>F&amp;T Reese Rabbit</t>
-  </si>
-  <si>
-    <t>F&amp;T Retro Tree Candy HOL</t>
-  </si>
-  <si>
-    <t>F&amp;T Robbie Reindeer HOL</t>
-  </si>
-  <si>
     <t>F&amp;T Rocket Raccoon</t>
   </si>
   <si>
@@ -628,9 +490,6 @@
     <t>F&amp;T Ruby Rainbow Trout</t>
   </si>
   <si>
-    <t>F&amp;T Sadie Bear DC</t>
-  </si>
-  <si>
     <t>F&amp;T Savannah Baby Gator</t>
   </si>
   <si>
@@ -640,9 +499,6 @@
     <t>F&amp;T Shelly Turtle</t>
   </si>
   <si>
-    <t>F&amp;T Soccer Ball 7"</t>
-  </si>
-  <si>
     <t>F&amp;T Soccer Ball Blue</t>
   </si>
   <si>
@@ -652,18 +508,12 @@
     <t>F&amp;T Spicy Caterpillar 11" SM</t>
   </si>
   <si>
-    <t>F&amp;T Spruce Moose HOL</t>
-  </si>
-  <si>
     <t>F&amp;T Squeakerless Soccer Ball</t>
   </si>
   <si>
     <t>F&amp;T Squirt Octopus</t>
   </si>
   <si>
-    <t>F&amp;T Stan Bear HOL</t>
-  </si>
-  <si>
     <t>F&amp;T Sterling Fox</t>
   </si>
   <si>
@@ -679,19 +529,19 @@
     <t>F&amp;T Tiger Bone MD</t>
   </si>
   <si>
-    <t>F&amp;T Tiny T-Rex 8" SM</t>
-  </si>
-  <si>
     <t>F&amp;T Troy Beaver</t>
   </si>
   <si>
     <t>F&amp;T Wally Mallard</t>
   </si>
   <si>
-    <t>F&amp;T Zebra Ball LG</t>
-  </si>
-  <si>
-    <t>F&amp;T Ziggy Starfish</t>
+    <t>F&amp;T Soccer Ball Lemonade</t>
+  </si>
+  <si>
+    <t>F&amp;T Soccer Ball Limeade</t>
+  </si>
+  <si>
+    <t>F&amp;T Zebra Ball SM SO</t>
   </si>
   <si>
     <t>Fluff &amp; Tuff</t>
@@ -1026,7 +876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN94"/>
+  <dimension ref="A1:AN69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:40">
@@ -1156,112 +1006,112 @@
         <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL2" t="b">
         <v>1</v>
@@ -1278,10 +1128,10 @@
         <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D3">
         <v>4</v>
@@ -1400,10 +1250,10 @@
         <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D4">
         <v>4</v>
@@ -1522,13 +1372,13 @@
         <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1644,10 +1494,10 @@
         <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>137</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -1766,13 +1616,13 @@
         <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="C7" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1888,13 +1738,13 @@
         <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C8" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -2010,112 +1860,112 @@
         <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>140</v>
+        <v>115</v>
       </c>
       <c r="C9" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL9" t="b">
         <v>1</v>
@@ -2132,112 +1982,112 @@
         <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="C10" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL10" t="b">
         <v>1</v>
@@ -2254,13 +2104,13 @@
         <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="C11" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="b">
         <v>0</v>
@@ -2376,112 +2226,112 @@
         <v>50</v>
       </c>
       <c r="B12" t="s">
-        <v>143</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL12" t="b">
         <v>1</v>
@@ -2498,112 +2348,112 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="C13" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL13" t="b">
         <v>1</v>
@@ -2620,10 +2470,10 @@
         <v>52</v>
       </c>
       <c r="B14" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -2742,112 +2592,112 @@
         <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL15" t="b">
         <v>1</v>
@@ -2864,112 +2714,112 @@
         <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="C16" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL16" t="b">
         <v>1</v>
@@ -2986,112 +2836,112 @@
         <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="C17" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL17" t="b">
         <v>1</v>
@@ -3108,112 +2958,112 @@
         <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="C18" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL18" t="b">
         <v>1</v>
@@ -3230,13 +3080,13 @@
         <v>57</v>
       </c>
       <c r="B19" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -3352,10 +3202,10 @@
         <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>151</v>
+        <v>126</v>
       </c>
       <c r="C20" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -3474,13 +3324,13 @@
         <v>59</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="C21" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -3596,112 +3446,112 @@
         <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>153</v>
+        <v>128</v>
       </c>
       <c r="C22" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL22" t="b">
         <v>1</v>
@@ -3718,10 +3568,10 @@
         <v>61</v>
       </c>
       <c r="B23" t="s">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="C23" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D23">
         <v>4</v>
@@ -3840,10 +3690,10 @@
         <v>62</v>
       </c>
       <c r="B24" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="C24" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D24">
         <v>4</v>
@@ -3962,112 +3812,112 @@
         <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="C25" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL25" t="b">
         <v>1</v>
@@ -4084,10 +3934,10 @@
         <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>132</v>
       </c>
       <c r="C26" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D26">
         <v>4</v>
@@ -4206,10 +4056,10 @@
         <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="C27" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D27">
         <v>4</v>
@@ -4328,13 +4178,13 @@
         <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="C28" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -4450,112 +4300,112 @@
         <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="C29" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL29" t="b">
         <v>1</v>
@@ -4572,112 +4422,112 @@
         <v>68</v>
       </c>
       <c r="B30" t="s">
-        <v>161</v>
+        <v>136</v>
       </c>
       <c r="C30" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL30" t="b">
         <v>1</v>
@@ -4694,10 +4544,10 @@
         <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="C31" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -4816,112 +4666,112 @@
         <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>163</v>
+        <v>138</v>
       </c>
       <c r="C32" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="b">
         <v>1</v>
@@ -4938,10 +4788,10 @@
         <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>164</v>
+        <v>139</v>
       </c>
       <c r="C33" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -5060,13 +4910,13 @@
         <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="C34" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -5182,10 +5032,10 @@
         <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>141</v>
       </c>
       <c r="C35" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D35">
         <v>4</v>
@@ -5304,10 +5154,10 @@
         <v>74</v>
       </c>
       <c r="B36" t="s">
-        <v>167</v>
+        <v>142</v>
       </c>
       <c r="C36" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -5426,10 +5276,10 @@
         <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="C37" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -5548,10 +5398,10 @@
         <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C38" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -5670,112 +5520,112 @@
         <v>77</v>
       </c>
       <c r="B39" t="s">
-        <v>170</v>
+        <v>145</v>
       </c>
       <c r="C39" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL39" t="b">
         <v>1</v>
@@ -5792,10 +5642,10 @@
         <v>78</v>
       </c>
       <c r="B40" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="C40" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -5914,10 +5764,10 @@
         <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="C41" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -6036,112 +5886,112 @@
         <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="C42" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL42" t="b">
         <v>1</v>
@@ -6158,13 +6008,13 @@
         <v>81</v>
       </c>
       <c r="B43" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="C43" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D43">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -6280,13 +6130,13 @@
         <v>82</v>
       </c>
       <c r="B44" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="C44" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -6402,112 +6252,112 @@
         <v>83</v>
       </c>
       <c r="B45" t="s">
+        <v>151</v>
+      </c>
+      <c r="C45" t="s">
         <v>176</v>
       </c>
-      <c r="C45" t="s">
-        <v>226</v>
-      </c>
       <c r="D45">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI45" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL45" t="b">
         <v>1</v>
@@ -6524,10 +6374,10 @@
         <v>84</v>
       </c>
       <c r="B46" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="C46" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D46">
         <v>4</v>
@@ -6646,13 +6496,13 @@
         <v>85</v>
       </c>
       <c r="B47" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="C47" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E47" t="b">
         <v>0</v>
@@ -6768,112 +6618,112 @@
         <v>86</v>
       </c>
       <c r="B48" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="C48" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI48" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL48" t="b">
         <v>1</v>
@@ -6890,112 +6740,112 @@
         <v>87</v>
       </c>
       <c r="B49" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="C49" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI49" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL49" t="b">
         <v>1</v>
@@ -7012,10 +6862,10 @@
         <v>88</v>
       </c>
       <c r="B50" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="C50" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D50">
         <v>4</v>
@@ -7134,10 +6984,10 @@
         <v>89</v>
       </c>
       <c r="B51" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="C51" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D51">
         <v>4</v>
@@ -7256,10 +7106,10 @@
         <v>90</v>
       </c>
       <c r="B52" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="C52" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D52">
         <v>4</v>
@@ -7378,10 +7228,10 @@
         <v>91</v>
       </c>
       <c r="B53" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="C53" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D53">
         <v>4</v>
@@ -7500,10 +7350,10 @@
         <v>92</v>
       </c>
       <c r="B54" t="s">
-        <v>185</v>
+        <v>160</v>
       </c>
       <c r="C54" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D54">
         <v>4</v>
@@ -7622,13 +7472,13 @@
         <v>93</v>
       </c>
       <c r="B55" t="s">
-        <v>186</v>
+        <v>161</v>
       </c>
       <c r="C55" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -7744,10 +7594,10 @@
         <v>94</v>
       </c>
       <c r="B56" t="s">
-        <v>187</v>
+        <v>162</v>
       </c>
       <c r="C56" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -7866,10 +7716,10 @@
         <v>95</v>
       </c>
       <c r="B57" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="C57" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -7988,13 +7838,13 @@
         <v>96</v>
       </c>
       <c r="B58" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="C58" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -8110,10 +7960,10 @@
         <v>97</v>
       </c>
       <c r="B59" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="C59" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D59">
         <v>4</v>
@@ -8232,10 +8082,10 @@
         <v>98</v>
       </c>
       <c r="B60" t="s">
-        <v>191</v>
+        <v>166</v>
       </c>
       <c r="C60" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D60">
         <v>4</v>
@@ -8354,13 +8204,13 @@
         <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>192</v>
+        <v>167</v>
       </c>
       <c r="C61" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
@@ -8476,10 +8326,10 @@
         <v>100</v>
       </c>
       <c r="B62" t="s">
-        <v>193</v>
+        <v>168</v>
       </c>
       <c r="C62" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D62">
         <v>4</v>
@@ -8598,10 +8448,10 @@
         <v>101</v>
       </c>
       <c r="B63" t="s">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="C63" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D63">
         <v>4</v>
@@ -8720,112 +8570,112 @@
         <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>195</v>
+        <v>170</v>
       </c>
       <c r="C64" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL64" t="b">
         <v>1</v>
@@ -8842,13 +8692,13 @@
         <v>103</v>
       </c>
       <c r="B65" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="C65" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
@@ -8964,10 +8814,10 @@
         <v>104</v>
       </c>
       <c r="B66" t="s">
-        <v>197</v>
+        <v>172</v>
       </c>
       <c r="C66" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D66">
         <v>4</v>
@@ -9086,10 +8936,10 @@
         <v>105</v>
       </c>
       <c r="B67" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="C67" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -9208,10 +9058,10 @@
         <v>106</v>
       </c>
       <c r="B68" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="C68" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D68">
         <v>1</v>
@@ -9330,10 +9180,10 @@
         <v>107</v>
       </c>
       <c r="B69" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="C69" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -9444,3056 +9294,6 @@
         <v>0</v>
       </c>
       <c r="AN69">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:40">
-      <c r="A70" t="s">
-        <v>108</v>
-      </c>
-      <c r="B70" t="s">
-        <v>201</v>
-      </c>
-      <c r="C70" t="s">
-        <v>226</v>
-      </c>
-      <c r="D70">
-        <v>4</v>
-      </c>
-      <c r="E70" t="b">
-        <v>0</v>
-      </c>
-      <c r="F70">
-        <v>1</v>
-      </c>
-      <c r="G70">
-        <v>2</v>
-      </c>
-      <c r="H70" t="b">
-        <v>0</v>
-      </c>
-      <c r="I70">
-        <v>2</v>
-      </c>
-      <c r="J70">
-        <v>4</v>
-      </c>
-      <c r="K70" t="b">
-        <v>0</v>
-      </c>
-      <c r="L70">
-        <v>1</v>
-      </c>
-      <c r="M70">
-        <v>2</v>
-      </c>
-      <c r="N70" t="b">
-        <v>0</v>
-      </c>
-      <c r="O70">
-        <v>1</v>
-      </c>
-      <c r="P70">
-        <v>2</v>
-      </c>
-      <c r="Q70" t="b">
-        <v>0</v>
-      </c>
-      <c r="R70">
-        <v>2</v>
-      </c>
-      <c r="S70">
-        <v>4</v>
-      </c>
-      <c r="T70" t="b">
-        <v>0</v>
-      </c>
-      <c r="U70">
-        <v>1</v>
-      </c>
-      <c r="V70">
-        <v>2</v>
-      </c>
-      <c r="W70" t="b">
-        <v>0</v>
-      </c>
-      <c r="X70">
-        <v>1</v>
-      </c>
-      <c r="Y70">
-        <v>2</v>
-      </c>
-      <c r="Z70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA70">
-        <v>1</v>
-      </c>
-      <c r="AB70">
-        <v>2</v>
-      </c>
-      <c r="AC70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD70">
-        <v>1</v>
-      </c>
-      <c r="AE70">
-        <v>2</v>
-      </c>
-      <c r="AF70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG70">
-        <v>1</v>
-      </c>
-      <c r="AH70">
-        <v>2</v>
-      </c>
-      <c r="AI70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ70">
-        <v>2</v>
-      </c>
-      <c r="AK70">
-        <v>4</v>
-      </c>
-      <c r="AL70" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM70">
-        <v>0</v>
-      </c>
-      <c r="AN70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:40">
-      <c r="A71" t="s">
-        <v>109</v>
-      </c>
-      <c r="B71" t="s">
-        <v>202</v>
-      </c>
-      <c r="C71" t="s">
-        <v>226</v>
-      </c>
-      <c r="D71">
-        <v>4</v>
-      </c>
-      <c r="E71" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71">
-        <v>1</v>
-      </c>
-      <c r="G71">
-        <v>2</v>
-      </c>
-      <c r="H71" t="b">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>2</v>
-      </c>
-      <c r="J71">
-        <v>4</v>
-      </c>
-      <c r="K71" t="b">
-        <v>0</v>
-      </c>
-      <c r="L71">
-        <v>1</v>
-      </c>
-      <c r="M71">
-        <v>2</v>
-      </c>
-      <c r="N71" t="b">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>1</v>
-      </c>
-      <c r="P71">
-        <v>2</v>
-      </c>
-      <c r="Q71" t="b">
-        <v>0</v>
-      </c>
-      <c r="R71">
-        <v>2</v>
-      </c>
-      <c r="S71">
-        <v>4</v>
-      </c>
-      <c r="T71" t="b">
-        <v>0</v>
-      </c>
-      <c r="U71">
-        <v>1</v>
-      </c>
-      <c r="V71">
-        <v>2</v>
-      </c>
-      <c r="W71" t="b">
-        <v>0</v>
-      </c>
-      <c r="X71">
-        <v>1</v>
-      </c>
-      <c r="Y71">
-        <v>2</v>
-      </c>
-      <c r="Z71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA71">
-        <v>1</v>
-      </c>
-      <c r="AB71">
-        <v>2</v>
-      </c>
-      <c r="AC71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD71">
-        <v>1</v>
-      </c>
-      <c r="AE71">
-        <v>2</v>
-      </c>
-      <c r="AF71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71">
-        <v>1</v>
-      </c>
-      <c r="AH71">
-        <v>2</v>
-      </c>
-      <c r="AI71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ71">
-        <v>2</v>
-      </c>
-      <c r="AK71">
-        <v>4</v>
-      </c>
-      <c r="AL71" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM71">
-        <v>0</v>
-      </c>
-      <c r="AN71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:40">
-      <c r="A72" t="s">
-        <v>110</v>
-      </c>
-      <c r="B72" t="s">
-        <v>203</v>
-      </c>
-      <c r="C72" t="s">
-        <v>226</v>
-      </c>
-      <c r="D72">
-        <v>4</v>
-      </c>
-      <c r="E72" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72">
-        <v>1</v>
-      </c>
-      <c r="G72">
-        <v>2</v>
-      </c>
-      <c r="H72" t="b">
-        <v>0</v>
-      </c>
-      <c r="I72">
-        <v>2</v>
-      </c>
-      <c r="J72">
-        <v>4</v>
-      </c>
-      <c r="K72" t="b">
-        <v>0</v>
-      </c>
-      <c r="L72">
-        <v>1</v>
-      </c>
-      <c r="M72">
-        <v>2</v>
-      </c>
-      <c r="N72" t="b">
-        <v>0</v>
-      </c>
-      <c r="O72">
-        <v>1</v>
-      </c>
-      <c r="P72">
-        <v>2</v>
-      </c>
-      <c r="Q72" t="b">
-        <v>0</v>
-      </c>
-      <c r="R72">
-        <v>2</v>
-      </c>
-      <c r="S72">
-        <v>4</v>
-      </c>
-      <c r="T72" t="b">
-        <v>0</v>
-      </c>
-      <c r="U72">
-        <v>1</v>
-      </c>
-      <c r="V72">
-        <v>2</v>
-      </c>
-      <c r="W72" t="b">
-        <v>0</v>
-      </c>
-      <c r="X72">
-        <v>1</v>
-      </c>
-      <c r="Y72">
-        <v>2</v>
-      </c>
-      <c r="Z72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA72">
-        <v>1</v>
-      </c>
-      <c r="AB72">
-        <v>2</v>
-      </c>
-      <c r="AC72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD72">
-        <v>1</v>
-      </c>
-      <c r="AE72">
-        <v>2</v>
-      </c>
-      <c r="AF72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72">
-        <v>1</v>
-      </c>
-      <c r="AH72">
-        <v>2</v>
-      </c>
-      <c r="AI72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ72">
-        <v>2</v>
-      </c>
-      <c r="AK72">
-        <v>4</v>
-      </c>
-      <c r="AL72" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM72">
-        <v>0</v>
-      </c>
-      <c r="AN72">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:40">
-      <c r="A73" t="s">
-        <v>111</v>
-      </c>
-      <c r="B73" t="s">
-        <v>204</v>
-      </c>
-      <c r="C73" t="s">
-        <v>226</v>
-      </c>
-      <c r="D73">
-        <v>1</v>
-      </c>
-      <c r="E73" t="b">
-        <v>1</v>
-      </c>
-      <c r="F73">
-        <v>0</v>
-      </c>
-      <c r="G73">
-        <v>0</v>
-      </c>
-      <c r="H73" t="b">
-        <v>1</v>
-      </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="J73">
-        <v>0</v>
-      </c>
-      <c r="K73" t="b">
-        <v>1</v>
-      </c>
-      <c r="L73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <v>0</v>
-      </c>
-      <c r="N73" t="b">
-        <v>1</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
-      </c>
-      <c r="P73">
-        <v>0</v>
-      </c>
-      <c r="Q73" t="b">
-        <v>1</v>
-      </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
-        <v>0</v>
-      </c>
-      <c r="T73" t="b">
-        <v>1</v>
-      </c>
-      <c r="U73">
-        <v>0</v>
-      </c>
-      <c r="V73">
-        <v>0</v>
-      </c>
-      <c r="W73" t="b">
-        <v>1</v>
-      </c>
-      <c r="X73">
-        <v>0</v>
-      </c>
-      <c r="Y73">
-        <v>0</v>
-      </c>
-      <c r="Z73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA73">
-        <v>0</v>
-      </c>
-      <c r="AB73">
-        <v>0</v>
-      </c>
-      <c r="AC73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD73">
-        <v>0</v>
-      </c>
-      <c r="AE73">
-        <v>0</v>
-      </c>
-      <c r="AF73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG73">
-        <v>0</v>
-      </c>
-      <c r="AH73">
-        <v>0</v>
-      </c>
-      <c r="AI73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ73">
-        <v>0</v>
-      </c>
-      <c r="AK73">
-        <v>0</v>
-      </c>
-      <c r="AL73" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM73">
-        <v>0</v>
-      </c>
-      <c r="AN73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:40">
-      <c r="A74" t="s">
-        <v>112</v>
-      </c>
-      <c r="B74" t="s">
-        <v>205</v>
-      </c>
-      <c r="C74" t="s">
-        <v>226</v>
-      </c>
-      <c r="D74">
-        <v>4</v>
-      </c>
-      <c r="E74" t="b">
-        <v>0</v>
-      </c>
-      <c r="F74">
-        <v>1</v>
-      </c>
-      <c r="G74">
-        <v>2</v>
-      </c>
-      <c r="H74" t="b">
-        <v>0</v>
-      </c>
-      <c r="I74">
-        <v>2</v>
-      </c>
-      <c r="J74">
-        <v>4</v>
-      </c>
-      <c r="K74" t="b">
-        <v>0</v>
-      </c>
-      <c r="L74">
-        <v>1</v>
-      </c>
-      <c r="M74">
-        <v>2</v>
-      </c>
-      <c r="N74" t="b">
-        <v>0</v>
-      </c>
-      <c r="O74">
-        <v>1</v>
-      </c>
-      <c r="P74">
-        <v>2</v>
-      </c>
-      <c r="Q74" t="b">
-        <v>0</v>
-      </c>
-      <c r="R74">
-        <v>2</v>
-      </c>
-      <c r="S74">
-        <v>4</v>
-      </c>
-      <c r="T74" t="b">
-        <v>0</v>
-      </c>
-      <c r="U74">
-        <v>1</v>
-      </c>
-      <c r="V74">
-        <v>2</v>
-      </c>
-      <c r="W74" t="b">
-        <v>0</v>
-      </c>
-      <c r="X74">
-        <v>1</v>
-      </c>
-      <c r="Y74">
-        <v>2</v>
-      </c>
-      <c r="Z74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA74">
-        <v>1</v>
-      </c>
-      <c r="AB74">
-        <v>2</v>
-      </c>
-      <c r="AC74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD74">
-        <v>1</v>
-      </c>
-      <c r="AE74">
-        <v>2</v>
-      </c>
-      <c r="AF74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG74">
-        <v>1</v>
-      </c>
-      <c r="AH74">
-        <v>2</v>
-      </c>
-      <c r="AI74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ74">
-        <v>2</v>
-      </c>
-      <c r="AK74">
-        <v>4</v>
-      </c>
-      <c r="AL74" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM74">
-        <v>0</v>
-      </c>
-      <c r="AN74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:40">
-      <c r="A75" t="s">
-        <v>113</v>
-      </c>
-      <c r="B75" t="s">
-        <v>206</v>
-      </c>
-      <c r="C75" t="s">
-        <v>226</v>
-      </c>
-      <c r="D75">
-        <v>4</v>
-      </c>
-      <c r="E75" t="b">
-        <v>0</v>
-      </c>
-      <c r="F75">
-        <v>1</v>
-      </c>
-      <c r="G75">
-        <v>2</v>
-      </c>
-      <c r="H75" t="b">
-        <v>0</v>
-      </c>
-      <c r="I75">
-        <v>2</v>
-      </c>
-      <c r="J75">
-        <v>4</v>
-      </c>
-      <c r="K75" t="b">
-        <v>0</v>
-      </c>
-      <c r="L75">
-        <v>1</v>
-      </c>
-      <c r="M75">
-        <v>2</v>
-      </c>
-      <c r="N75" t="b">
-        <v>0</v>
-      </c>
-      <c r="O75">
-        <v>1</v>
-      </c>
-      <c r="P75">
-        <v>2</v>
-      </c>
-      <c r="Q75" t="b">
-        <v>0</v>
-      </c>
-      <c r="R75">
-        <v>2</v>
-      </c>
-      <c r="S75">
-        <v>4</v>
-      </c>
-      <c r="T75" t="b">
-        <v>0</v>
-      </c>
-      <c r="U75">
-        <v>1</v>
-      </c>
-      <c r="V75">
-        <v>2</v>
-      </c>
-      <c r="W75" t="b">
-        <v>0</v>
-      </c>
-      <c r="X75">
-        <v>1</v>
-      </c>
-      <c r="Y75">
-        <v>2</v>
-      </c>
-      <c r="Z75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA75">
-        <v>1</v>
-      </c>
-      <c r="AB75">
-        <v>2</v>
-      </c>
-      <c r="AC75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD75">
-        <v>1</v>
-      </c>
-      <c r="AE75">
-        <v>2</v>
-      </c>
-      <c r="AF75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG75">
-        <v>1</v>
-      </c>
-      <c r="AH75">
-        <v>2</v>
-      </c>
-      <c r="AI75" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ75">
-        <v>2</v>
-      </c>
-      <c r="AK75">
-        <v>4</v>
-      </c>
-      <c r="AL75" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM75">
-        <v>0</v>
-      </c>
-      <c r="AN75">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:40">
-      <c r="A76" t="s">
-        <v>114</v>
-      </c>
-      <c r="B76" t="s">
-        <v>207</v>
-      </c>
-      <c r="C76" t="s">
-        <v>226</v>
-      </c>
-      <c r="D76">
-        <v>4</v>
-      </c>
-      <c r="E76" t="b">
-        <v>0</v>
-      </c>
-      <c r="F76">
-        <v>1</v>
-      </c>
-      <c r="G76">
-        <v>2</v>
-      </c>
-      <c r="H76" t="b">
-        <v>0</v>
-      </c>
-      <c r="I76">
-        <v>2</v>
-      </c>
-      <c r="J76">
-        <v>4</v>
-      </c>
-      <c r="K76" t="b">
-        <v>0</v>
-      </c>
-      <c r="L76">
-        <v>1</v>
-      </c>
-      <c r="M76">
-        <v>2</v>
-      </c>
-      <c r="N76" t="b">
-        <v>0</v>
-      </c>
-      <c r="O76">
-        <v>1</v>
-      </c>
-      <c r="P76">
-        <v>2</v>
-      </c>
-      <c r="Q76" t="b">
-        <v>0</v>
-      </c>
-      <c r="R76">
-        <v>2</v>
-      </c>
-      <c r="S76">
-        <v>4</v>
-      </c>
-      <c r="T76" t="b">
-        <v>0</v>
-      </c>
-      <c r="U76">
-        <v>1</v>
-      </c>
-      <c r="V76">
-        <v>2</v>
-      </c>
-      <c r="W76" t="b">
-        <v>0</v>
-      </c>
-      <c r="X76">
-        <v>1</v>
-      </c>
-      <c r="Y76">
-        <v>2</v>
-      </c>
-      <c r="Z76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA76">
-        <v>1</v>
-      </c>
-      <c r="AB76">
-        <v>2</v>
-      </c>
-      <c r="AC76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD76">
-        <v>1</v>
-      </c>
-      <c r="AE76">
-        <v>2</v>
-      </c>
-      <c r="AF76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG76">
-        <v>1</v>
-      </c>
-      <c r="AH76">
-        <v>2</v>
-      </c>
-      <c r="AI76" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ76">
-        <v>2</v>
-      </c>
-      <c r="AK76">
-        <v>4</v>
-      </c>
-      <c r="AL76" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM76">
-        <v>0</v>
-      </c>
-      <c r="AN76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:40">
-      <c r="A77" t="s">
-        <v>115</v>
-      </c>
-      <c r="B77" t="s">
-        <v>208</v>
-      </c>
-      <c r="C77" t="s">
-        <v>226</v>
-      </c>
-      <c r="D77">
-        <v>3</v>
-      </c>
-      <c r="E77" t="b">
-        <v>0</v>
-      </c>
-      <c r="F77">
-        <v>1</v>
-      </c>
-      <c r="G77">
-        <v>2</v>
-      </c>
-      <c r="H77" t="b">
-        <v>0</v>
-      </c>
-      <c r="I77">
-        <v>2</v>
-      </c>
-      <c r="J77">
-        <v>4</v>
-      </c>
-      <c r="K77" t="b">
-        <v>0</v>
-      </c>
-      <c r="L77">
-        <v>1</v>
-      </c>
-      <c r="M77">
-        <v>2</v>
-      </c>
-      <c r="N77" t="b">
-        <v>0</v>
-      </c>
-      <c r="O77">
-        <v>1</v>
-      </c>
-      <c r="P77">
-        <v>2</v>
-      </c>
-      <c r="Q77" t="b">
-        <v>0</v>
-      </c>
-      <c r="R77">
-        <v>2</v>
-      </c>
-      <c r="S77">
-        <v>4</v>
-      </c>
-      <c r="T77" t="b">
-        <v>0</v>
-      </c>
-      <c r="U77">
-        <v>1</v>
-      </c>
-      <c r="V77">
-        <v>2</v>
-      </c>
-      <c r="W77" t="b">
-        <v>0</v>
-      </c>
-      <c r="X77">
-        <v>1</v>
-      </c>
-      <c r="Y77">
-        <v>2</v>
-      </c>
-      <c r="Z77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA77">
-        <v>1</v>
-      </c>
-      <c r="AB77">
-        <v>2</v>
-      </c>
-      <c r="AC77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD77">
-        <v>1</v>
-      </c>
-      <c r="AE77">
-        <v>2</v>
-      </c>
-      <c r="AF77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG77">
-        <v>1</v>
-      </c>
-      <c r="AH77">
-        <v>2</v>
-      </c>
-      <c r="AI77" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ77">
-        <v>2</v>
-      </c>
-      <c r="AK77">
-        <v>4</v>
-      </c>
-      <c r="AL77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM77">
-        <v>0</v>
-      </c>
-      <c r="AN77">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:40">
-      <c r="A78" t="s">
-        <v>116</v>
-      </c>
-      <c r="B78" t="s">
-        <v>209</v>
-      </c>
-      <c r="C78" t="s">
-        <v>226</v>
-      </c>
-      <c r="D78">
-        <v>3</v>
-      </c>
-      <c r="E78" t="b">
-        <v>0</v>
-      </c>
-      <c r="F78">
-        <v>1</v>
-      </c>
-      <c r="G78">
-        <v>2</v>
-      </c>
-      <c r="H78" t="b">
-        <v>0</v>
-      </c>
-      <c r="I78">
-        <v>2</v>
-      </c>
-      <c r="J78">
-        <v>4</v>
-      </c>
-      <c r="K78" t="b">
-        <v>0</v>
-      </c>
-      <c r="L78">
-        <v>1</v>
-      </c>
-      <c r="M78">
-        <v>2</v>
-      </c>
-      <c r="N78" t="b">
-        <v>0</v>
-      </c>
-      <c r="O78">
-        <v>1</v>
-      </c>
-      <c r="P78">
-        <v>2</v>
-      </c>
-      <c r="Q78" t="b">
-        <v>0</v>
-      </c>
-      <c r="R78">
-        <v>2</v>
-      </c>
-      <c r="S78">
-        <v>4</v>
-      </c>
-      <c r="T78" t="b">
-        <v>0</v>
-      </c>
-      <c r="U78">
-        <v>1</v>
-      </c>
-      <c r="V78">
-        <v>2</v>
-      </c>
-      <c r="W78" t="b">
-        <v>0</v>
-      </c>
-      <c r="X78">
-        <v>1</v>
-      </c>
-      <c r="Y78">
-        <v>2</v>
-      </c>
-      <c r="Z78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA78">
-        <v>1</v>
-      </c>
-      <c r="AB78">
-        <v>2</v>
-      </c>
-      <c r="AC78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD78">
-        <v>1</v>
-      </c>
-      <c r="AE78">
-        <v>2</v>
-      </c>
-      <c r="AF78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG78">
-        <v>1</v>
-      </c>
-      <c r="AH78">
-        <v>2</v>
-      </c>
-      <c r="AI78" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ78">
-        <v>2</v>
-      </c>
-      <c r="AK78">
-        <v>4</v>
-      </c>
-      <c r="AL78" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM78">
-        <v>0</v>
-      </c>
-      <c r="AN78">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:40">
-      <c r="A79" t="s">
-        <v>117</v>
-      </c>
-      <c r="B79" t="s">
-        <v>210</v>
-      </c>
-      <c r="C79" t="s">
-        <v>226</v>
-      </c>
-      <c r="D79">
-        <v>4</v>
-      </c>
-      <c r="E79" t="b">
-        <v>0</v>
-      </c>
-      <c r="F79">
-        <v>1</v>
-      </c>
-      <c r="G79">
-        <v>2</v>
-      </c>
-      <c r="H79" t="b">
-        <v>0</v>
-      </c>
-      <c r="I79">
-        <v>2</v>
-      </c>
-      <c r="J79">
-        <v>4</v>
-      </c>
-      <c r="K79" t="b">
-        <v>0</v>
-      </c>
-      <c r="L79">
-        <v>1</v>
-      </c>
-      <c r="M79">
-        <v>2</v>
-      </c>
-      <c r="N79" t="b">
-        <v>0</v>
-      </c>
-      <c r="O79">
-        <v>1</v>
-      </c>
-      <c r="P79">
-        <v>2</v>
-      </c>
-      <c r="Q79" t="b">
-        <v>0</v>
-      </c>
-      <c r="R79">
-        <v>2</v>
-      </c>
-      <c r="S79">
-        <v>4</v>
-      </c>
-      <c r="T79" t="b">
-        <v>0</v>
-      </c>
-      <c r="U79">
-        <v>1</v>
-      </c>
-      <c r="V79">
-        <v>2</v>
-      </c>
-      <c r="W79" t="b">
-        <v>0</v>
-      </c>
-      <c r="X79">
-        <v>1</v>
-      </c>
-      <c r="Y79">
-        <v>2</v>
-      </c>
-      <c r="Z79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA79">
-        <v>1</v>
-      </c>
-      <c r="AB79">
-        <v>2</v>
-      </c>
-      <c r="AC79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD79">
-        <v>1</v>
-      </c>
-      <c r="AE79">
-        <v>2</v>
-      </c>
-      <c r="AF79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG79">
-        <v>1</v>
-      </c>
-      <c r="AH79">
-        <v>2</v>
-      </c>
-      <c r="AI79" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ79">
-        <v>2</v>
-      </c>
-      <c r="AK79">
-        <v>4</v>
-      </c>
-      <c r="AL79" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM79">
-        <v>0</v>
-      </c>
-      <c r="AN79">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:40">
-      <c r="A80" t="s">
-        <v>118</v>
-      </c>
-      <c r="B80" t="s">
-        <v>211</v>
-      </c>
-      <c r="C80" t="s">
-        <v>226</v>
-      </c>
-      <c r="D80">
-        <v>4</v>
-      </c>
-      <c r="E80" t="b">
-        <v>0</v>
-      </c>
-      <c r="F80">
-        <v>1</v>
-      </c>
-      <c r="G80">
-        <v>2</v>
-      </c>
-      <c r="H80" t="b">
-        <v>0</v>
-      </c>
-      <c r="I80">
-        <v>2</v>
-      </c>
-      <c r="J80">
-        <v>4</v>
-      </c>
-      <c r="K80" t="b">
-        <v>0</v>
-      </c>
-      <c r="L80">
-        <v>1</v>
-      </c>
-      <c r="M80">
-        <v>2</v>
-      </c>
-      <c r="N80" t="b">
-        <v>0</v>
-      </c>
-      <c r="O80">
-        <v>1</v>
-      </c>
-      <c r="P80">
-        <v>2</v>
-      </c>
-      <c r="Q80" t="b">
-        <v>0</v>
-      </c>
-      <c r="R80">
-        <v>2</v>
-      </c>
-      <c r="S80">
-        <v>4</v>
-      </c>
-      <c r="T80" t="b">
-        <v>0</v>
-      </c>
-      <c r="U80">
-        <v>1</v>
-      </c>
-      <c r="V80">
-        <v>2</v>
-      </c>
-      <c r="W80" t="b">
-        <v>0</v>
-      </c>
-      <c r="X80">
-        <v>1</v>
-      </c>
-      <c r="Y80">
-        <v>2</v>
-      </c>
-      <c r="Z80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA80">
-        <v>1</v>
-      </c>
-      <c r="AB80">
-        <v>2</v>
-      </c>
-      <c r="AC80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD80">
-        <v>1</v>
-      </c>
-      <c r="AE80">
-        <v>2</v>
-      </c>
-      <c r="AF80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG80">
-        <v>1</v>
-      </c>
-      <c r="AH80">
-        <v>2</v>
-      </c>
-      <c r="AI80" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ80">
-        <v>2</v>
-      </c>
-      <c r="AK80">
-        <v>4</v>
-      </c>
-      <c r="AL80" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM80">
-        <v>0</v>
-      </c>
-      <c r="AN80">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:40">
-      <c r="A81" t="s">
-        <v>119</v>
-      </c>
-      <c r="B81" t="s">
-        <v>212</v>
-      </c>
-      <c r="C81" t="s">
-        <v>226</v>
-      </c>
-      <c r="D81">
-        <v>1</v>
-      </c>
-      <c r="E81" t="b">
-        <v>1</v>
-      </c>
-      <c r="F81">
-        <v>0</v>
-      </c>
-      <c r="G81">
-        <v>0</v>
-      </c>
-      <c r="H81" t="b">
-        <v>1</v>
-      </c>
-      <c r="I81">
-        <v>0</v>
-      </c>
-      <c r="J81">
-        <v>0</v>
-      </c>
-      <c r="K81" t="b">
-        <v>1</v>
-      </c>
-      <c r="L81">
-        <v>0</v>
-      </c>
-      <c r="M81">
-        <v>0</v>
-      </c>
-      <c r="N81" t="b">
-        <v>1</v>
-      </c>
-      <c r="O81">
-        <v>0</v>
-      </c>
-      <c r="P81">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="b">
-        <v>1</v>
-      </c>
-      <c r="R81">
-        <v>0</v>
-      </c>
-      <c r="S81">
-        <v>0</v>
-      </c>
-      <c r="T81" t="b">
-        <v>1</v>
-      </c>
-      <c r="U81">
-        <v>0</v>
-      </c>
-      <c r="V81">
-        <v>0</v>
-      </c>
-      <c r="W81" t="b">
-        <v>1</v>
-      </c>
-      <c r="X81">
-        <v>0</v>
-      </c>
-      <c r="Y81">
-        <v>0</v>
-      </c>
-      <c r="Z81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA81">
-        <v>0</v>
-      </c>
-      <c r="AB81">
-        <v>0</v>
-      </c>
-      <c r="AC81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD81">
-        <v>0</v>
-      </c>
-      <c r="AE81">
-        <v>0</v>
-      </c>
-      <c r="AF81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG81">
-        <v>0</v>
-      </c>
-      <c r="AH81">
-        <v>0</v>
-      </c>
-      <c r="AI81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ81">
-        <v>0</v>
-      </c>
-      <c r="AK81">
-        <v>0</v>
-      </c>
-      <c r="AL81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM81">
-        <v>0</v>
-      </c>
-      <c r="AN81">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:40">
-      <c r="A82" t="s">
-        <v>120</v>
-      </c>
-      <c r="B82" t="s">
-        <v>213</v>
-      </c>
-      <c r="C82" t="s">
-        <v>226</v>
-      </c>
-      <c r="D82">
-        <v>3</v>
-      </c>
-      <c r="E82" t="b">
-        <v>0</v>
-      </c>
-      <c r="F82">
-        <v>1</v>
-      </c>
-      <c r="G82">
-        <v>2</v>
-      </c>
-      <c r="H82" t="b">
-        <v>0</v>
-      </c>
-      <c r="I82">
-        <v>2</v>
-      </c>
-      <c r="J82">
-        <v>4</v>
-      </c>
-      <c r="K82" t="b">
-        <v>0</v>
-      </c>
-      <c r="L82">
-        <v>1</v>
-      </c>
-      <c r="M82">
-        <v>2</v>
-      </c>
-      <c r="N82" t="b">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>1</v>
-      </c>
-      <c r="P82">
-        <v>2</v>
-      </c>
-      <c r="Q82" t="b">
-        <v>0</v>
-      </c>
-      <c r="R82">
-        <v>2</v>
-      </c>
-      <c r="S82">
-        <v>4</v>
-      </c>
-      <c r="T82" t="b">
-        <v>0</v>
-      </c>
-      <c r="U82">
-        <v>1</v>
-      </c>
-      <c r="V82">
-        <v>2</v>
-      </c>
-      <c r="W82" t="b">
-        <v>0</v>
-      </c>
-      <c r="X82">
-        <v>1</v>
-      </c>
-      <c r="Y82">
-        <v>2</v>
-      </c>
-      <c r="Z82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA82">
-        <v>1</v>
-      </c>
-      <c r="AB82">
-        <v>2</v>
-      </c>
-      <c r="AC82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD82">
-        <v>1</v>
-      </c>
-      <c r="AE82">
-        <v>2</v>
-      </c>
-      <c r="AF82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG82">
-        <v>1</v>
-      </c>
-      <c r="AH82">
-        <v>2</v>
-      </c>
-      <c r="AI82" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ82">
-        <v>2</v>
-      </c>
-      <c r="AK82">
-        <v>4</v>
-      </c>
-      <c r="AL82" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM82">
-        <v>0</v>
-      </c>
-      <c r="AN82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:40">
-      <c r="A83" t="s">
-        <v>121</v>
-      </c>
-      <c r="B83" t="s">
-        <v>214</v>
-      </c>
-      <c r="C83" t="s">
-        <v>226</v>
-      </c>
-      <c r="D83">
-        <v>4</v>
-      </c>
-      <c r="E83" t="b">
-        <v>0</v>
-      </c>
-      <c r="F83">
-        <v>1</v>
-      </c>
-      <c r="G83">
-        <v>2</v>
-      </c>
-      <c r="H83" t="b">
-        <v>0</v>
-      </c>
-      <c r="I83">
-        <v>2</v>
-      </c>
-      <c r="J83">
-        <v>4</v>
-      </c>
-      <c r="K83" t="b">
-        <v>0</v>
-      </c>
-      <c r="L83">
-        <v>1</v>
-      </c>
-      <c r="M83">
-        <v>2</v>
-      </c>
-      <c r="N83" t="b">
-        <v>0</v>
-      </c>
-      <c r="O83">
-        <v>1</v>
-      </c>
-      <c r="P83">
-        <v>2</v>
-      </c>
-      <c r="Q83" t="b">
-        <v>0</v>
-      </c>
-      <c r="R83">
-        <v>2</v>
-      </c>
-      <c r="S83">
-        <v>4</v>
-      </c>
-      <c r="T83" t="b">
-        <v>0</v>
-      </c>
-      <c r="U83">
-        <v>1</v>
-      </c>
-      <c r="V83">
-        <v>2</v>
-      </c>
-      <c r="W83" t="b">
-        <v>0</v>
-      </c>
-      <c r="X83">
-        <v>1</v>
-      </c>
-      <c r="Y83">
-        <v>2</v>
-      </c>
-      <c r="Z83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA83">
-        <v>1</v>
-      </c>
-      <c r="AB83">
-        <v>2</v>
-      </c>
-      <c r="AC83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD83">
-        <v>1</v>
-      </c>
-      <c r="AE83">
-        <v>2</v>
-      </c>
-      <c r="AF83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG83">
-        <v>1</v>
-      </c>
-      <c r="AH83">
-        <v>2</v>
-      </c>
-      <c r="AI83" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ83">
-        <v>2</v>
-      </c>
-      <c r="AK83">
-        <v>4</v>
-      </c>
-      <c r="AL83" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM83">
-        <v>0</v>
-      </c>
-      <c r="AN83">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="1:40">
-      <c r="A84" t="s">
-        <v>122</v>
-      </c>
-      <c r="B84" t="s">
-        <v>215</v>
-      </c>
-      <c r="C84" t="s">
-        <v>226</v>
-      </c>
-      <c r="D84">
-        <v>1</v>
-      </c>
-      <c r="E84" t="b">
-        <v>1</v>
-      </c>
-      <c r="F84">
-        <v>0</v>
-      </c>
-      <c r="G84">
-        <v>0</v>
-      </c>
-      <c r="H84" t="b">
-        <v>1</v>
-      </c>
-      <c r="I84">
-        <v>0</v>
-      </c>
-      <c r="J84">
-        <v>0</v>
-      </c>
-      <c r="K84" t="b">
-        <v>1</v>
-      </c>
-      <c r="L84">
-        <v>0</v>
-      </c>
-      <c r="M84">
-        <v>0</v>
-      </c>
-      <c r="N84" t="b">
-        <v>1</v>
-      </c>
-      <c r="O84">
-        <v>0</v>
-      </c>
-      <c r="P84">
-        <v>0</v>
-      </c>
-      <c r="Q84" t="b">
-        <v>1</v>
-      </c>
-      <c r="R84">
-        <v>0</v>
-      </c>
-      <c r="S84">
-        <v>0</v>
-      </c>
-      <c r="T84" t="b">
-        <v>1</v>
-      </c>
-      <c r="U84">
-        <v>0</v>
-      </c>
-      <c r="V84">
-        <v>0</v>
-      </c>
-      <c r="W84" t="b">
-        <v>1</v>
-      </c>
-      <c r="X84">
-        <v>0</v>
-      </c>
-      <c r="Y84">
-        <v>0</v>
-      </c>
-      <c r="Z84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA84">
-        <v>0</v>
-      </c>
-      <c r="AB84">
-        <v>0</v>
-      </c>
-      <c r="AC84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD84">
-        <v>0</v>
-      </c>
-      <c r="AE84">
-        <v>0</v>
-      </c>
-      <c r="AF84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG84">
-        <v>0</v>
-      </c>
-      <c r="AH84">
-        <v>0</v>
-      </c>
-      <c r="AI84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ84">
-        <v>0</v>
-      </c>
-      <c r="AK84">
-        <v>0</v>
-      </c>
-      <c r="AL84" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM84">
-        <v>0</v>
-      </c>
-      <c r="AN84">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:40">
-      <c r="A85" t="s">
-        <v>123</v>
-      </c>
-      <c r="B85" t="s">
-        <v>216</v>
-      </c>
-      <c r="C85" t="s">
-        <v>226</v>
-      </c>
-      <c r="D85">
-        <v>4</v>
-      </c>
-      <c r="E85" t="b">
-        <v>0</v>
-      </c>
-      <c r="F85">
-        <v>1</v>
-      </c>
-      <c r="G85">
-        <v>2</v>
-      </c>
-      <c r="H85" t="b">
-        <v>0</v>
-      </c>
-      <c r="I85">
-        <v>2</v>
-      </c>
-      <c r="J85">
-        <v>4</v>
-      </c>
-      <c r="K85" t="b">
-        <v>0</v>
-      </c>
-      <c r="L85">
-        <v>1</v>
-      </c>
-      <c r="M85">
-        <v>2</v>
-      </c>
-      <c r="N85" t="b">
-        <v>0</v>
-      </c>
-      <c r="O85">
-        <v>1</v>
-      </c>
-      <c r="P85">
-        <v>2</v>
-      </c>
-      <c r="Q85" t="b">
-        <v>0</v>
-      </c>
-      <c r="R85">
-        <v>2</v>
-      </c>
-      <c r="S85">
-        <v>4</v>
-      </c>
-      <c r="T85" t="b">
-        <v>0</v>
-      </c>
-      <c r="U85">
-        <v>1</v>
-      </c>
-      <c r="V85">
-        <v>2</v>
-      </c>
-      <c r="W85" t="b">
-        <v>0</v>
-      </c>
-      <c r="X85">
-        <v>1</v>
-      </c>
-      <c r="Y85">
-        <v>2</v>
-      </c>
-      <c r="Z85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA85">
-        <v>1</v>
-      </c>
-      <c r="AB85">
-        <v>2</v>
-      </c>
-      <c r="AC85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD85">
-        <v>1</v>
-      </c>
-      <c r="AE85">
-        <v>2</v>
-      </c>
-      <c r="AF85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG85">
-        <v>1</v>
-      </c>
-      <c r="AH85">
-        <v>2</v>
-      </c>
-      <c r="AI85" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ85">
-        <v>2</v>
-      </c>
-      <c r="AK85">
-        <v>4</v>
-      </c>
-      <c r="AL85" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM85">
-        <v>0</v>
-      </c>
-      <c r="AN85">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:40">
-      <c r="A86" t="s">
-        <v>124</v>
-      </c>
-      <c r="B86" t="s">
-        <v>217</v>
-      </c>
-      <c r="C86" t="s">
-        <v>226</v>
-      </c>
-      <c r="D86">
-        <v>3</v>
-      </c>
-      <c r="E86" t="b">
-        <v>0</v>
-      </c>
-      <c r="F86">
-        <v>1</v>
-      </c>
-      <c r="G86">
-        <v>2</v>
-      </c>
-      <c r="H86" t="b">
-        <v>0</v>
-      </c>
-      <c r="I86">
-        <v>2</v>
-      </c>
-      <c r="J86">
-        <v>4</v>
-      </c>
-      <c r="K86" t="b">
-        <v>0</v>
-      </c>
-      <c r="L86">
-        <v>1</v>
-      </c>
-      <c r="M86">
-        <v>2</v>
-      </c>
-      <c r="N86" t="b">
-        <v>0</v>
-      </c>
-      <c r="O86">
-        <v>1</v>
-      </c>
-      <c r="P86">
-        <v>2</v>
-      </c>
-      <c r="Q86" t="b">
-        <v>0</v>
-      </c>
-      <c r="R86">
-        <v>2</v>
-      </c>
-      <c r="S86">
-        <v>4</v>
-      </c>
-      <c r="T86" t="b">
-        <v>0</v>
-      </c>
-      <c r="U86">
-        <v>1</v>
-      </c>
-      <c r="V86">
-        <v>2</v>
-      </c>
-      <c r="W86" t="b">
-        <v>0</v>
-      </c>
-      <c r="X86">
-        <v>1</v>
-      </c>
-      <c r="Y86">
-        <v>2</v>
-      </c>
-      <c r="Z86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA86">
-        <v>1</v>
-      </c>
-      <c r="AB86">
-        <v>2</v>
-      </c>
-      <c r="AC86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD86">
-        <v>1</v>
-      </c>
-      <c r="AE86">
-        <v>2</v>
-      </c>
-      <c r="AF86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG86">
-        <v>1</v>
-      </c>
-      <c r="AH86">
-        <v>2</v>
-      </c>
-      <c r="AI86" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ86">
-        <v>2</v>
-      </c>
-      <c r="AK86">
-        <v>4</v>
-      </c>
-      <c r="AL86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM86">
-        <v>0</v>
-      </c>
-      <c r="AN86">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="1:40">
-      <c r="A87" t="s">
-        <v>125</v>
-      </c>
-      <c r="B87" t="s">
-        <v>218</v>
-      </c>
-      <c r="C87" t="s">
-        <v>226</v>
-      </c>
-      <c r="D87">
-        <v>4</v>
-      </c>
-      <c r="E87" t="b">
-        <v>0</v>
-      </c>
-      <c r="F87">
-        <v>1</v>
-      </c>
-      <c r="G87">
-        <v>2</v>
-      </c>
-      <c r="H87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I87">
-        <v>2</v>
-      </c>
-      <c r="J87">
-        <v>4</v>
-      </c>
-      <c r="K87" t="b">
-        <v>0</v>
-      </c>
-      <c r="L87">
-        <v>1</v>
-      </c>
-      <c r="M87">
-        <v>2</v>
-      </c>
-      <c r="N87" t="b">
-        <v>0</v>
-      </c>
-      <c r="O87">
-        <v>1</v>
-      </c>
-      <c r="P87">
-        <v>2</v>
-      </c>
-      <c r="Q87" t="b">
-        <v>0</v>
-      </c>
-      <c r="R87">
-        <v>2</v>
-      </c>
-      <c r="S87">
-        <v>4</v>
-      </c>
-      <c r="T87" t="b">
-        <v>0</v>
-      </c>
-      <c r="U87">
-        <v>1</v>
-      </c>
-      <c r="V87">
-        <v>2</v>
-      </c>
-      <c r="W87" t="b">
-        <v>0</v>
-      </c>
-      <c r="X87">
-        <v>1</v>
-      </c>
-      <c r="Y87">
-        <v>2</v>
-      </c>
-      <c r="Z87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA87">
-        <v>1</v>
-      </c>
-      <c r="AB87">
-        <v>2</v>
-      </c>
-      <c r="AC87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD87">
-        <v>1</v>
-      </c>
-      <c r="AE87">
-        <v>2</v>
-      </c>
-      <c r="AF87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG87">
-        <v>1</v>
-      </c>
-      <c r="AH87">
-        <v>2</v>
-      </c>
-      <c r="AI87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ87">
-        <v>2</v>
-      </c>
-      <c r="AK87">
-        <v>4</v>
-      </c>
-      <c r="AL87" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM87">
-        <v>0</v>
-      </c>
-      <c r="AN87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:40">
-      <c r="A88" t="s">
-        <v>126</v>
-      </c>
-      <c r="B88" t="s">
-        <v>219</v>
-      </c>
-      <c r="C88" t="s">
-        <v>226</v>
-      </c>
-      <c r="D88">
-        <v>4</v>
-      </c>
-      <c r="E88" t="b">
-        <v>0</v>
-      </c>
-      <c r="F88">
-        <v>1</v>
-      </c>
-      <c r="G88">
-        <v>2</v>
-      </c>
-      <c r="H88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I88">
-        <v>2</v>
-      </c>
-      <c r="J88">
-        <v>4</v>
-      </c>
-      <c r="K88" t="b">
-        <v>0</v>
-      </c>
-      <c r="L88">
-        <v>1</v>
-      </c>
-      <c r="M88">
-        <v>2</v>
-      </c>
-      <c r="N88" t="b">
-        <v>0</v>
-      </c>
-      <c r="O88">
-        <v>1</v>
-      </c>
-      <c r="P88">
-        <v>2</v>
-      </c>
-      <c r="Q88" t="b">
-        <v>0</v>
-      </c>
-      <c r="R88">
-        <v>2</v>
-      </c>
-      <c r="S88">
-        <v>4</v>
-      </c>
-      <c r="T88" t="b">
-        <v>0</v>
-      </c>
-      <c r="U88">
-        <v>1</v>
-      </c>
-      <c r="V88">
-        <v>2</v>
-      </c>
-      <c r="W88" t="b">
-        <v>0</v>
-      </c>
-      <c r="X88">
-        <v>1</v>
-      </c>
-      <c r="Y88">
-        <v>2</v>
-      </c>
-      <c r="Z88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA88">
-        <v>1</v>
-      </c>
-      <c r="AB88">
-        <v>2</v>
-      </c>
-      <c r="AC88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD88">
-        <v>1</v>
-      </c>
-      <c r="AE88">
-        <v>2</v>
-      </c>
-      <c r="AF88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88">
-        <v>1</v>
-      </c>
-      <c r="AH88">
-        <v>2</v>
-      </c>
-      <c r="AI88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ88">
-        <v>2</v>
-      </c>
-      <c r="AK88">
-        <v>4</v>
-      </c>
-      <c r="AL88" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM88">
-        <v>0</v>
-      </c>
-      <c r="AN88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:40">
-      <c r="A89" t="s">
-        <v>127</v>
-      </c>
-      <c r="B89" t="s">
-        <v>220</v>
-      </c>
-      <c r="C89" t="s">
-        <v>226</v>
-      </c>
-      <c r="D89">
-        <v>4</v>
-      </c>
-      <c r="E89" t="b">
-        <v>0</v>
-      </c>
-      <c r="F89">
-        <v>1</v>
-      </c>
-      <c r="G89">
-        <v>2</v>
-      </c>
-      <c r="H89" t="b">
-        <v>0</v>
-      </c>
-      <c r="I89">
-        <v>2</v>
-      </c>
-      <c r="J89">
-        <v>4</v>
-      </c>
-      <c r="K89" t="b">
-        <v>0</v>
-      </c>
-      <c r="L89">
-        <v>1</v>
-      </c>
-      <c r="M89">
-        <v>2</v>
-      </c>
-      <c r="N89" t="b">
-        <v>0</v>
-      </c>
-      <c r="O89">
-        <v>1</v>
-      </c>
-      <c r="P89">
-        <v>2</v>
-      </c>
-      <c r="Q89" t="b">
-        <v>0</v>
-      </c>
-      <c r="R89">
-        <v>2</v>
-      </c>
-      <c r="S89">
-        <v>4</v>
-      </c>
-      <c r="T89" t="b">
-        <v>0</v>
-      </c>
-      <c r="U89">
-        <v>1</v>
-      </c>
-      <c r="V89">
-        <v>2</v>
-      </c>
-      <c r="W89" t="b">
-        <v>0</v>
-      </c>
-      <c r="X89">
-        <v>1</v>
-      </c>
-      <c r="Y89">
-        <v>2</v>
-      </c>
-      <c r="Z89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA89">
-        <v>1</v>
-      </c>
-      <c r="AB89">
-        <v>2</v>
-      </c>
-      <c r="AC89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD89">
-        <v>1</v>
-      </c>
-      <c r="AE89">
-        <v>2</v>
-      </c>
-      <c r="AF89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89">
-        <v>1</v>
-      </c>
-      <c r="AH89">
-        <v>2</v>
-      </c>
-      <c r="AI89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ89">
-        <v>2</v>
-      </c>
-      <c r="AK89">
-        <v>4</v>
-      </c>
-      <c r="AL89" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM89">
-        <v>0</v>
-      </c>
-      <c r="AN89">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:40">
-      <c r="A90" t="s">
-        <v>128</v>
-      </c>
-      <c r="B90" t="s">
-        <v>221</v>
-      </c>
-      <c r="C90" t="s">
-        <v>226</v>
-      </c>
-      <c r="D90">
-        <v>1</v>
-      </c>
-      <c r="E90" t="b">
-        <v>1</v>
-      </c>
-      <c r="F90">
-        <v>0</v>
-      </c>
-      <c r="G90">
-        <v>0</v>
-      </c>
-      <c r="H90" t="b">
-        <v>1</v>
-      </c>
-      <c r="I90">
-        <v>0</v>
-      </c>
-      <c r="J90">
-        <v>0</v>
-      </c>
-      <c r="K90" t="b">
-        <v>1</v>
-      </c>
-      <c r="L90">
-        <v>0</v>
-      </c>
-      <c r="M90">
-        <v>0</v>
-      </c>
-      <c r="N90" t="b">
-        <v>1</v>
-      </c>
-      <c r="O90">
-        <v>0</v>
-      </c>
-      <c r="P90">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="b">
-        <v>1</v>
-      </c>
-      <c r="R90">
-        <v>0</v>
-      </c>
-      <c r="S90">
-        <v>0</v>
-      </c>
-      <c r="T90" t="b">
-        <v>1</v>
-      </c>
-      <c r="U90">
-        <v>0</v>
-      </c>
-      <c r="V90">
-        <v>0</v>
-      </c>
-      <c r="W90" t="b">
-        <v>1</v>
-      </c>
-      <c r="X90">
-        <v>0</v>
-      </c>
-      <c r="Y90">
-        <v>0</v>
-      </c>
-      <c r="Z90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA90">
-        <v>0</v>
-      </c>
-      <c r="AB90">
-        <v>0</v>
-      </c>
-      <c r="AC90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD90">
-        <v>0</v>
-      </c>
-      <c r="AE90">
-        <v>0</v>
-      </c>
-      <c r="AF90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG90">
-        <v>0</v>
-      </c>
-      <c r="AH90">
-        <v>0</v>
-      </c>
-      <c r="AI90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ90">
-        <v>0</v>
-      </c>
-      <c r="AK90">
-        <v>0</v>
-      </c>
-      <c r="AL90" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM90">
-        <v>0</v>
-      </c>
-      <c r="AN90">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:40">
-      <c r="A91" t="s">
-        <v>129</v>
-      </c>
-      <c r="B91" t="s">
-        <v>222</v>
-      </c>
-      <c r="C91" t="s">
-        <v>226</v>
-      </c>
-      <c r="D91">
-        <v>4</v>
-      </c>
-      <c r="E91" t="b">
-        <v>0</v>
-      </c>
-      <c r="F91">
-        <v>1</v>
-      </c>
-      <c r="G91">
-        <v>2</v>
-      </c>
-      <c r="H91" t="b">
-        <v>0</v>
-      </c>
-      <c r="I91">
-        <v>2</v>
-      </c>
-      <c r="J91">
-        <v>4</v>
-      </c>
-      <c r="K91" t="b">
-        <v>0</v>
-      </c>
-      <c r="L91">
-        <v>1</v>
-      </c>
-      <c r="M91">
-        <v>2</v>
-      </c>
-      <c r="N91" t="b">
-        <v>0</v>
-      </c>
-      <c r="O91">
-        <v>1</v>
-      </c>
-      <c r="P91">
-        <v>2</v>
-      </c>
-      <c r="Q91" t="b">
-        <v>0</v>
-      </c>
-      <c r="R91">
-        <v>2</v>
-      </c>
-      <c r="S91">
-        <v>4</v>
-      </c>
-      <c r="T91" t="b">
-        <v>0</v>
-      </c>
-      <c r="U91">
-        <v>1</v>
-      </c>
-      <c r="V91">
-        <v>2</v>
-      </c>
-      <c r="W91" t="b">
-        <v>0</v>
-      </c>
-      <c r="X91">
-        <v>1</v>
-      </c>
-      <c r="Y91">
-        <v>2</v>
-      </c>
-      <c r="Z91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA91">
-        <v>1</v>
-      </c>
-      <c r="AB91">
-        <v>2</v>
-      </c>
-      <c r="AC91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD91">
-        <v>1</v>
-      </c>
-      <c r="AE91">
-        <v>2</v>
-      </c>
-      <c r="AF91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG91">
-        <v>1</v>
-      </c>
-      <c r="AH91">
-        <v>2</v>
-      </c>
-      <c r="AI91" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ91">
-        <v>2</v>
-      </c>
-      <c r="AK91">
-        <v>4</v>
-      </c>
-      <c r="AL91" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM91">
-        <v>0</v>
-      </c>
-      <c r="AN91">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:40">
-      <c r="A92" t="s">
-        <v>130</v>
-      </c>
-      <c r="B92" t="s">
-        <v>223</v>
-      </c>
-      <c r="C92" t="s">
-        <v>226</v>
-      </c>
-      <c r="D92">
-        <v>4</v>
-      </c>
-      <c r="E92" t="b">
-        <v>0</v>
-      </c>
-      <c r="F92">
-        <v>1</v>
-      </c>
-      <c r="G92">
-        <v>2</v>
-      </c>
-      <c r="H92" t="b">
-        <v>0</v>
-      </c>
-      <c r="I92">
-        <v>2</v>
-      </c>
-      <c r="J92">
-        <v>4</v>
-      </c>
-      <c r="K92" t="b">
-        <v>0</v>
-      </c>
-      <c r="L92">
-        <v>1</v>
-      </c>
-      <c r="M92">
-        <v>2</v>
-      </c>
-      <c r="N92" t="b">
-        <v>0</v>
-      </c>
-      <c r="O92">
-        <v>1</v>
-      </c>
-      <c r="P92">
-        <v>2</v>
-      </c>
-      <c r="Q92" t="b">
-        <v>0</v>
-      </c>
-      <c r="R92">
-        <v>2</v>
-      </c>
-      <c r="S92">
-        <v>4</v>
-      </c>
-      <c r="T92" t="b">
-        <v>0</v>
-      </c>
-      <c r="U92">
-        <v>1</v>
-      </c>
-      <c r="V92">
-        <v>2</v>
-      </c>
-      <c r="W92" t="b">
-        <v>0</v>
-      </c>
-      <c r="X92">
-        <v>1</v>
-      </c>
-      <c r="Y92">
-        <v>2</v>
-      </c>
-      <c r="Z92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA92">
-        <v>1</v>
-      </c>
-      <c r="AB92">
-        <v>2</v>
-      </c>
-      <c r="AC92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD92">
-        <v>1</v>
-      </c>
-      <c r="AE92">
-        <v>2</v>
-      </c>
-      <c r="AF92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG92">
-        <v>1</v>
-      </c>
-      <c r="AH92">
-        <v>2</v>
-      </c>
-      <c r="AI92" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ92">
-        <v>2</v>
-      </c>
-      <c r="AK92">
-        <v>4</v>
-      </c>
-      <c r="AL92" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM92">
-        <v>0</v>
-      </c>
-      <c r="AN92">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:40">
-      <c r="A93" t="s">
-        <v>131</v>
-      </c>
-      <c r="B93" t="s">
-        <v>224</v>
-      </c>
-      <c r="C93" t="s">
-        <v>226</v>
-      </c>
-      <c r="D93">
-        <v>1</v>
-      </c>
-      <c r="E93" t="b">
-        <v>1</v>
-      </c>
-      <c r="F93">
-        <v>0</v>
-      </c>
-      <c r="G93">
-        <v>0</v>
-      </c>
-      <c r="H93" t="b">
-        <v>1</v>
-      </c>
-      <c r="I93">
-        <v>0</v>
-      </c>
-      <c r="J93">
-        <v>0</v>
-      </c>
-      <c r="K93" t="b">
-        <v>1</v>
-      </c>
-      <c r="L93">
-        <v>0</v>
-      </c>
-      <c r="M93">
-        <v>0</v>
-      </c>
-      <c r="N93" t="b">
-        <v>1</v>
-      </c>
-      <c r="O93">
-        <v>0</v>
-      </c>
-      <c r="P93">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="b">
-        <v>1</v>
-      </c>
-      <c r="R93">
-        <v>0</v>
-      </c>
-      <c r="S93">
-        <v>0</v>
-      </c>
-      <c r="T93" t="b">
-        <v>1</v>
-      </c>
-      <c r="U93">
-        <v>0</v>
-      </c>
-      <c r="V93">
-        <v>0</v>
-      </c>
-      <c r="W93" t="b">
-        <v>1</v>
-      </c>
-      <c r="X93">
-        <v>0</v>
-      </c>
-      <c r="Y93">
-        <v>0</v>
-      </c>
-      <c r="Z93" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA93">
-        <v>0</v>
-      </c>
-      <c r="AB93">
-        <v>0</v>
-      </c>
-      <c r="AC93" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD93">
-        <v>0</v>
-      </c>
-      <c r="AE93">
-        <v>0</v>
-      </c>
-      <c r="AF93" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG93">
-        <v>0</v>
-      </c>
-      <c r="AH93">
-        <v>0</v>
-      </c>
-      <c r="AI93" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ93">
-        <v>0</v>
-      </c>
-      <c r="AK93">
-        <v>0</v>
-      </c>
-      <c r="AL93" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM93">
-        <v>0</v>
-      </c>
-      <c r="AN93">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:40">
-      <c r="A94" t="s">
-        <v>132</v>
-      </c>
-      <c r="B94" t="s">
-        <v>225</v>
-      </c>
-      <c r="C94" t="s">
-        <v>226</v>
-      </c>
-      <c r="D94">
-        <v>1</v>
-      </c>
-      <c r="E94" t="b">
-        <v>1</v>
-      </c>
-      <c r="F94">
-        <v>0</v>
-      </c>
-      <c r="G94">
-        <v>0</v>
-      </c>
-      <c r="H94" t="b">
-        <v>1</v>
-      </c>
-      <c r="I94">
-        <v>0</v>
-      </c>
-      <c r="J94">
-        <v>0</v>
-      </c>
-      <c r="K94" t="b">
-        <v>1</v>
-      </c>
-      <c r="L94">
-        <v>0</v>
-      </c>
-      <c r="M94">
-        <v>0</v>
-      </c>
-      <c r="N94" t="b">
-        <v>1</v>
-      </c>
-      <c r="O94">
-        <v>0</v>
-      </c>
-      <c r="P94">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="b">
-        <v>1</v>
-      </c>
-      <c r="R94">
-        <v>0</v>
-      </c>
-      <c r="S94">
-        <v>0</v>
-      </c>
-      <c r="T94" t="b">
-        <v>1</v>
-      </c>
-      <c r="U94">
-        <v>0</v>
-      </c>
-      <c r="V94">
-        <v>0</v>
-      </c>
-      <c r="W94" t="b">
-        <v>1</v>
-      </c>
-      <c r="X94">
-        <v>0</v>
-      </c>
-      <c r="Y94">
-        <v>0</v>
-      </c>
-      <c r="Z94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA94">
-        <v>0</v>
-      </c>
-      <c r="AB94">
-        <v>0</v>
-      </c>
-      <c r="AC94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AD94">
-        <v>0</v>
-      </c>
-      <c r="AE94">
-        <v>0</v>
-      </c>
-      <c r="AF94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG94">
-        <v>0</v>
-      </c>
-      <c r="AH94">
-        <v>0</v>
-      </c>
-      <c r="AI94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AJ94">
-        <v>0</v>
-      </c>
-      <c r="AK94">
-        <v>0</v>
-      </c>
-      <c r="AL94" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM94">
-        <v>0</v>
-      </c>
-      <c r="AN94">
         <v>0</v>
       </c>
     </row>

--- a/Data/Rules/Fluff & Tuff Rules Matrix.xlsx
+++ b/Data/Rules/Fluff & Tuff Rules Matrix.xlsx
@@ -1036,10 +1036,10 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N2" t="b">
         <v>0</v>
@@ -1054,28 +1054,28 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W2" t="b">
         <v>0</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
@@ -1090,19 +1090,19 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF2" t="b">
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI2" t="b">
         <v>0</v>
@@ -1111,7 +1111,7 @@
         <v>2</v>
       </c>
       <c r="AK2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL2" t="b">
         <v>1</v>
@@ -1158,10 +1158,10 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -1185,19 +1185,19 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
@@ -1212,19 +1212,19 @@
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF3" t="b">
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI3" t="b">
         <v>0</v>
@@ -1233,7 +1233,7 @@
         <v>2</v>
       </c>
       <c r="AK3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL3" t="b">
         <v>1</v>
@@ -1280,10 +1280,10 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" t="b">
         <v>0</v>
@@ -1298,28 +1298,28 @@
         <v>0</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
@@ -1334,19 +1334,19 @@
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>2</v>
       </c>
       <c r="AK4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL4" t="b">
         <v>1</v>
@@ -1402,10 +1402,10 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1420,28 +1420,28 @@
         <v>0</v>
       </c>
       <c r="R5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
@@ -1465,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -1477,7 +1477,7 @@
         <v>2</v>
       </c>
       <c r="AK5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL5" t="b">
         <v>1</v>
@@ -1524,10 +1524,10 @@
         <v>0</v>
       </c>
       <c r="L6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -1545,25 +1545,25 @@
         <v>2</v>
       </c>
       <c r="S6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -1599,7 +1599,7 @@
         <v>2</v>
       </c>
       <c r="AK6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL6" t="b">
         <v>1</v>
@@ -1646,10 +1646,10 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1673,19 +1673,19 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W7" t="b">
         <v>0</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
@@ -1700,19 +1700,19 @@
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF7" t="b">
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>2</v>
       </c>
       <c r="AK7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL7" t="b">
         <v>1</v>
@@ -1768,10 +1768,10 @@
         <v>0</v>
       </c>
       <c r="L8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -1795,19 +1795,19 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
@@ -1822,19 +1822,19 @@
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF8" t="b">
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -1843,7 +1843,7 @@
         <v>2</v>
       </c>
       <c r="AK8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL8" t="b">
         <v>1</v>
@@ -1890,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -1917,19 +1917,19 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W9" t="b">
         <v>0</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
@@ -1944,19 +1944,19 @@
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF9" t="b">
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -1965,7 +1965,7 @@
         <v>2</v>
       </c>
       <c r="AK9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL9" t="b">
         <v>1</v>
@@ -2012,10 +2012,10 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -2039,19 +2039,19 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W10" t="b">
         <v>0</v>
       </c>
       <c r="X10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
@@ -2066,19 +2066,19 @@
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF10" t="b">
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
@@ -2087,7 +2087,7 @@
         <v>2</v>
       </c>
       <c r="AK10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL10" t="b">
         <v>1</v>
@@ -2134,10 +2134,10 @@
         <v>0</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N11" t="b">
         <v>0</v>
@@ -2152,28 +2152,28 @@
         <v>0</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T11" t="b">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W11" t="b">
         <v>0</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
@@ -2188,19 +2188,19 @@
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF11" t="b">
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI11" t="b">
         <v>0</v>
@@ -2209,7 +2209,7 @@
         <v>2</v>
       </c>
       <c r="AK11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL11" t="b">
         <v>1</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12" t="b">
         <v>0</v>
@@ -2274,28 +2274,28 @@
         <v>0</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T12" t="b">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W12" t="b">
         <v>0</v>
       </c>
       <c r="X12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
@@ -2310,19 +2310,19 @@
         <v>0</v>
       </c>
       <c r="AD12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="b">
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="b">
         <v>0</v>
@@ -2331,7 +2331,7 @@
         <v>2</v>
       </c>
       <c r="AK12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL12" t="b">
         <v>1</v>
@@ -2378,10 +2378,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -2405,19 +2405,19 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W13" t="b">
         <v>0</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
@@ -2432,19 +2432,19 @@
         <v>0</v>
       </c>
       <c r="AD13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF13" t="b">
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="b">
         <v>0</v>
@@ -2453,7 +2453,7 @@
         <v>2</v>
       </c>
       <c r="AK13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="b">
         <v>1</v>
@@ -2500,10 +2500,10 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14" t="b">
         <v>0</v>
@@ -2518,28 +2518,28 @@
         <v>0</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T14" t="b">
         <v>0</v>
       </c>
       <c r="U14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W14" t="b">
         <v>0</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
@@ -2554,19 +2554,19 @@
         <v>0</v>
       </c>
       <c r="AD14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="b">
         <v>0</v>
       </c>
       <c r="AG14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI14" t="b">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>2</v>
       </c>
       <c r="AK14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="b">
         <v>1</v>
@@ -2622,10 +2622,10 @@
         <v>0</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -2640,28 +2640,28 @@
         <v>0</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T15" t="b">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W15" t="b">
         <v>0</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
@@ -2676,19 +2676,19 @@
         <v>0</v>
       </c>
       <c r="AD15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF15" t="b">
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="b">
         <v>0</v>
@@ -2697,7 +2697,7 @@
         <v>2</v>
       </c>
       <c r="AK15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL15" t="b">
         <v>1</v>
@@ -2744,10 +2744,10 @@
         <v>0</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N16" t="b">
         <v>0</v>
@@ -2771,19 +2771,19 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W16" t="b">
         <v>0</v>
       </c>
       <c r="X16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="b">
         <v>0</v>
@@ -2798,19 +2798,19 @@
         <v>0</v>
       </c>
       <c r="AD16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF16" t="b">
         <v>0</v>
       </c>
       <c r="AG16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
@@ -2819,7 +2819,7 @@
         <v>2</v>
       </c>
       <c r="AK16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL16" t="b">
         <v>1</v>
@@ -2866,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -2884,28 +2884,28 @@
         <v>0</v>
       </c>
       <c r="R17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T17" t="b">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W17" t="b">
         <v>0</v>
       </c>
       <c r="X17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z17" t="b">
         <v>0</v>
@@ -2920,19 +2920,19 @@
         <v>0</v>
       </c>
       <c r="AD17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="b">
         <v>0</v>
       </c>
       <c r="AG17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="b">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>2</v>
       </c>
       <c r="AK17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL17" t="b">
         <v>1</v>
@@ -2988,10 +2988,10 @@
         <v>0</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N18" t="b">
         <v>0</v>
@@ -3006,28 +3006,28 @@
         <v>0</v>
       </c>
       <c r="R18">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S18">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="b">
         <v>0</v>
       </c>
       <c r="U18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W18" t="b">
         <v>0</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z18" t="b">
         <v>0</v>
@@ -3042,19 +3042,19 @@
         <v>0</v>
       </c>
       <c r="AD18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE18">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF18" t="b">
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI18" t="b">
         <v>0</v>
@@ -3063,7 +3063,7 @@
         <v>2</v>
       </c>
       <c r="AK18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL18" t="b">
         <v>1</v>
@@ -3110,10 +3110,10 @@
         <v>0</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -3128,28 +3128,28 @@
         <v>0</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T19" t="b">
         <v>0</v>
       </c>
       <c r="U19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W19" t="b">
         <v>0</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="b">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="AG19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI19" t="b">
         <v>0</v>
@@ -3185,7 +3185,7 @@
         <v>2</v>
       </c>
       <c r="AK19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL19" t="b">
         <v>1</v>
@@ -3232,10 +3232,10 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -3259,19 +3259,19 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W20" t="b">
         <v>0</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z20" t="b">
         <v>0</v>
@@ -3286,19 +3286,19 @@
         <v>0</v>
       </c>
       <c r="AD20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF20" t="b">
         <v>0</v>
       </c>
       <c r="AG20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI20" t="b">
         <v>0</v>
@@ -3307,7 +3307,7 @@
         <v>2</v>
       </c>
       <c r="AK20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL20" t="b">
         <v>1</v>
@@ -3354,10 +3354,10 @@
         <v>0</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
@@ -3381,19 +3381,19 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W21" t="b">
         <v>0</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z21" t="b">
         <v>0</v>
@@ -3408,19 +3408,19 @@
         <v>0</v>
       </c>
       <c r="AD21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF21" t="b">
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3429,7 +3429,7 @@
         <v>2</v>
       </c>
       <c r="AK21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL21" t="b">
         <v>1</v>
@@ -3476,10 +3476,10 @@
         <v>0</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N22" t="b">
         <v>0</v>
@@ -3494,28 +3494,28 @@
         <v>0</v>
       </c>
       <c r="R22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S22">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T22" t="b">
         <v>0</v>
       </c>
       <c r="U22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W22" t="b">
         <v>0</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z22" t="b">
         <v>0</v>
@@ -3530,19 +3530,19 @@
         <v>0</v>
       </c>
       <c r="AD22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="b">
         <v>0</v>
       </c>
       <c r="AG22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI22" t="b">
         <v>0</v>
@@ -3551,7 +3551,7 @@
         <v>2</v>
       </c>
       <c r="AK22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL22" t="b">
         <v>1</v>
@@ -3598,10 +3598,10 @@
         <v>0</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N23" t="b">
         <v>0</v>
@@ -3616,28 +3616,28 @@
         <v>0</v>
       </c>
       <c r="R23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S23">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T23" t="b">
         <v>0</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W23" t="b">
         <v>0</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z23" t="b">
         <v>0</v>
@@ -3652,19 +3652,19 @@
         <v>0</v>
       </c>
       <c r="AD23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="b">
         <v>0</v>
       </c>
       <c r="AG23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="b">
         <v>0</v>
@@ -3673,7 +3673,7 @@
         <v>2</v>
       </c>
       <c r="AK23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL23" t="b">
         <v>1</v>
@@ -3720,10 +3720,10 @@
         <v>0</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -3738,28 +3738,28 @@
         <v>0</v>
       </c>
       <c r="R24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S24">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T24" t="b">
         <v>0</v>
       </c>
       <c r="U24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W24" t="b">
         <v>0</v>
       </c>
       <c r="X24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z24" t="b">
         <v>0</v>
@@ -3774,19 +3774,19 @@
         <v>0</v>
       </c>
       <c r="AD24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF24" t="b">
         <v>0</v>
       </c>
       <c r="AG24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI24" t="b">
         <v>0</v>
@@ -3795,7 +3795,7 @@
         <v>2</v>
       </c>
       <c r="AK24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL24" t="b">
         <v>1</v>
@@ -3842,10 +3842,10 @@
         <v>0</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -3869,19 +3869,19 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W25" t="b">
         <v>0</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z25" t="b">
         <v>0</v>
@@ -3896,19 +3896,19 @@
         <v>0</v>
       </c>
       <c r="AD25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF25" t="b">
         <v>0</v>
       </c>
       <c r="AG25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI25" t="b">
         <v>0</v>
@@ -3917,7 +3917,7 @@
         <v>2</v>
       </c>
       <c r="AK25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL25" t="b">
         <v>1</v>
@@ -3964,10 +3964,10 @@
         <v>0</v>
       </c>
       <c r="L26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -3991,19 +3991,19 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W26" t="b">
         <v>0</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z26" t="b">
         <v>0</v>
@@ -4018,19 +4018,19 @@
         <v>0</v>
       </c>
       <c r="AD26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF26" t="b">
         <v>0</v>
       </c>
       <c r="AG26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
@@ -4039,7 +4039,7 @@
         <v>2</v>
       </c>
       <c r="AK26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL26" t="b">
         <v>1</v>
@@ -4086,10 +4086,10 @@
         <v>0</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -4113,19 +4113,19 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W27" t="b">
         <v>0</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z27" t="b">
         <v>0</v>
@@ -4140,19 +4140,19 @@
         <v>0</v>
       </c>
       <c r="AD27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF27" t="b">
         <v>0</v>
       </c>
       <c r="AG27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" t="b">
         <v>0</v>
@@ -4161,7 +4161,7 @@
         <v>2</v>
       </c>
       <c r="AK27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL27" t="b">
         <v>1</v>
@@ -4208,10 +4208,10 @@
         <v>0</v>
       </c>
       <c r="L28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -4235,19 +4235,19 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W28" t="b">
         <v>0</v>
       </c>
       <c r="X28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z28" t="b">
         <v>0</v>
@@ -4262,19 +4262,19 @@
         <v>0</v>
       </c>
       <c r="AD28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF28" t="b">
         <v>0</v>
       </c>
       <c r="AG28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4283,7 +4283,7 @@
         <v>2</v>
       </c>
       <c r="AK28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL28" t="b">
         <v>1</v>
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N29" t="b">
         <v>0</v>
@@ -4348,28 +4348,28 @@
         <v>0</v>
       </c>
       <c r="R29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S29">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T29" t="b">
         <v>0</v>
       </c>
       <c r="U29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W29" t="b">
         <v>0</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z29" t="b">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         <v>0</v>
       </c>
       <c r="AD29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF29" t="b">
         <v>0</v>
       </c>
       <c r="AG29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="b">
         <v>0</v>
@@ -4405,7 +4405,7 @@
         <v>2</v>
       </c>
       <c r="AK29">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL29" t="b">
         <v>1</v>
@@ -4452,10 +4452,10 @@
         <v>0</v>
       </c>
       <c r="L30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -4479,19 +4479,19 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W30" t="b">
         <v>0</v>
       </c>
       <c r="X30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z30" t="b">
         <v>0</v>
@@ -4506,19 +4506,19 @@
         <v>0</v>
       </c>
       <c r="AD30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF30" t="b">
         <v>0</v>
       </c>
       <c r="AG30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI30" t="b">
         <v>0</v>
@@ -4527,7 +4527,7 @@
         <v>2</v>
       </c>
       <c r="AK30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL30" t="b">
         <v>1</v>
@@ -4574,10 +4574,10 @@
         <v>0</v>
       </c>
       <c r="L31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -4592,28 +4592,28 @@
         <v>0</v>
       </c>
       <c r="R31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S31">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T31" t="b">
         <v>0</v>
       </c>
       <c r="U31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W31" t="b">
         <v>0</v>
       </c>
       <c r="X31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="b">
         <v>0</v>
@@ -4628,19 +4628,19 @@
         <v>0</v>
       </c>
       <c r="AD31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF31" t="b">
         <v>0</v>
       </c>
       <c r="AG31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI31" t="b">
         <v>0</v>
@@ -4649,7 +4649,7 @@
         <v>2</v>
       </c>
       <c r="AK31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL31" t="b">
         <v>1</v>
@@ -4675,103 +4675,103 @@
         <v>1</v>
       </c>
       <c r="E32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T32" t="b">
         <v>1</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI32" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL32" t="b">
         <v>1</v>
@@ -4818,10 +4818,10 @@
         <v>0</v>
       </c>
       <c r="L33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -4845,19 +4845,19 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W33" t="b">
         <v>0</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z33" t="b">
         <v>0</v>
@@ -4872,19 +4872,19 @@
         <v>0</v>
       </c>
       <c r="AD33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF33" t="b">
         <v>0</v>
       </c>
       <c r="AG33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>2</v>
       </c>
       <c r="AK33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL33" t="b">
         <v>1</v>
@@ -4940,10 +4940,10 @@
         <v>0</v>
       </c>
       <c r="L34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
@@ -4967,19 +4967,19 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W34" t="b">
         <v>0</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z34" t="b">
         <v>0</v>
@@ -4994,19 +4994,19 @@
         <v>0</v>
       </c>
       <c r="AD34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF34" t="b">
         <v>0</v>
       </c>
       <c r="AG34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI34" t="b">
         <v>0</v>
@@ -5015,7 +5015,7 @@
         <v>2</v>
       </c>
       <c r="AK34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL34" t="b">
         <v>1</v>
@@ -5062,10 +5062,10 @@
         <v>0</v>
       </c>
       <c r="L35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -5080,28 +5080,28 @@
         <v>0</v>
       </c>
       <c r="R35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S35">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T35" t="b">
         <v>0</v>
       </c>
       <c r="U35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W35" t="b">
         <v>0</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z35" t="b">
         <v>0</v>
@@ -5116,19 +5116,19 @@
         <v>0</v>
       </c>
       <c r="AD35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF35" t="b">
         <v>0</v>
       </c>
       <c r="AG35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
@@ -5137,7 +5137,7 @@
         <v>2</v>
       </c>
       <c r="AK35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL35" t="b">
         <v>1</v>
@@ -5184,10 +5184,10 @@
         <v>0</v>
       </c>
       <c r="L36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -5211,19 +5211,19 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W36" t="b">
         <v>0</v>
       </c>
       <c r="X36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z36" t="b">
         <v>0</v>
@@ -5238,19 +5238,19 @@
         <v>0</v>
       </c>
       <c r="AD36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF36" t="b">
         <v>0</v>
       </c>
       <c r="AG36">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
@@ -5259,7 +5259,7 @@
         <v>2</v>
       </c>
       <c r="AK36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL36" t="b">
         <v>1</v>
@@ -5306,10 +5306,10 @@
         <v>0</v>
       </c>
       <c r="L37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -5333,19 +5333,19 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W37" t="b">
         <v>0</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z37" t="b">
         <v>0</v>
@@ -5360,19 +5360,19 @@
         <v>0</v>
       </c>
       <c r="AD37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF37" t="b">
         <v>0</v>
       </c>
       <c r="AG37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
@@ -5381,7 +5381,7 @@
         <v>2</v>
       </c>
       <c r="AK37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL37" t="b">
         <v>1</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="L38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
@@ -5446,28 +5446,28 @@
         <v>0</v>
       </c>
       <c r="R38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S38">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T38" t="b">
         <v>0</v>
       </c>
       <c r="U38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W38" t="b">
         <v>0</v>
       </c>
       <c r="X38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z38" t="b">
         <v>0</v>
@@ -5482,19 +5482,19 @@
         <v>0</v>
       </c>
       <c r="AD38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF38" t="b">
         <v>0</v>
       </c>
       <c r="AG38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5503,7 +5503,7 @@
         <v>2</v>
       </c>
       <c r="AK38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL38" t="b">
         <v>1</v>
@@ -5550,10 +5550,10 @@
         <v>0</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -5568,28 +5568,28 @@
         <v>0</v>
       </c>
       <c r="R39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S39">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T39" t="b">
         <v>0</v>
       </c>
       <c r="U39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W39" t="b">
         <v>0</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z39" t="b">
         <v>0</v>
@@ -5604,19 +5604,19 @@
         <v>0</v>
       </c>
       <c r="AD39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF39" t="b">
         <v>0</v>
       </c>
       <c r="AG39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH39">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
@@ -5625,7 +5625,7 @@
         <v>2</v>
       </c>
       <c r="AK39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL39" t="b">
         <v>1</v>
@@ -5672,10 +5672,10 @@
         <v>0</v>
       </c>
       <c r="L40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -5699,19 +5699,19 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W40" t="b">
         <v>0</v>
       </c>
       <c r="X40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z40" t="b">
         <v>0</v>
@@ -5726,19 +5726,19 @@
         <v>0</v>
       </c>
       <c r="AD40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF40" t="b">
         <v>0</v>
       </c>
       <c r="AG40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
@@ -5747,7 +5747,7 @@
         <v>2</v>
       </c>
       <c r="AK40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL40" t="b">
         <v>1</v>
@@ -5794,10 +5794,10 @@
         <v>0</v>
       </c>
       <c r="L41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -5821,19 +5821,19 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W41" t="b">
         <v>0</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z41" t="b">
         <v>0</v>
@@ -5848,19 +5848,19 @@
         <v>0</v>
       </c>
       <c r="AD41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF41" t="b">
         <v>0</v>
       </c>
       <c r="AG41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -5869,7 +5869,7 @@
         <v>2</v>
       </c>
       <c r="AK41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL41" t="b">
         <v>1</v>
@@ -5916,10 +5916,10 @@
         <v>0</v>
       </c>
       <c r="L42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
@@ -5934,28 +5934,28 @@
         <v>0</v>
       </c>
       <c r="R42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T42" t="b">
         <v>0</v>
       </c>
       <c r="U42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W42" t="b">
         <v>0</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z42" t="b">
         <v>0</v>
@@ -5970,19 +5970,19 @@
         <v>0</v>
       </c>
       <c r="AD42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF42" t="b">
         <v>0</v>
       </c>
       <c r="AG42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -5991,7 +5991,7 @@
         <v>2</v>
       </c>
       <c r="AK42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL42" t="b">
         <v>1</v>
@@ -6038,10 +6038,10 @@
         <v>0</v>
       </c>
       <c r="L43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -6056,28 +6056,28 @@
         <v>0</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S43">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T43" t="b">
         <v>0</v>
       </c>
       <c r="U43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W43" t="b">
         <v>0</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z43" t="b">
         <v>0</v>
@@ -6092,19 +6092,19 @@
         <v>0</v>
       </c>
       <c r="AD43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF43" t="b">
         <v>0</v>
       </c>
       <c r="AG43">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>2</v>
       </c>
       <c r="AK43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL43" t="b">
         <v>1</v>
@@ -6160,10 +6160,10 @@
         <v>0</v>
       </c>
       <c r="L44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -6178,28 +6178,28 @@
         <v>0</v>
       </c>
       <c r="R44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S44">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T44" t="b">
         <v>0</v>
       </c>
       <c r="U44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W44" t="b">
         <v>0</v>
       </c>
       <c r="X44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z44" t="b">
         <v>0</v>
@@ -6214,19 +6214,19 @@
         <v>0</v>
       </c>
       <c r="AD44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF44" t="b">
         <v>0</v>
       </c>
       <c r="AG44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6235,7 +6235,7 @@
         <v>2</v>
       </c>
       <c r="AK44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL44" t="b">
         <v>1</v>
@@ -6282,10 +6282,10 @@
         <v>0</v>
       </c>
       <c r="L45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -6300,28 +6300,28 @@
         <v>0</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S45">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T45" t="b">
         <v>0</v>
       </c>
       <c r="U45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W45" t="b">
         <v>0</v>
       </c>
       <c r="X45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z45" t="b">
         <v>0</v>
@@ -6336,19 +6336,19 @@
         <v>0</v>
       </c>
       <c r="AD45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF45" t="b">
         <v>0</v>
       </c>
       <c r="AG45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6357,7 +6357,7 @@
         <v>2</v>
       </c>
       <c r="AK45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL45" t="b">
         <v>1</v>
@@ -6404,10 +6404,10 @@
         <v>0</v>
       </c>
       <c r="L46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -6422,28 +6422,28 @@
         <v>0</v>
       </c>
       <c r="R46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S46">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T46" t="b">
         <v>0</v>
       </c>
       <c r="U46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W46" t="b">
         <v>0</v>
       </c>
       <c r="X46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z46" t="b">
         <v>0</v>
@@ -6458,19 +6458,19 @@
         <v>0</v>
       </c>
       <c r="AD46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF46" t="b">
         <v>0</v>
       </c>
       <c r="AG46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6479,7 +6479,7 @@
         <v>2</v>
       </c>
       <c r="AK46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL46" t="b">
         <v>1</v>
@@ -6526,10 +6526,10 @@
         <v>0</v>
       </c>
       <c r="L47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N47" t="b">
         <v>0</v>
@@ -6544,28 +6544,28 @@
         <v>0</v>
       </c>
       <c r="R47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S47">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T47" t="b">
         <v>0</v>
       </c>
       <c r="U47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W47" t="b">
         <v>0</v>
       </c>
       <c r="X47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z47" t="b">
         <v>0</v>
@@ -6580,19 +6580,19 @@
         <v>0</v>
       </c>
       <c r="AD47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF47" t="b">
         <v>0</v>
       </c>
       <c r="AG47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -6601,7 +6601,7 @@
         <v>2</v>
       </c>
       <c r="AK47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL47" t="b">
         <v>1</v>
@@ -6648,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="L48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -6675,19 +6675,19 @@
         <v>0</v>
       </c>
       <c r="U48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W48" t="b">
         <v>0</v>
       </c>
       <c r="X48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z48" t="b">
         <v>0</v>
@@ -6702,19 +6702,19 @@
         <v>0</v>
       </c>
       <c r="AD48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF48" t="b">
         <v>0</v>
       </c>
       <c r="AG48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH48">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -6723,7 +6723,7 @@
         <v>2</v>
       </c>
       <c r="AK48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL48" t="b">
         <v>1</v>
@@ -6770,10 +6770,10 @@
         <v>0</v>
       </c>
       <c r="L49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -6797,19 +6797,19 @@
         <v>0</v>
       </c>
       <c r="U49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W49" t="b">
         <v>0</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z49" t="b">
         <v>0</v>
@@ -6824,19 +6824,19 @@
         <v>0</v>
       </c>
       <c r="AD49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF49" t="b">
         <v>0</v>
       </c>
       <c r="AG49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -6845,7 +6845,7 @@
         <v>2</v>
       </c>
       <c r="AK49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL49" t="b">
         <v>1</v>
@@ -6892,10 +6892,10 @@
         <v>0</v>
       </c>
       <c r="L50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N50" t="b">
         <v>0</v>
@@ -6919,19 +6919,19 @@
         <v>0</v>
       </c>
       <c r="U50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W50" t="b">
         <v>0</v>
       </c>
       <c r="X50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z50" t="b">
         <v>0</v>
@@ -6946,19 +6946,19 @@
         <v>0</v>
       </c>
       <c r="AD50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF50" t="b">
         <v>0</v>
       </c>
       <c r="AG50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>2</v>
       </c>
       <c r="AK50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL50" t="b">
         <v>1</v>
@@ -7014,10 +7014,10 @@
         <v>0</v>
       </c>
       <c r="L51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N51" t="b">
         <v>0</v>
@@ -7041,19 +7041,19 @@
         <v>0</v>
       </c>
       <c r="U51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W51" t="b">
         <v>0</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z51" t="b">
         <v>0</v>
@@ -7068,19 +7068,19 @@
         <v>0</v>
       </c>
       <c r="AD51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF51" t="b">
         <v>0</v>
       </c>
       <c r="AG51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7089,7 +7089,7 @@
         <v>2</v>
       </c>
       <c r="AK51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL51" t="b">
         <v>1</v>
@@ -7136,10 +7136,10 @@
         <v>0</v>
       </c>
       <c r="L52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N52" t="b">
         <v>0</v>
@@ -7154,28 +7154,28 @@
         <v>0</v>
       </c>
       <c r="R52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T52" t="b">
         <v>0</v>
       </c>
       <c r="U52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W52" t="b">
         <v>0</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z52" t="b">
         <v>0</v>
@@ -7190,19 +7190,19 @@
         <v>0</v>
       </c>
       <c r="AD52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF52" t="b">
         <v>0</v>
       </c>
       <c r="AG52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI52" t="b">
         <v>0</v>
@@ -7211,7 +7211,7 @@
         <v>2</v>
       </c>
       <c r="AK52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL52" t="b">
         <v>1</v>
@@ -7258,10 +7258,10 @@
         <v>0</v>
       </c>
       <c r="L53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N53" t="b">
         <v>0</v>
@@ -7285,19 +7285,19 @@
         <v>0</v>
       </c>
       <c r="U53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W53" t="b">
         <v>0</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z53" t="b">
         <v>0</v>
@@ -7312,19 +7312,19 @@
         <v>0</v>
       </c>
       <c r="AD53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF53" t="b">
         <v>0</v>
       </c>
       <c r="AG53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI53" t="b">
         <v>0</v>
@@ -7333,7 +7333,7 @@
         <v>2</v>
       </c>
       <c r="AK53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL53" t="b">
         <v>1</v>
@@ -7380,10 +7380,10 @@
         <v>0</v>
       </c>
       <c r="L54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
@@ -7398,28 +7398,28 @@
         <v>0</v>
       </c>
       <c r="R54">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S54">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T54" t="b">
         <v>0</v>
       </c>
       <c r="U54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W54" t="b">
         <v>0</v>
       </c>
       <c r="X54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z54" t="b">
         <v>0</v>
@@ -7434,19 +7434,19 @@
         <v>0</v>
       </c>
       <c r="AD54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF54" t="b">
         <v>0</v>
       </c>
       <c r="AG54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI54" t="b">
         <v>0</v>
@@ -7455,7 +7455,7 @@
         <v>2</v>
       </c>
       <c r="AK54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL54" t="b">
         <v>1</v>
@@ -7502,10 +7502,10 @@
         <v>0</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
@@ -7520,28 +7520,28 @@
         <v>0</v>
       </c>
       <c r="R55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S55">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T55" t="b">
         <v>0</v>
       </c>
       <c r="U55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W55" t="b">
         <v>0</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z55" t="b">
         <v>0</v>
@@ -7565,10 +7565,10 @@
         <v>0</v>
       </c>
       <c r="AG55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI55" t="b">
         <v>0</v>
@@ -7577,7 +7577,7 @@
         <v>2</v>
       </c>
       <c r="AK55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL55" t="b">
         <v>1</v>
@@ -7624,10 +7624,10 @@
         <v>0</v>
       </c>
       <c r="L56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N56" t="b">
         <v>0</v>
@@ -7651,19 +7651,19 @@
         <v>0</v>
       </c>
       <c r="U56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W56" t="b">
         <v>0</v>
       </c>
       <c r="X56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z56" t="b">
         <v>0</v>
@@ -7678,19 +7678,19 @@
         <v>0</v>
       </c>
       <c r="AD56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF56" t="b">
         <v>0</v>
       </c>
       <c r="AG56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI56" t="b">
         <v>0</v>
@@ -7699,7 +7699,7 @@
         <v>2</v>
       </c>
       <c r="AK56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL56" t="b">
         <v>1</v>
@@ -7746,10 +7746,10 @@
         <v>0</v>
       </c>
       <c r="L57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N57" t="b">
         <v>0</v>
@@ -7773,19 +7773,19 @@
         <v>0</v>
       </c>
       <c r="U57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W57" t="b">
         <v>0</v>
       </c>
       <c r="X57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z57" t="b">
         <v>0</v>
@@ -7800,19 +7800,19 @@
         <v>0</v>
       </c>
       <c r="AD57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF57" t="b">
         <v>0</v>
       </c>
       <c r="AG57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI57" t="b">
         <v>0</v>
@@ -7821,7 +7821,7 @@
         <v>2</v>
       </c>
       <c r="AK57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL57" t="b">
         <v>1</v>
@@ -7868,10 +7868,10 @@
         <v>0</v>
       </c>
       <c r="L58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -7886,28 +7886,28 @@
         <v>0</v>
       </c>
       <c r="R58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S58">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T58" t="b">
         <v>0</v>
       </c>
       <c r="U58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W58" t="b">
         <v>0</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z58" t="b">
         <v>0</v>
@@ -7931,10 +7931,10 @@
         <v>0</v>
       </c>
       <c r="AG58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI58" t="b">
         <v>0</v>
@@ -7943,7 +7943,7 @@
         <v>2</v>
       </c>
       <c r="AK58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL58" t="b">
         <v>1</v>
@@ -7990,10 +7990,10 @@
         <v>0</v>
       </c>
       <c r="L59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -8008,28 +8008,28 @@
         <v>0</v>
       </c>
       <c r="R59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S59">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T59" t="b">
         <v>0</v>
       </c>
       <c r="U59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W59" t="b">
         <v>0</v>
       </c>
       <c r="X59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z59" t="b">
         <v>0</v>
@@ -8044,19 +8044,19 @@
         <v>0</v>
       </c>
       <c r="AD59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE59">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AF59" t="b">
         <v>0</v>
       </c>
       <c r="AG59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI59" t="b">
         <v>0</v>
@@ -8065,7 +8065,7 @@
         <v>2</v>
       </c>
       <c r="AK59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL59" t="b">
         <v>1</v>
@@ -8112,10 +8112,10 @@
         <v>0</v>
       </c>
       <c r="L60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
@@ -8139,19 +8139,19 @@
         <v>0</v>
       </c>
       <c r="U60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W60" t="b">
         <v>0</v>
       </c>
       <c r="X60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z60" t="b">
         <v>0</v>
@@ -8166,19 +8166,19 @@
         <v>0</v>
       </c>
       <c r="AD60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF60" t="b">
         <v>0</v>
       </c>
       <c r="AG60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI60" t="b">
         <v>0</v>
@@ -8187,7 +8187,7 @@
         <v>2</v>
       </c>
       <c r="AK60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL60" t="b">
         <v>1</v>
@@ -8234,10 +8234,10 @@
         <v>0</v>
       </c>
       <c r="L61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
@@ -8261,19 +8261,19 @@
         <v>0</v>
       </c>
       <c r="U61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W61" t="b">
         <v>0</v>
       </c>
       <c r="X61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z61" t="b">
         <v>0</v>
@@ -8288,19 +8288,19 @@
         <v>0</v>
       </c>
       <c r="AD61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF61" t="b">
         <v>0</v>
       </c>
       <c r="AG61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI61" t="b">
         <v>0</v>
@@ -8309,7 +8309,7 @@
         <v>2</v>
       </c>
       <c r="AK61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL61" t="b">
         <v>1</v>
@@ -8356,10 +8356,10 @@
         <v>0</v>
       </c>
       <c r="L62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N62" t="b">
         <v>0</v>
@@ -8374,28 +8374,28 @@
         <v>0</v>
       </c>
       <c r="R62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S62">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T62" t="b">
         <v>0</v>
       </c>
       <c r="U62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W62" t="b">
         <v>0</v>
       </c>
       <c r="X62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z62" t="b">
         <v>0</v>
@@ -8410,19 +8410,19 @@
         <v>0</v>
       </c>
       <c r="AD62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF62" t="b">
         <v>0</v>
       </c>
       <c r="AG62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI62" t="b">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>2</v>
       </c>
       <c r="AK62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL62" t="b">
         <v>1</v>
@@ -8478,10 +8478,10 @@
         <v>0</v>
       </c>
       <c r="L63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -8505,19 +8505,19 @@
         <v>0</v>
       </c>
       <c r="U63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W63" t="b">
         <v>0</v>
       </c>
       <c r="X63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z63" t="b">
         <v>0</v>
@@ -8532,19 +8532,19 @@
         <v>0</v>
       </c>
       <c r="AD63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF63" t="b">
         <v>0</v>
       </c>
       <c r="AG63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI63" t="b">
         <v>0</v>
@@ -8553,7 +8553,7 @@
         <v>2</v>
       </c>
       <c r="AK63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL63" t="b">
         <v>1</v>
@@ -8600,10 +8600,10 @@
         <v>0</v>
       </c>
       <c r="L64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -8621,25 +8621,25 @@
         <v>2</v>
       </c>
       <c r="S64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T64" t="b">
         <v>0</v>
       </c>
       <c r="U64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W64" t="b">
         <v>0</v>
       </c>
       <c r="X64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z64" t="b">
         <v>0</v>
@@ -8654,19 +8654,19 @@
         <v>0</v>
       </c>
       <c r="AD64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF64" t="b">
         <v>0</v>
       </c>
       <c r="AG64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI64" t="b">
         <v>0</v>
@@ -8675,7 +8675,7 @@
         <v>2</v>
       </c>
       <c r="AK64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL64" t="b">
         <v>1</v>
@@ -8722,10 +8722,10 @@
         <v>0</v>
       </c>
       <c r="L65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -8749,19 +8749,19 @@
         <v>0</v>
       </c>
       <c r="U65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W65" t="b">
         <v>0</v>
       </c>
       <c r="X65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z65" t="b">
         <v>0</v>
@@ -8776,19 +8776,19 @@
         <v>0</v>
       </c>
       <c r="AD65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF65" t="b">
         <v>0</v>
       </c>
       <c r="AG65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI65" t="b">
         <v>0</v>
@@ -8797,7 +8797,7 @@
         <v>2</v>
       </c>
       <c r="AK65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL65" t="b">
         <v>1</v>
@@ -8844,10 +8844,10 @@
         <v>0</v>
       </c>
       <c r="L66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -8871,19 +8871,19 @@
         <v>0</v>
       </c>
       <c r="U66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W66" t="b">
         <v>0</v>
       </c>
       <c r="X66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z66" t="b">
         <v>0</v>
@@ -8898,19 +8898,19 @@
         <v>0</v>
       </c>
       <c r="AD66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF66" t="b">
         <v>0</v>
       </c>
       <c r="AG66">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI66" t="b">
         <v>0</v>
@@ -8919,7 +8919,7 @@
         <v>2</v>
       </c>
       <c r="AK66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL66" t="b">
         <v>1</v>
@@ -8945,103 +8945,103 @@
         <v>1</v>
       </c>
       <c r="E67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL67" t="b">
         <v>1</v>
@@ -9064,106 +9064,106 @@
         <v>176</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J68">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI68" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL68" t="b">
         <v>1</v>
@@ -9186,7 +9186,7 @@
         <v>176</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E69" t="b">
         <v>1</v>

--- a/Data/Rules/Fluff & Tuff Rules Matrix.xlsx
+++ b/Data/Rules/Fluff & Tuff Rules Matrix.xlsx
@@ -1012,70 +1012,70 @@
         <v>176</v>
       </c>
       <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>2</v>
+      </c>
+      <c r="N2" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>3</v>
+      </c>
+      <c r="S2">
         <v>4</v>
       </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-      <c r="H2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
-      <c r="K2" t="b">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>2</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>4</v>
-      </c>
-      <c r="S2">
-        <v>8</v>
-      </c>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W2" t="b">
         <v>0</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z2" t="b">
         <v>0</v>
@@ -1090,19 +1090,19 @@
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="b">
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="b">
         <v>0</v>
@@ -1134,7 +1134,7 @@
         <v>176</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3" t="b">
         <v>0</v>
@@ -1152,16 +1152,16 @@
         <v>2</v>
       </c>
       <c r="J3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3" t="b">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S3">
         <v>4</v>
@@ -1185,19 +1185,19 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W3" t="b">
         <v>0</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z3" t="b">
         <v>0</v>
@@ -1212,19 +1212,19 @@
         <v>0</v>
       </c>
       <c r="AD3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="b">
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI3" t="b">
         <v>0</v>
@@ -1256,70 +1256,70 @@
         <v>176</v>
       </c>
       <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <v>3</v>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>2</v>
+      </c>
+      <c r="N4" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4">
         <v>4</v>
       </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4" t="b">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>4</v>
-      </c>
-      <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>2</v>
-      </c>
-      <c r="M4">
-        <v>3</v>
-      </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <v>5</v>
-      </c>
       <c r="S4">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W4" t="b">
         <v>0</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z4" t="b">
         <v>0</v>
@@ -1334,19 +1334,19 @@
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="b">
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="b">
         <v>0</v>
@@ -1378,7 +1378,7 @@
         <v>176</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" t="b">
         <v>0</v>
@@ -1396,16 +1396,16 @@
         <v>2</v>
       </c>
       <c r="J5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="b">
         <v>0</v>
       </c>
       <c r="L5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="b">
         <v>0</v>
@@ -1429,19 +1429,19 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z5" t="b">
         <v>0</v>
@@ -1465,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="b">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>176</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="b">
         <v>0</v>
@@ -1518,16 +1518,16 @@
         <v>2</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="b">
         <v>0</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N6" t="b">
         <v>0</v>
@@ -1551,19 +1551,19 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
       <c r="X6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z6" t="b">
         <v>0</v>
@@ -1587,10 +1587,10 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI6" t="b">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>176</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7" t="b">
         <v>0</v>
@@ -1640,16 +1640,16 @@
         <v>2</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" t="b">
         <v>0</v>
       </c>
       <c r="L7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7" t="b">
         <v>0</v>
@@ -1673,19 +1673,19 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W7" t="b">
         <v>0</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z7" t="b">
         <v>0</v>
@@ -1700,19 +1700,19 @@
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="b">
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="b">
         <v>0</v>
@@ -1744,7 +1744,7 @@
         <v>176</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="b">
         <v>0</v>
@@ -1762,16 +1762,16 @@
         <v>2</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" t="b">
         <v>0</v>
       </c>
       <c r="L8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" t="b">
         <v>0</v>
@@ -1795,19 +1795,19 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
       </c>
       <c r="X8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z8" t="b">
         <v>0</v>
@@ -1822,19 +1822,19 @@
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="b">
         <v>0</v>
       </c>
       <c r="AG8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="b">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         <v>176</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E9" t="b">
         <v>0</v>
@@ -1884,16 +1884,16 @@
         <v>2</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="b">
         <v>0</v>
       </c>
       <c r="L9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" t="b">
         <v>0</v>
@@ -1917,19 +1917,19 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W9" t="b">
         <v>0</v>
       </c>
       <c r="X9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="b">
         <v>0</v>
@@ -1944,19 +1944,19 @@
         <v>0</v>
       </c>
       <c r="AD9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="b">
         <v>0</v>
       </c>
       <c r="AG9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="b">
         <v>0</v>
@@ -1988,7 +1988,7 @@
         <v>176</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="b">
         <v>0</v>
@@ -2006,16 +2006,16 @@
         <v>2</v>
       </c>
       <c r="J10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K10" t="b">
         <v>0</v>
       </c>
       <c r="L10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N10" t="b">
         <v>0</v>
@@ -2039,19 +2039,19 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W10" t="b">
         <v>0</v>
       </c>
       <c r="X10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z10" t="b">
         <v>0</v>
@@ -2066,19 +2066,19 @@
         <v>0</v>
       </c>
       <c r="AD10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="b">
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI10" t="b">
         <v>0</v>
@@ -2110,70 +2110,70 @@
         <v>176</v>
       </c>
       <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="M11">
+        <v>2</v>
+      </c>
+      <c r="N11" t="b">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>3</v>
+      </c>
+      <c r="S11">
         <v>4</v>
       </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-      <c r="H11" t="b">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>2</v>
-      </c>
-      <c r="J11">
-        <v>4</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>2</v>
-      </c>
-      <c r="M11">
-        <v>3</v>
-      </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>1</v>
-      </c>
-      <c r="P11">
-        <v>2</v>
-      </c>
-      <c r="Q11" t="b">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>3</v>
-      </c>
-      <c r="S11">
-        <v>6</v>
-      </c>
       <c r="T11" t="b">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W11" t="b">
         <v>0</v>
       </c>
       <c r="X11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="b">
         <v>0</v>
@@ -2188,19 +2188,19 @@
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="b">
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="b">
         <v>0</v>
@@ -2232,70 +2232,70 @@
         <v>176</v>
       </c>
       <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <v>3</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>1</v>
+      </c>
+      <c r="M12">
+        <v>2</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>1</v>
+      </c>
+      <c r="P12">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>3</v>
+      </c>
+      <c r="S12">
         <v>4</v>
       </c>
-      <c r="E12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-      <c r="H12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
-      <c r="J12">
-        <v>4</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>2</v>
-      </c>
-      <c r="M12">
-        <v>3</v>
-      </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>1</v>
-      </c>
-      <c r="P12">
-        <v>2</v>
-      </c>
-      <c r="Q12" t="b">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>3</v>
-      </c>
-      <c r="S12">
-        <v>6</v>
-      </c>
       <c r="T12" t="b">
         <v>0</v>
       </c>
       <c r="U12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W12" t="b">
         <v>0</v>
       </c>
       <c r="X12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="b">
         <v>0</v>
@@ -2310,19 +2310,19 @@
         <v>0</v>
       </c>
       <c r="AD12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="b">
         <v>0</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="b">
         <v>0</v>
@@ -2354,7 +2354,7 @@
         <v>176</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E13" t="b">
         <v>0</v>
@@ -2372,16 +2372,16 @@
         <v>2</v>
       </c>
       <c r="J13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" t="b">
         <v>0</v>
       </c>
       <c r="L13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N13" t="b">
         <v>0</v>
@@ -2405,19 +2405,19 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W13" t="b">
         <v>0</v>
       </c>
       <c r="X13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z13" t="b">
         <v>0</v>
@@ -2432,19 +2432,19 @@
         <v>0</v>
       </c>
       <c r="AD13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE13">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="b">
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI13" t="b">
         <v>0</v>
@@ -2476,70 +2476,70 @@
         <v>176</v>
       </c>
       <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>2</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>2</v>
+      </c>
+      <c r="N14" t="b">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>3</v>
+      </c>
+      <c r="S14">
         <v>4</v>
       </c>
-      <c r="E14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-      <c r="H14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-      <c r="J14">
-        <v>4</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>2</v>
-      </c>
-      <c r="M14">
-        <v>3</v>
-      </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>1</v>
-      </c>
-      <c r="P14">
-        <v>2</v>
-      </c>
-      <c r="Q14" t="b">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>3</v>
-      </c>
-      <c r="S14">
-        <v>6</v>
-      </c>
       <c r="T14" t="b">
         <v>0</v>
       </c>
       <c r="U14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W14" t="b">
         <v>0</v>
       </c>
       <c r="X14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z14" t="b">
         <v>0</v>
@@ -2554,19 +2554,19 @@
         <v>0</v>
       </c>
       <c r="AD14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="b">
         <v>0</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI14" t="b">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>176</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E15" t="b">
         <v>0</v>
@@ -2616,16 +2616,16 @@
         <v>2</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K15" t="b">
         <v>0</v>
       </c>
       <c r="L15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N15" t="b">
         <v>0</v>
@@ -2640,28 +2640,28 @@
         <v>0</v>
       </c>
       <c r="R15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S15">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T15" t="b">
         <v>0</v>
       </c>
       <c r="U15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W15" t="b">
         <v>0</v>
       </c>
       <c r="X15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z15" t="b">
         <v>0</v>
@@ -2676,19 +2676,19 @@
         <v>0</v>
       </c>
       <c r="AD15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF15" t="b">
         <v>0</v>
       </c>
       <c r="AG15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI15" t="b">
         <v>0</v>
@@ -2720,7 +2720,7 @@
         <v>176</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" t="b">
         <v>0</v>
@@ -2738,16 +2738,16 @@
         <v>2</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K16" t="b">
         <v>0</v>
       </c>
       <c r="L16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" t="b">
         <v>0</v>
@@ -2771,19 +2771,19 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W16" t="b">
         <v>0</v>
       </c>
       <c r="X16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z16" t="b">
         <v>0</v>
@@ -2798,19 +2798,19 @@
         <v>0</v>
       </c>
       <c r="AD16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="b">
         <v>0</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="b">
         <v>0</v>
@@ -2842,7 +2842,7 @@
         <v>176</v>
       </c>
       <c r="D17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" t="b">
         <v>0</v>
@@ -2860,16 +2860,16 @@
         <v>2</v>
       </c>
       <c r="J17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K17" t="b">
         <v>0</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N17" t="b">
         <v>0</v>
@@ -2893,19 +2893,19 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W17" t="b">
         <v>0</v>
       </c>
       <c r="X17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="b">
         <v>0</v>
@@ -2920,19 +2920,19 @@
         <v>0</v>
       </c>
       <c r="AD17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="b">
         <v>0</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI17" t="b">
         <v>0</v>
@@ -2964,70 +2964,70 @@
         <v>176</v>
       </c>
       <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>2</v>
+      </c>
+      <c r="J18">
+        <v>3</v>
+      </c>
+      <c r="K18" t="b">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>2</v>
+      </c>
+      <c r="N18" t="b">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>1</v>
+      </c>
+      <c r="P18">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
+      <c r="R18">
         <v>4</v>
       </c>
-      <c r="E18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>2</v>
-      </c>
-      <c r="H18" t="b">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>2</v>
-      </c>
-      <c r="J18">
-        <v>4</v>
-      </c>
-      <c r="K18" t="b">
-        <v>0</v>
-      </c>
-      <c r="L18">
-        <v>2</v>
-      </c>
-      <c r="M18">
-        <v>3</v>
-      </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
-      <c r="O18">
-        <v>1</v>
-      </c>
-      <c r="P18">
-        <v>2</v>
-      </c>
-      <c r="Q18" t="b">
-        <v>0</v>
-      </c>
-      <c r="R18">
-        <v>5</v>
-      </c>
       <c r="S18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="b">
         <v>0</v>
       </c>
       <c r="U18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W18" t="b">
         <v>0</v>
       </c>
       <c r="X18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="b">
         <v>0</v>
@@ -3042,19 +3042,19 @@
         <v>0</v>
       </c>
       <c r="AD18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE18">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="b">
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI18" t="b">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>176</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E19" t="b">
         <v>0</v>
@@ -3104,16 +3104,16 @@
         <v>2</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N19" t="b">
         <v>0</v>
@@ -3137,19 +3137,19 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W19" t="b">
         <v>0</v>
       </c>
       <c r="X19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z19" t="b">
         <v>0</v>
@@ -3173,10 +3173,10 @@
         <v>0</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI19" t="b">
         <v>0</v>
@@ -3208,7 +3208,7 @@
         <v>176</v>
       </c>
       <c r="D20">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" t="b">
         <v>0</v>
@@ -3226,16 +3226,16 @@
         <v>2</v>
       </c>
       <c r="J20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" t="b">
         <v>0</v>
       </c>
       <c r="L20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20" t="b">
         <v>0</v>
@@ -3259,19 +3259,19 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W20" t="b">
         <v>0</v>
       </c>
       <c r="X20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z20" t="b">
         <v>0</v>
@@ -3286,19 +3286,19 @@
         <v>0</v>
       </c>
       <c r="AD20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="b">
         <v>0</v>
       </c>
       <c r="AG20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI20" t="b">
         <v>0</v>
@@ -3330,7 +3330,7 @@
         <v>176</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" t="b">
         <v>0</v>
@@ -3348,16 +3348,16 @@
         <v>2</v>
       </c>
       <c r="J21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K21" t="b">
         <v>0</v>
       </c>
       <c r="L21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21" t="b">
         <v>0</v>
@@ -3381,19 +3381,19 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W21" t="b">
         <v>0</v>
       </c>
       <c r="X21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="b">
         <v>0</v>
@@ -3408,19 +3408,19 @@
         <v>0</v>
       </c>
       <c r="AD21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="b">
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI21" t="b">
         <v>0</v>
@@ -3452,7 +3452,7 @@
         <v>176</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E22" t="b">
         <v>0</v>
@@ -3470,16 +3470,16 @@
         <v>2</v>
       </c>
       <c r="J22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K22" t="b">
         <v>0</v>
       </c>
       <c r="L22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N22" t="b">
         <v>0</v>
@@ -3494,28 +3494,28 @@
         <v>0</v>
       </c>
       <c r="R22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T22" t="b">
         <v>0</v>
       </c>
       <c r="U22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W22" t="b">
         <v>0</v>
       </c>
       <c r="X22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y22">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="b">
         <v>0</v>
@@ -3530,19 +3530,19 @@
         <v>0</v>
       </c>
       <c r="AD22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF22" t="b">
         <v>0</v>
       </c>
       <c r="AG22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI22" t="b">
         <v>0</v>
@@ -3574,70 +3574,70 @@
         <v>176</v>
       </c>
       <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>2</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>1</v>
+      </c>
+      <c r="M23">
+        <v>2</v>
+      </c>
+      <c r="N23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>2</v>
+      </c>
+      <c r="S23">
         <v>4</v>
       </c>
-      <c r="E23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-      <c r="H23" t="b">
-        <v>0</v>
-      </c>
-      <c r="I23">
-        <v>2</v>
-      </c>
-      <c r="J23">
-        <v>4</v>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23">
-        <v>2</v>
-      </c>
-      <c r="M23">
-        <v>3</v>
-      </c>
-      <c r="N23" t="b">
-        <v>0</v>
-      </c>
-      <c r="O23">
-        <v>1</v>
-      </c>
-      <c r="P23">
-        <v>2</v>
-      </c>
-      <c r="Q23" t="b">
-        <v>0</v>
-      </c>
-      <c r="R23">
-        <v>3</v>
-      </c>
-      <c r="S23">
-        <v>6</v>
-      </c>
       <c r="T23" t="b">
         <v>0</v>
       </c>
       <c r="U23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W23" t="b">
         <v>0</v>
       </c>
       <c r="X23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z23" t="b">
         <v>0</v>
@@ -3652,19 +3652,19 @@
         <v>0</v>
       </c>
       <c r="AD23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="b">
         <v>0</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI23" t="b">
         <v>0</v>
@@ -3696,7 +3696,7 @@
         <v>176</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E24" t="b">
         <v>0</v>
@@ -3714,16 +3714,16 @@
         <v>2</v>
       </c>
       <c r="J24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K24" t="b">
         <v>0</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N24" t="b">
         <v>0</v>
@@ -3738,28 +3738,28 @@
         <v>0</v>
       </c>
       <c r="R24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T24" t="b">
         <v>0</v>
       </c>
       <c r="U24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W24" t="b">
         <v>0</v>
       </c>
       <c r="X24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="b">
         <v>0</v>
@@ -3774,19 +3774,19 @@
         <v>0</v>
       </c>
       <c r="AD24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE24">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="b">
         <v>0</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI24" t="b">
         <v>0</v>
@@ -3818,7 +3818,7 @@
         <v>176</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E25" t="b">
         <v>0</v>
@@ -3836,16 +3836,16 @@
         <v>2</v>
       </c>
       <c r="J25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K25" t="b">
         <v>0</v>
       </c>
       <c r="L25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N25" t="b">
         <v>0</v>
@@ -3869,19 +3869,19 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W25" t="b">
         <v>0</v>
       </c>
       <c r="X25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="b">
         <v>0</v>
@@ -3896,19 +3896,19 @@
         <v>0</v>
       </c>
       <c r="AD25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="b">
         <v>0</v>
       </c>
       <c r="AG25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI25" t="b">
         <v>0</v>
@@ -3940,7 +3940,7 @@
         <v>176</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E26" t="b">
         <v>0</v>
@@ -3958,16 +3958,16 @@
         <v>2</v>
       </c>
       <c r="J26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K26" t="b">
         <v>0</v>
       </c>
       <c r="L26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N26" t="b">
         <v>0</v>
@@ -3991,19 +3991,19 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W26" t="b">
         <v>0</v>
       </c>
       <c r="X26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z26" t="b">
         <v>0</v>
@@ -4018,19 +4018,19 @@
         <v>0</v>
       </c>
       <c r="AD26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF26" t="b">
         <v>0</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI26" t="b">
         <v>0</v>
@@ -4062,7 +4062,7 @@
         <v>176</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E27" t="b">
         <v>0</v>
@@ -4080,16 +4080,16 @@
         <v>2</v>
       </c>
       <c r="J27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K27" t="b">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27" t="b">
         <v>0</v>
@@ -4113,19 +4113,19 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W27" t="b">
         <v>0</v>
       </c>
       <c r="X27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="b">
         <v>0</v>
@@ -4140,19 +4140,19 @@
         <v>0</v>
       </c>
       <c r="AD27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF27" t="b">
         <v>0</v>
       </c>
       <c r="AG27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI27" t="b">
         <v>0</v>
@@ -4184,7 +4184,7 @@
         <v>176</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -4202,16 +4202,16 @@
         <v>2</v>
       </c>
       <c r="J28">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K28" t="b">
         <v>0</v>
       </c>
       <c r="L28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N28" t="b">
         <v>0</v>
@@ -4235,19 +4235,19 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W28" t="b">
         <v>0</v>
       </c>
       <c r="X28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="b">
         <v>0</v>
@@ -4262,19 +4262,19 @@
         <v>0</v>
       </c>
       <c r="AD28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF28" t="b">
         <v>0</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI28" t="b">
         <v>0</v>
@@ -4306,7 +4306,7 @@
         <v>176</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -4324,52 +4324,52 @@
         <v>2</v>
       </c>
       <c r="J29">
+        <v>3</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="M29">
+        <v>2</v>
+      </c>
+      <c r="N29" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29">
+        <v>1</v>
+      </c>
+      <c r="P29">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>2</v>
+      </c>
+      <c r="S29">
         <v>4</v>
       </c>
-      <c r="K29" t="b">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>2</v>
-      </c>
-      <c r="M29">
-        <v>3</v>
-      </c>
-      <c r="N29" t="b">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>1</v>
-      </c>
-      <c r="P29">
-        <v>2</v>
-      </c>
-      <c r="Q29" t="b">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>3</v>
-      </c>
-      <c r="S29">
-        <v>6</v>
-      </c>
       <c r="T29" t="b">
         <v>0</v>
       </c>
       <c r="U29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W29" t="b">
         <v>0</v>
       </c>
       <c r="X29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z29" t="b">
         <v>0</v>
@@ -4384,19 +4384,19 @@
         <v>0</v>
       </c>
       <c r="AD29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF29" t="b">
         <v>0</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI29" t="b">
         <v>0</v>
@@ -4428,7 +4428,7 @@
         <v>176</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -4446,16 +4446,16 @@
         <v>2</v>
       </c>
       <c r="J30">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K30" t="b">
         <v>0</v>
       </c>
       <c r="L30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N30" t="b">
         <v>0</v>
@@ -4479,19 +4479,19 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W30" t="b">
         <v>0</v>
       </c>
       <c r="X30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z30" t="b">
         <v>0</v>
@@ -4506,19 +4506,19 @@
         <v>0</v>
       </c>
       <c r="AD30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF30" t="b">
         <v>0</v>
       </c>
       <c r="AG30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI30" t="b">
         <v>0</v>
@@ -4550,7 +4550,7 @@
         <v>176</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -4568,16 +4568,16 @@
         <v>2</v>
       </c>
       <c r="J31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K31" t="b">
         <v>0</v>
       </c>
       <c r="L31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N31" t="b">
         <v>0</v>
@@ -4592,28 +4592,28 @@
         <v>0</v>
       </c>
       <c r="R31">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T31" t="b">
         <v>0</v>
       </c>
       <c r="U31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W31" t="b">
         <v>0</v>
       </c>
       <c r="X31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z31" t="b">
         <v>0</v>
@@ -4628,19 +4628,19 @@
         <v>0</v>
       </c>
       <c r="AD31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE31">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF31" t="b">
         <v>0</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI31" t="b">
         <v>0</v>
@@ -4690,16 +4690,16 @@
         <v>2</v>
       </c>
       <c r="J32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K32" t="b">
         <v>0</v>
       </c>
       <c r="L32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N32" t="b">
         <v>0</v>
@@ -4723,19 +4723,19 @@
         <v>1</v>
       </c>
       <c r="U32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W32" t="b">
         <v>0</v>
       </c>
       <c r="X32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z32" t="b">
         <v>0</v>
@@ -4750,19 +4750,19 @@
         <v>0</v>
       </c>
       <c r="AD32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF32" t="b">
         <v>0</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI32" t="b">
         <v>0</v>
@@ -4794,7 +4794,7 @@
         <v>176</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E33" t="b">
         <v>0</v>
@@ -4812,16 +4812,16 @@
         <v>2</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" t="b">
         <v>0</v>
       </c>
       <c r="L33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N33" t="b">
         <v>0</v>
@@ -4845,19 +4845,19 @@
         <v>0</v>
       </c>
       <c r="U33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W33" t="b">
         <v>0</v>
       </c>
       <c r="X33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="b">
         <v>0</v>
@@ -4872,19 +4872,19 @@
         <v>0</v>
       </c>
       <c r="AD33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF33" t="b">
         <v>0</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI33" t="b">
         <v>0</v>
@@ -4916,7 +4916,7 @@
         <v>176</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E34" t="b">
         <v>0</v>
@@ -4934,16 +4934,16 @@
         <v>2</v>
       </c>
       <c r="J34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K34" t="b">
         <v>0</v>
       </c>
       <c r="L34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N34" t="b">
         <v>0</v>
@@ -4967,19 +4967,19 @@
         <v>0</v>
       </c>
       <c r="U34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W34" t="b">
         <v>0</v>
       </c>
       <c r="X34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z34" t="b">
         <v>0</v>
@@ -4994,19 +4994,19 @@
         <v>0</v>
       </c>
       <c r="AD34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF34" t="b">
         <v>0</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI34" t="b">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>176</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E35" t="b">
         <v>0</v>
@@ -5056,16 +5056,16 @@
         <v>2</v>
       </c>
       <c r="J35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K35" t="b">
         <v>0</v>
       </c>
       <c r="L35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N35" t="b">
         <v>0</v>
@@ -5089,19 +5089,19 @@
         <v>0</v>
       </c>
       <c r="U35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W35" t="b">
         <v>0</v>
       </c>
       <c r="X35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="b">
         <v>0</v>
@@ -5116,19 +5116,19 @@
         <v>0</v>
       </c>
       <c r="AD35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF35" t="b">
         <v>0</v>
       </c>
       <c r="AG35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI35" t="b">
         <v>0</v>
@@ -5160,7 +5160,7 @@
         <v>176</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E36" t="b">
         <v>0</v>
@@ -5178,16 +5178,16 @@
         <v>2</v>
       </c>
       <c r="J36">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K36" t="b">
         <v>0</v>
       </c>
       <c r="L36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N36" t="b">
         <v>0</v>
@@ -5211,19 +5211,19 @@
         <v>0</v>
       </c>
       <c r="U36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W36" t="b">
         <v>0</v>
       </c>
       <c r="X36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z36" t="b">
         <v>0</v>
@@ -5238,19 +5238,19 @@
         <v>0</v>
       </c>
       <c r="AD36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF36" t="b">
         <v>0</v>
       </c>
       <c r="AG36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI36" t="b">
         <v>0</v>
@@ -5282,7 +5282,7 @@
         <v>176</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E37" t="b">
         <v>0</v>
@@ -5300,16 +5300,16 @@
         <v>2</v>
       </c>
       <c r="J37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K37" t="b">
         <v>0</v>
       </c>
       <c r="L37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N37" t="b">
         <v>0</v>
@@ -5333,19 +5333,19 @@
         <v>0</v>
       </c>
       <c r="U37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W37" t="b">
         <v>0</v>
       </c>
       <c r="X37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z37" t="b">
         <v>0</v>
@@ -5360,19 +5360,19 @@
         <v>0</v>
       </c>
       <c r="AD37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF37" t="b">
         <v>0</v>
       </c>
       <c r="AG37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI37" t="b">
         <v>0</v>
@@ -5404,7 +5404,7 @@
         <v>176</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E38" t="b">
         <v>0</v>
@@ -5422,16 +5422,16 @@
         <v>2</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K38" t="b">
         <v>0</v>
       </c>
       <c r="L38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N38" t="b">
         <v>0</v>
@@ -5455,19 +5455,19 @@
         <v>0</v>
       </c>
       <c r="U38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W38" t="b">
         <v>0</v>
       </c>
       <c r="X38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z38" t="b">
         <v>0</v>
@@ -5482,19 +5482,19 @@
         <v>0</v>
       </c>
       <c r="AD38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF38" t="b">
         <v>0</v>
       </c>
       <c r="AG38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI38" t="b">
         <v>0</v>
@@ -5526,7 +5526,7 @@
         <v>176</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E39" t="b">
         <v>0</v>
@@ -5544,16 +5544,16 @@
         <v>2</v>
       </c>
       <c r="J39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" t="b">
         <v>0</v>
       </c>
       <c r="L39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N39" t="b">
         <v>0</v>
@@ -5568,28 +5568,28 @@
         <v>0</v>
       </c>
       <c r="R39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S39">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T39" t="b">
         <v>0</v>
       </c>
       <c r="U39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W39" t="b">
         <v>0</v>
       </c>
       <c r="X39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z39" t="b">
         <v>0</v>
@@ -5604,19 +5604,19 @@
         <v>0</v>
       </c>
       <c r="AD39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE39">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF39" t="b">
         <v>0</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI39" t="b">
         <v>0</v>
@@ -5648,7 +5648,7 @@
         <v>176</v>
       </c>
       <c r="D40">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E40" t="b">
         <v>0</v>
@@ -5666,16 +5666,16 @@
         <v>2</v>
       </c>
       <c r="J40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K40" t="b">
         <v>0</v>
       </c>
       <c r="L40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N40" t="b">
         <v>0</v>
@@ -5699,19 +5699,19 @@
         <v>0</v>
       </c>
       <c r="U40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W40" t="b">
         <v>0</v>
       </c>
       <c r="X40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="b">
         <v>0</v>
@@ -5726,19 +5726,19 @@
         <v>0</v>
       </c>
       <c r="AD40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF40" t="b">
         <v>0</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI40" t="b">
         <v>0</v>
@@ -5770,7 +5770,7 @@
         <v>176</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E41" t="b">
         <v>0</v>
@@ -5788,16 +5788,16 @@
         <v>2</v>
       </c>
       <c r="J41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" t="b">
         <v>0</v>
       </c>
       <c r="L41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N41" t="b">
         <v>0</v>
@@ -5821,19 +5821,19 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W41" t="b">
         <v>0</v>
       </c>
       <c r="X41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z41" t="b">
         <v>0</v>
@@ -5848,19 +5848,19 @@
         <v>0</v>
       </c>
       <c r="AD41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF41" t="b">
         <v>0</v>
       </c>
       <c r="AG41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI41" t="b">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>176</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E42" t="b">
         <v>0</v>
@@ -5910,16 +5910,16 @@
         <v>2</v>
       </c>
       <c r="J42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K42" t="b">
         <v>0</v>
       </c>
       <c r="L42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N42" t="b">
         <v>0</v>
@@ -5943,19 +5943,19 @@
         <v>0</v>
       </c>
       <c r="U42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W42" t="b">
         <v>0</v>
       </c>
       <c r="X42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="b">
         <v>0</v>
@@ -5970,19 +5970,19 @@
         <v>0</v>
       </c>
       <c r="AD42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF42" t="b">
         <v>0</v>
       </c>
       <c r="AG42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI42" t="b">
         <v>0</v>
@@ -6014,7 +6014,7 @@
         <v>176</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E43" t="b">
         <v>0</v>
@@ -6032,16 +6032,16 @@
         <v>2</v>
       </c>
       <c r="J43">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K43" t="b">
         <v>0</v>
       </c>
       <c r="L43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N43" t="b">
         <v>0</v>
@@ -6065,19 +6065,19 @@
         <v>0</v>
       </c>
       <c r="U43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W43" t="b">
         <v>0</v>
       </c>
       <c r="X43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="b">
         <v>0</v>
@@ -6092,19 +6092,19 @@
         <v>0</v>
       </c>
       <c r="AD43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF43" t="b">
         <v>0</v>
       </c>
       <c r="AG43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI43" t="b">
         <v>0</v>
@@ -6136,7 +6136,7 @@
         <v>176</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E44" t="b">
         <v>0</v>
@@ -6154,16 +6154,16 @@
         <v>2</v>
       </c>
       <c r="J44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K44" t="b">
         <v>0</v>
       </c>
       <c r="L44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N44" t="b">
         <v>0</v>
@@ -6187,19 +6187,19 @@
         <v>0</v>
       </c>
       <c r="U44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W44" t="b">
         <v>0</v>
       </c>
       <c r="X44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="b">
         <v>0</v>
@@ -6214,19 +6214,19 @@
         <v>0</v>
       </c>
       <c r="AD44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE44">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF44" t="b">
         <v>0</v>
       </c>
       <c r="AG44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI44" t="b">
         <v>0</v>
@@ -6258,7 +6258,7 @@
         <v>176</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E45" t="b">
         <v>0</v>
@@ -6276,16 +6276,16 @@
         <v>2</v>
       </c>
       <c r="J45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K45" t="b">
         <v>0</v>
       </c>
       <c r="L45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N45" t="b">
         <v>0</v>
@@ -6309,19 +6309,19 @@
         <v>0</v>
       </c>
       <c r="U45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W45" t="b">
         <v>0</v>
       </c>
       <c r="X45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z45" t="b">
         <v>0</v>
@@ -6336,19 +6336,19 @@
         <v>0</v>
       </c>
       <c r="AD45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF45" t="b">
         <v>0</v>
       </c>
       <c r="AG45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI45" t="b">
         <v>0</v>
@@ -6380,7 +6380,7 @@
         <v>176</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E46" t="b">
         <v>0</v>
@@ -6398,16 +6398,16 @@
         <v>2</v>
       </c>
       <c r="J46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K46" t="b">
         <v>0</v>
       </c>
       <c r="L46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N46" t="b">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="U46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W46" t="b">
         <v>0</v>
       </c>
       <c r="X46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z46" t="b">
         <v>0</v>
@@ -6458,19 +6458,19 @@
         <v>0</v>
       </c>
       <c r="AD46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE46">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF46" t="b">
         <v>0</v>
       </c>
       <c r="AG46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI46" t="b">
         <v>0</v>
@@ -6502,70 +6502,70 @@
         <v>176</v>
       </c>
       <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>2</v>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>2</v>
+      </c>
+      <c r="J47">
+        <v>3</v>
+      </c>
+      <c r="K47" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>1</v>
+      </c>
+      <c r="M47">
+        <v>2</v>
+      </c>
+      <c r="N47" t="b">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>1</v>
+      </c>
+      <c r="P47">
+        <v>2</v>
+      </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
+      <c r="R47">
+        <v>3</v>
+      </c>
+      <c r="S47">
         <v>6</v>
       </c>
-      <c r="E47" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47">
-        <v>2</v>
-      </c>
-      <c r="H47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47">
-        <v>2</v>
-      </c>
-      <c r="J47">
-        <v>4</v>
-      </c>
-      <c r="K47" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>2</v>
-      </c>
-      <c r="M47">
-        <v>3</v>
-      </c>
-      <c r="N47" t="b">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>1</v>
-      </c>
-      <c r="P47">
-        <v>2</v>
-      </c>
-      <c r="Q47" t="b">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>4</v>
-      </c>
-      <c r="S47">
-        <v>8</v>
-      </c>
       <c r="T47" t="b">
         <v>0</v>
       </c>
       <c r="U47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W47" t="b">
         <v>0</v>
       </c>
       <c r="X47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z47" t="b">
         <v>0</v>
@@ -6580,19 +6580,19 @@
         <v>0</v>
       </c>
       <c r="AD47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF47" t="b">
         <v>0</v>
       </c>
       <c r="AG47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI47" t="b">
         <v>0</v>
@@ -6624,7 +6624,7 @@
         <v>176</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E48" t="b">
         <v>0</v>
@@ -6642,16 +6642,16 @@
         <v>2</v>
       </c>
       <c r="J48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K48" t="b">
         <v>0</v>
       </c>
       <c r="L48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N48" t="b">
         <v>0</v>
@@ -6675,19 +6675,19 @@
         <v>0</v>
       </c>
       <c r="U48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W48" t="b">
         <v>0</v>
       </c>
       <c r="X48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z48" t="b">
         <v>0</v>
@@ -6702,19 +6702,19 @@
         <v>0</v>
       </c>
       <c r="AD48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF48" t="b">
         <v>0</v>
       </c>
       <c r="AG48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI48" t="b">
         <v>0</v>
@@ -6746,7 +6746,7 @@
         <v>176</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E49" t="b">
         <v>0</v>
@@ -6764,16 +6764,16 @@
         <v>2</v>
       </c>
       <c r="J49">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K49" t="b">
         <v>0</v>
       </c>
       <c r="L49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N49" t="b">
         <v>0</v>
@@ -6797,19 +6797,19 @@
         <v>0</v>
       </c>
       <c r="U49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W49" t="b">
         <v>0</v>
       </c>
       <c r="X49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z49" t="b">
         <v>0</v>
@@ -6824,19 +6824,19 @@
         <v>0</v>
       </c>
       <c r="AD49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF49" t="b">
         <v>0</v>
       </c>
       <c r="AG49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI49" t="b">
         <v>0</v>
@@ -6868,7 +6868,7 @@
         <v>176</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E50" t="b">
         <v>0</v>
@@ -6886,16 +6886,16 @@
         <v>2</v>
       </c>
       <c r="J50">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K50" t="b">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N50" t="b">
         <v>0</v>
@@ -6919,19 +6919,19 @@
         <v>0</v>
       </c>
       <c r="U50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W50" t="b">
         <v>0</v>
       </c>
       <c r="X50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z50" t="b">
         <v>0</v>
@@ -6946,19 +6946,19 @@
         <v>0</v>
       </c>
       <c r="AD50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF50" t="b">
         <v>0</v>
       </c>
       <c r="AG50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI50" t="b">
         <v>0</v>
@@ -6990,7 +6990,7 @@
         <v>176</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E51" t="b">
         <v>0</v>
@@ -7008,16 +7008,16 @@
         <v>2</v>
       </c>
       <c r="J51">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K51" t="b">
         <v>0</v>
       </c>
       <c r="L51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N51" t="b">
         <v>0</v>
@@ -7041,19 +7041,19 @@
         <v>0</v>
       </c>
       <c r="U51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W51" t="b">
         <v>0</v>
       </c>
       <c r="X51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z51" t="b">
         <v>0</v>
@@ -7068,19 +7068,19 @@
         <v>0</v>
       </c>
       <c r="AD51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF51" t="b">
         <v>0</v>
       </c>
       <c r="AG51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI51" t="b">
         <v>0</v>
@@ -7112,7 +7112,7 @@
         <v>176</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E52" t="b">
         <v>0</v>
@@ -7130,16 +7130,16 @@
         <v>2</v>
       </c>
       <c r="J52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K52" t="b">
         <v>0</v>
       </c>
       <c r="L52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N52" t="b">
         <v>0</v>
@@ -7163,19 +7163,19 @@
         <v>0</v>
       </c>
       <c r="U52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W52" t="b">
         <v>0</v>
       </c>
       <c r="X52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z52" t="b">
         <v>0</v>
@@ -7190,19 +7190,19 @@
         <v>0</v>
       </c>
       <c r="AD52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF52" t="b">
         <v>0</v>
       </c>
       <c r="AG52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI52" t="b">
         <v>0</v>
@@ -7234,7 +7234,7 @@
         <v>176</v>
       </c>
       <c r="D53">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E53" t="b">
         <v>0</v>
@@ -7252,16 +7252,16 @@
         <v>2</v>
       </c>
       <c r="J53">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53" t="b">
         <v>0</v>
       </c>
       <c r="L53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N53" t="b">
         <v>0</v>
@@ -7285,19 +7285,19 @@
         <v>0</v>
       </c>
       <c r="U53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W53" t="b">
         <v>0</v>
       </c>
       <c r="X53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z53" t="b">
         <v>0</v>
@@ -7312,19 +7312,19 @@
         <v>0</v>
       </c>
       <c r="AD53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF53" t="b">
         <v>0</v>
       </c>
       <c r="AG53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI53" t="b">
         <v>0</v>
@@ -7356,7 +7356,7 @@
         <v>176</v>
       </c>
       <c r="D54">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E54" t="b">
         <v>0</v>
@@ -7374,16 +7374,16 @@
         <v>2</v>
       </c>
       <c r="J54">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K54" t="b">
         <v>0</v>
       </c>
       <c r="L54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N54" t="b">
         <v>0</v>
@@ -7398,28 +7398,28 @@
         <v>0</v>
       </c>
       <c r="R54">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S54">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T54" t="b">
         <v>0</v>
       </c>
       <c r="U54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W54" t="b">
         <v>0</v>
       </c>
       <c r="X54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z54" t="b">
         <v>0</v>
@@ -7434,19 +7434,19 @@
         <v>0</v>
       </c>
       <c r="AD54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE54">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF54" t="b">
         <v>0</v>
       </c>
       <c r="AG54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI54" t="b">
         <v>0</v>
@@ -7478,7 +7478,7 @@
         <v>176</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E55" t="b">
         <v>0</v>
@@ -7496,16 +7496,16 @@
         <v>2</v>
       </c>
       <c r="J55">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K55" t="b">
         <v>0</v>
       </c>
       <c r="L55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N55" t="b">
         <v>0</v>
@@ -7529,19 +7529,19 @@
         <v>0</v>
       </c>
       <c r="U55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W55" t="b">
         <v>0</v>
       </c>
       <c r="X55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z55" t="b">
         <v>0</v>
@@ -7565,10 +7565,10 @@
         <v>0</v>
       </c>
       <c r="AG55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI55" t="b">
         <v>0</v>
@@ -7600,7 +7600,7 @@
         <v>176</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E56" t="b">
         <v>0</v>
@@ -7618,16 +7618,16 @@
         <v>2</v>
       </c>
       <c r="J56">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K56" t="b">
         <v>0</v>
       </c>
       <c r="L56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N56" t="b">
         <v>0</v>
@@ -7651,19 +7651,19 @@
         <v>0</v>
       </c>
       <c r="U56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W56" t="b">
         <v>0</v>
       </c>
       <c r="X56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z56" t="b">
         <v>0</v>
@@ -7678,19 +7678,19 @@
         <v>0</v>
       </c>
       <c r="AD56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF56" t="b">
         <v>0</v>
       </c>
       <c r="AG56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI56" t="b">
         <v>0</v>
@@ -7722,7 +7722,7 @@
         <v>176</v>
       </c>
       <c r="D57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E57" t="b">
         <v>0</v>
@@ -7740,16 +7740,16 @@
         <v>2</v>
       </c>
       <c r="J57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K57" t="b">
         <v>0</v>
       </c>
       <c r="L57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N57" t="b">
         <v>0</v>
@@ -7773,19 +7773,19 @@
         <v>0</v>
       </c>
       <c r="U57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W57" t="b">
         <v>0</v>
       </c>
       <c r="X57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z57" t="b">
         <v>0</v>
@@ -7800,19 +7800,19 @@
         <v>0</v>
       </c>
       <c r="AD57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF57" t="b">
         <v>0</v>
       </c>
       <c r="AG57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI57" t="b">
         <v>0</v>
@@ -7844,7 +7844,7 @@
         <v>176</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E58" t="b">
         <v>0</v>
@@ -7862,16 +7862,16 @@
         <v>2</v>
       </c>
       <c r="J58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K58" t="b">
         <v>0</v>
       </c>
       <c r="L58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N58" t="b">
         <v>0</v>
@@ -7895,19 +7895,19 @@
         <v>0</v>
       </c>
       <c r="U58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W58" t="b">
         <v>0</v>
       </c>
       <c r="X58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z58" t="b">
         <v>0</v>
@@ -7931,10 +7931,10 @@
         <v>0</v>
       </c>
       <c r="AG58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI58" t="b">
         <v>0</v>
@@ -7966,7 +7966,7 @@
         <v>176</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E59" t="b">
         <v>0</v>
@@ -7984,16 +7984,16 @@
         <v>2</v>
       </c>
       <c r="J59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K59" t="b">
         <v>0</v>
       </c>
       <c r="L59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N59" t="b">
         <v>0</v>
@@ -8008,28 +8008,28 @@
         <v>0</v>
       </c>
       <c r="R59">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S59">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T59" t="b">
         <v>0</v>
       </c>
       <c r="U59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W59" t="b">
         <v>0</v>
       </c>
       <c r="X59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z59" t="b">
         <v>0</v>
@@ -8044,19 +8044,19 @@
         <v>0</v>
       </c>
       <c r="AD59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE59">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF59" t="b">
         <v>0</v>
       </c>
       <c r="AG59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI59" t="b">
         <v>0</v>
@@ -8088,7 +8088,7 @@
         <v>176</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E60" t="b">
         <v>0</v>
@@ -8106,16 +8106,16 @@
         <v>2</v>
       </c>
       <c r="J60">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K60" t="b">
         <v>0</v>
       </c>
       <c r="L60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N60" t="b">
         <v>0</v>
@@ -8139,19 +8139,19 @@
         <v>0</v>
       </c>
       <c r="U60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W60" t="b">
         <v>0</v>
       </c>
       <c r="X60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z60" t="b">
         <v>0</v>
@@ -8166,19 +8166,19 @@
         <v>0</v>
       </c>
       <c r="AD60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF60" t="b">
         <v>0</v>
       </c>
       <c r="AG60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI60" t="b">
         <v>0</v>
@@ -8210,7 +8210,7 @@
         <v>176</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E61" t="b">
         <v>0</v>
@@ -8228,16 +8228,16 @@
         <v>2</v>
       </c>
       <c r="J61">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K61" t="b">
         <v>0</v>
       </c>
       <c r="L61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N61" t="b">
         <v>0</v>
@@ -8261,19 +8261,19 @@
         <v>0</v>
       </c>
       <c r="U61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W61" t="b">
         <v>0</v>
       </c>
       <c r="X61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z61" t="b">
         <v>0</v>
@@ -8288,19 +8288,19 @@
         <v>0</v>
       </c>
       <c r="AD61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF61" t="b">
         <v>0</v>
       </c>
       <c r="AG61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI61" t="b">
         <v>0</v>
@@ -8332,7 +8332,7 @@
         <v>176</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E62" t="b">
         <v>0</v>
@@ -8350,16 +8350,16 @@
         <v>2</v>
       </c>
       <c r="J62">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K62" t="b">
         <v>0</v>
       </c>
       <c r="L62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N62" t="b">
         <v>0</v>
@@ -8383,19 +8383,19 @@
         <v>0</v>
       </c>
       <c r="U62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W62" t="b">
         <v>0</v>
       </c>
       <c r="X62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z62" t="b">
         <v>0</v>
@@ -8410,19 +8410,19 @@
         <v>0</v>
       </c>
       <c r="AD62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF62" t="b">
         <v>0</v>
       </c>
       <c r="AG62">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI62" t="b">
         <v>0</v>
@@ -8454,7 +8454,7 @@
         <v>176</v>
       </c>
       <c r="D63">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E63" t="b">
         <v>0</v>
@@ -8472,16 +8472,16 @@
         <v>2</v>
       </c>
       <c r="J63">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K63" t="b">
         <v>0</v>
       </c>
       <c r="L63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N63" t="b">
         <v>0</v>
@@ -8505,19 +8505,19 @@
         <v>0</v>
       </c>
       <c r="U63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W63" t="b">
         <v>0</v>
       </c>
       <c r="X63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z63" t="b">
         <v>0</v>
@@ -8532,19 +8532,19 @@
         <v>0</v>
       </c>
       <c r="AD63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF63" t="b">
         <v>0</v>
       </c>
       <c r="AG63">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI63" t="b">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>176</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E64" t="b">
         <v>0</v>
@@ -8594,16 +8594,16 @@
         <v>2</v>
       </c>
       <c r="J64">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K64" t="b">
         <v>0</v>
       </c>
       <c r="L64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N64" t="b">
         <v>0</v>
@@ -8627,19 +8627,19 @@
         <v>0</v>
       </c>
       <c r="U64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W64" t="b">
         <v>0</v>
       </c>
       <c r="X64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z64" t="b">
         <v>0</v>
@@ -8654,19 +8654,19 @@
         <v>0</v>
       </c>
       <c r="AD64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF64" t="b">
         <v>0</v>
       </c>
       <c r="AG64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI64" t="b">
         <v>0</v>
@@ -8698,7 +8698,7 @@
         <v>176</v>
       </c>
       <c r="D65">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E65" t="b">
         <v>0</v>
@@ -8716,16 +8716,16 @@
         <v>2</v>
       </c>
       <c r="J65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K65" t="b">
         <v>0</v>
       </c>
       <c r="L65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N65" t="b">
         <v>0</v>
@@ -8749,19 +8749,19 @@
         <v>0</v>
       </c>
       <c r="U65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W65" t="b">
         <v>0</v>
       </c>
       <c r="X65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z65" t="b">
         <v>0</v>
@@ -8776,19 +8776,19 @@
         <v>0</v>
       </c>
       <c r="AD65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF65" t="b">
         <v>0</v>
       </c>
       <c r="AG65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI65" t="b">
         <v>0</v>
@@ -8820,7 +8820,7 @@
         <v>176</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E66" t="b">
         <v>0</v>
@@ -8838,16 +8838,16 @@
         <v>2</v>
       </c>
       <c r="J66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K66" t="b">
         <v>0</v>
       </c>
       <c r="L66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N66" t="b">
         <v>0</v>
@@ -8871,19 +8871,19 @@
         <v>0</v>
       </c>
       <c r="U66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W66" t="b">
         <v>0</v>
       </c>
       <c r="X66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z66" t="b">
         <v>0</v>
@@ -8898,19 +8898,19 @@
         <v>0</v>
       </c>
       <c r="AD66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF66" t="b">
         <v>0</v>
       </c>
       <c r="AG66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI66" t="b">
         <v>0</v>
@@ -8960,16 +8960,16 @@
         <v>2</v>
       </c>
       <c r="J67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K67" t="b">
         <v>0</v>
       </c>
       <c r="L67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N67" t="b">
         <v>0</v>
@@ -8993,19 +8993,19 @@
         <v>0</v>
       </c>
       <c r="U67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W67" t="b">
         <v>0</v>
       </c>
       <c r="X67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z67" t="b">
         <v>0</v>
@@ -9029,10 +9029,10 @@
         <v>0</v>
       </c>
       <c r="AG67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI67" t="b">
         <v>0</v>
@@ -9064,7 +9064,7 @@
         <v>176</v>
       </c>
       <c r="D68">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E68" t="b">
         <v>0</v>
@@ -9082,16 +9082,16 @@
         <v>2</v>
       </c>
       <c r="J68">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K68" t="b">
         <v>0</v>
       </c>
       <c r="L68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N68" t="b">
         <v>0</v>
@@ -9115,19 +9115,19 @@
         <v>0</v>
       </c>
       <c r="U68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W68" t="b">
         <v>0</v>
       </c>
       <c r="X68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z68" t="b">
         <v>0</v>
@@ -9151,10 +9151,10 @@
         <v>0</v>
       </c>
       <c r="AG68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI68" t="b">
         <v>0</v>
@@ -9186,7 +9186,7 @@
         <v>176</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E69" t="b">
         <v>1</v>

--- a/Data/Rules/Fluff & Tuff Rules Matrix.xlsx
+++ b/Data/Rules/Fluff & Tuff Rules Matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="178">
   <si>
     <t>SKU</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>HQ_Max</t>
+  </si>
+  <si>
+    <t>Total Max</t>
   </si>
   <si>
     <t>10189</t>
@@ -876,10 +879,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN69"/>
+  <dimension ref="A1:AO69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:40">
+    <row r="1" spans="1:41">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1000,16 +1003,19 @@
       <c r="AN1" t="s">
         <v>39</v>
       </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="2" spans="1:40">
+    <row r="2" spans="1:41">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1122,16 +1128,19 @@
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" spans="1:40">
+    <row r="3" spans="1:41">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1244,16 +1253,19 @@
       <c r="AN3">
         <v>0</v>
       </c>
+      <c r="AO3">
+        <v>26</v>
+      </c>
     </row>
-    <row r="4" spans="1:40">
+    <row r="4" spans="1:41">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1366,16 +1378,19 @@
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>28</v>
+      </c>
     </row>
-    <row r="5" spans="1:40">
+    <row r="5" spans="1:41">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -1488,16 +1503,19 @@
       <c r="AN5">
         <v>0</v>
       </c>
+      <c r="AO5">
+        <v>24</v>
+      </c>
     </row>
-    <row r="6" spans="1:40">
+    <row r="6" spans="1:41">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -1610,16 +1628,19 @@
       <c r="AN6">
         <v>0</v>
       </c>
+      <c r="AO6">
+        <v>25</v>
+      </c>
     </row>
-    <row r="7" spans="1:40">
+    <row r="7" spans="1:41">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -1732,16 +1753,19 @@
       <c r="AN7">
         <v>0</v>
       </c>
+      <c r="AO7">
+        <v>26</v>
+      </c>
     </row>
-    <row r="8" spans="1:40">
+    <row r="8" spans="1:41">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -1854,16 +1878,19 @@
       <c r="AN8">
         <v>0</v>
       </c>
+      <c r="AO8">
+        <v>26</v>
+      </c>
     </row>
-    <row r="9" spans="1:40">
+    <row r="9" spans="1:41">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -1976,16 +2003,19 @@
       <c r="AN9">
         <v>0</v>
       </c>
+      <c r="AO9">
+        <v>26</v>
+      </c>
     </row>
-    <row r="10" spans="1:40">
+    <row r="10" spans="1:41">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2098,16 +2128,19 @@
       <c r="AN10">
         <v>0</v>
       </c>
+      <c r="AO10">
+        <v>26</v>
+      </c>
     </row>
-    <row r="11" spans="1:40">
+    <row r="11" spans="1:41">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2220,16 +2253,19 @@
       <c r="AN11">
         <v>0</v>
       </c>
+      <c r="AO11">
+        <v>26</v>
+      </c>
     </row>
-    <row r="12" spans="1:40">
+    <row r="12" spans="1:41">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2342,16 +2378,19 @@
       <c r="AN12">
         <v>0</v>
       </c>
+      <c r="AO12">
+        <v>26</v>
+      </c>
     </row>
-    <row r="13" spans="1:40">
+    <row r="13" spans="1:41">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2464,16 +2503,19 @@
       <c r="AN13">
         <v>0</v>
       </c>
+      <c r="AO13">
+        <v>26</v>
+      </c>
     </row>
-    <row r="14" spans="1:40">
+    <row r="14" spans="1:41">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2586,16 +2628,19 @@
       <c r="AN14">
         <v>0</v>
       </c>
+      <c r="AO14">
+        <v>26</v>
+      </c>
     </row>
-    <row r="15" spans="1:40">
+    <row r="15" spans="1:41">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2708,16 +2753,19 @@
       <c r="AN15">
         <v>0</v>
       </c>
+      <c r="AO15">
+        <v>28</v>
+      </c>
     </row>
-    <row r="16" spans="1:40">
+    <row r="16" spans="1:41">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2830,16 +2878,19 @@
       <c r="AN16">
         <v>0</v>
       </c>
+      <c r="AO16">
+        <v>26</v>
+      </c>
     </row>
-    <row r="17" spans="1:40">
+    <row r="17" spans="1:41">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2952,16 +3003,19 @@
       <c r="AN17">
         <v>0</v>
       </c>
+      <c r="AO17">
+        <v>28</v>
+      </c>
     </row>
-    <row r="18" spans="1:40">
+    <row r="18" spans="1:41">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -3074,16 +3128,19 @@
       <c r="AN18">
         <v>0</v>
       </c>
+      <c r="AO18">
+        <v>28</v>
+      </c>
     </row>
-    <row r="19" spans="1:40">
+    <row r="19" spans="1:41">
       <c r="A19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -3196,16 +3253,19 @@
       <c r="AN19">
         <v>0</v>
       </c>
+      <c r="AO19">
+        <v>25</v>
+      </c>
     </row>
-    <row r="20" spans="1:40">
+    <row r="20" spans="1:41">
       <c r="A20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -3318,16 +3378,19 @@
       <c r="AN20">
         <v>0</v>
       </c>
+      <c r="AO20">
+        <v>26</v>
+      </c>
     </row>
-    <row r="21" spans="1:40">
+    <row r="21" spans="1:41">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C21" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -3440,16 +3503,19 @@
       <c r="AN21">
         <v>0</v>
       </c>
+      <c r="AO21">
+        <v>26</v>
+      </c>
     </row>
-    <row r="22" spans="1:40">
+    <row r="22" spans="1:41">
       <c r="A22" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -3562,16 +3628,19 @@
       <c r="AN22">
         <v>0</v>
       </c>
+      <c r="AO22">
+        <v>28</v>
+      </c>
     </row>
-    <row r="23" spans="1:40">
+    <row r="23" spans="1:41">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C23" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -3684,16 +3753,19 @@
       <c r="AN23">
         <v>0</v>
       </c>
+      <c r="AO23">
+        <v>26</v>
+      </c>
     </row>
-    <row r="24" spans="1:40">
+    <row r="24" spans="1:41">
       <c r="A24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -3806,16 +3878,19 @@
       <c r="AN24">
         <v>0</v>
       </c>
+      <c r="AO24">
+        <v>28</v>
+      </c>
     </row>
-    <row r="25" spans="1:40">
+    <row r="25" spans="1:41">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B25" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C25" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -3928,16 +4003,19 @@
       <c r="AN25">
         <v>0</v>
       </c>
+      <c r="AO25">
+        <v>26</v>
+      </c>
     </row>
-    <row r="26" spans="1:40">
+    <row r="26" spans="1:41">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -4050,16 +4128,19 @@
       <c r="AN26">
         <v>0</v>
       </c>
+      <c r="AO26">
+        <v>26</v>
+      </c>
     </row>
-    <row r="27" spans="1:40">
+    <row r="27" spans="1:41">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -4172,16 +4253,19 @@
       <c r="AN27">
         <v>0</v>
       </c>
+      <c r="AO27">
+        <v>26</v>
+      </c>
     </row>
-    <row r="28" spans="1:40">
+    <row r="28" spans="1:41">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C28" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -4294,16 +4378,19 @@
       <c r="AN28">
         <v>0</v>
       </c>
+      <c r="AO28">
+        <v>26</v>
+      </c>
     </row>
-    <row r="29" spans="1:40">
+    <row r="29" spans="1:41">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C29" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -4416,16 +4503,19 @@
       <c r="AN29">
         <v>0</v>
       </c>
+      <c r="AO29">
+        <v>26</v>
+      </c>
     </row>
-    <row r="30" spans="1:40">
+    <row r="30" spans="1:41">
       <c r="A30" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -4538,16 +4628,19 @@
       <c r="AN30">
         <v>0</v>
       </c>
+      <c r="AO30">
+        <v>26</v>
+      </c>
     </row>
-    <row r="31" spans="1:40">
+    <row r="31" spans="1:41">
       <c r="A31" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -4660,16 +4753,19 @@
       <c r="AN31">
         <v>0</v>
       </c>
+      <c r="AO31">
+        <v>28</v>
+      </c>
     </row>
-    <row r="32" spans="1:40">
+    <row r="32" spans="1:41">
       <c r="A32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B32" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C32" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -4782,16 +4878,19 @@
       <c r="AN32">
         <v>0</v>
       </c>
+      <c r="AO32">
+        <v>26</v>
+      </c>
     </row>
-    <row r="33" spans="1:40">
+    <row r="33" spans="1:41">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -4904,16 +5003,19 @@
       <c r="AN33">
         <v>0</v>
       </c>
+      <c r="AO33">
+        <v>26</v>
+      </c>
     </row>
-    <row r="34" spans="1:40">
+    <row r="34" spans="1:41">
       <c r="A34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C34" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -5026,16 +5128,19 @@
       <c r="AN34">
         <v>0</v>
       </c>
+      <c r="AO34">
+        <v>26</v>
+      </c>
     </row>
-    <row r="35" spans="1:40">
+    <row r="35" spans="1:41">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -5148,16 +5253,19 @@
       <c r="AN35">
         <v>0</v>
       </c>
+      <c r="AO35">
+        <v>28</v>
+      </c>
     </row>
-    <row r="36" spans="1:40">
+    <row r="36" spans="1:41">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -5270,16 +5378,19 @@
       <c r="AN36">
         <v>0</v>
       </c>
+      <c r="AO36">
+        <v>26</v>
+      </c>
     </row>
-    <row r="37" spans="1:40">
+    <row r="37" spans="1:41">
       <c r="A37" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C37" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -5392,16 +5503,19 @@
       <c r="AN37">
         <v>0</v>
       </c>
+      <c r="AO37">
+        <v>26</v>
+      </c>
     </row>
-    <row r="38" spans="1:40">
+    <row r="38" spans="1:41">
       <c r="A38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C38" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -5514,16 +5628,19 @@
       <c r="AN38">
         <v>0</v>
       </c>
+      <c r="AO38">
+        <v>28</v>
+      </c>
     </row>
-    <row r="39" spans="1:40">
+    <row r="39" spans="1:41">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B39" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C39" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -5636,16 +5753,19 @@
       <c r="AN39">
         <v>0</v>
       </c>
+      <c r="AO39">
+        <v>28</v>
+      </c>
     </row>
-    <row r="40" spans="1:40">
+    <row r="40" spans="1:41">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C40" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -5758,16 +5878,19 @@
       <c r="AN40">
         <v>0</v>
       </c>
+      <c r="AO40">
+        <v>26</v>
+      </c>
     </row>
-    <row r="41" spans="1:40">
+    <row r="41" spans="1:41">
       <c r="A41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C41" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -5880,16 +6003,19 @@
       <c r="AN41">
         <v>0</v>
       </c>
+      <c r="AO41">
+        <v>26</v>
+      </c>
     </row>
-    <row r="42" spans="1:40">
+    <row r="42" spans="1:41">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C42" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -6002,16 +6128,19 @@
       <c r="AN42">
         <v>0</v>
       </c>
+      <c r="AO42">
+        <v>28</v>
+      </c>
     </row>
-    <row r="43" spans="1:40">
+    <row r="43" spans="1:41">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B43" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C43" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -6124,16 +6253,19 @@
       <c r="AN43">
         <v>0</v>
       </c>
+      <c r="AO43">
+        <v>28</v>
+      </c>
     </row>
-    <row r="44" spans="1:40">
+    <row r="44" spans="1:41">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B44" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C44" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -6246,16 +6378,19 @@
       <c r="AN44">
         <v>0</v>
       </c>
+      <c r="AO44">
+        <v>28</v>
+      </c>
     </row>
-    <row r="45" spans="1:40">
+    <row r="45" spans="1:41">
       <c r="A45" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B45" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C45" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -6368,16 +6503,19 @@
       <c r="AN45">
         <v>0</v>
       </c>
+      <c r="AO45">
+        <v>28</v>
+      </c>
     </row>
-    <row r="46" spans="1:40">
+    <row r="46" spans="1:41">
       <c r="A46" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C46" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -6490,16 +6628,19 @@
       <c r="AN46">
         <v>0</v>
       </c>
+      <c r="AO46">
+        <v>28</v>
+      </c>
     </row>
-    <row r="47" spans="1:40">
+    <row r="47" spans="1:41">
       <c r="A47" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C47" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -6612,16 +6753,19 @@
       <c r="AN47">
         <v>0</v>
       </c>
+      <c r="AO47">
+        <v>28</v>
+      </c>
     </row>
-    <row r="48" spans="1:40">
+    <row r="48" spans="1:41">
       <c r="A48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B48" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C48" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -6734,16 +6878,19 @@
       <c r="AN48">
         <v>0</v>
       </c>
+      <c r="AO48">
+        <v>26</v>
+      </c>
     </row>
-    <row r="49" spans="1:40">
+    <row r="49" spans="1:41">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B49" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C49" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -6856,16 +7003,19 @@
       <c r="AN49">
         <v>0</v>
       </c>
+      <c r="AO49">
+        <v>26</v>
+      </c>
     </row>
-    <row r="50" spans="1:40">
+    <row r="50" spans="1:41">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B50" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C50" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -6978,16 +7128,19 @@
       <c r="AN50">
         <v>0</v>
       </c>
+      <c r="AO50">
+        <v>26</v>
+      </c>
     </row>
-    <row r="51" spans="1:40">
+    <row r="51" spans="1:41">
       <c r="A51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B51" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -7100,16 +7253,19 @@
       <c r="AN51">
         <v>0</v>
       </c>
+      <c r="AO51">
+        <v>26</v>
+      </c>
     </row>
-    <row r="52" spans="1:40">
+    <row r="52" spans="1:41">
       <c r="A52" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B52" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C52" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -7222,16 +7378,19 @@
       <c r="AN52">
         <v>0</v>
       </c>
+      <c r="AO52">
+        <v>28</v>
+      </c>
     </row>
-    <row r="53" spans="1:40">
+    <row r="53" spans="1:41">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C53" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -7344,16 +7503,19 @@
       <c r="AN53">
         <v>0</v>
       </c>
+      <c r="AO53">
+        <v>26</v>
+      </c>
     </row>
-    <row r="54" spans="1:40">
+    <row r="54" spans="1:41">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B54" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C54" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -7466,16 +7628,19 @@
       <c r="AN54">
         <v>0</v>
       </c>
+      <c r="AO54">
+        <v>28</v>
+      </c>
     </row>
-    <row r="55" spans="1:40">
+    <row r="55" spans="1:41">
       <c r="A55" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B55" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C55" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -7588,16 +7753,19 @@
       <c r="AN55">
         <v>0</v>
       </c>
+      <c r="AO55">
+        <v>24</v>
+      </c>
     </row>
-    <row r="56" spans="1:40">
+    <row r="56" spans="1:41">
       <c r="A56" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B56" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C56" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -7710,16 +7878,19 @@
       <c r="AN56">
         <v>0</v>
       </c>
+      <c r="AO56">
+        <v>26</v>
+      </c>
     </row>
-    <row r="57" spans="1:40">
+    <row r="57" spans="1:41">
       <c r="A57" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B57" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C57" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -7832,16 +8003,19 @@
       <c r="AN57">
         <v>0</v>
       </c>
+      <c r="AO57">
+        <v>26</v>
+      </c>
     </row>
-    <row r="58" spans="1:40">
+    <row r="58" spans="1:41">
       <c r="A58" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B58" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C58" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -7954,16 +8128,19 @@
       <c r="AN58">
         <v>0</v>
       </c>
+      <c r="AO58">
+        <v>24</v>
+      </c>
     </row>
-    <row r="59" spans="1:40">
+    <row r="59" spans="1:41">
       <c r="A59" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B59" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C59" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -8076,16 +8253,19 @@
       <c r="AN59">
         <v>0</v>
       </c>
+      <c r="AO59">
+        <v>28</v>
+      </c>
     </row>
-    <row r="60" spans="1:40">
+    <row r="60" spans="1:41">
       <c r="A60" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B60" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C60" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -8198,16 +8378,19 @@
       <c r="AN60">
         <v>0</v>
       </c>
+      <c r="AO60">
+        <v>26</v>
+      </c>
     </row>
-    <row r="61" spans="1:40">
+    <row r="61" spans="1:41">
       <c r="A61" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B61" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C61" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -8320,16 +8503,19 @@
       <c r="AN61">
         <v>0</v>
       </c>
+      <c r="AO61">
+        <v>26</v>
+      </c>
     </row>
-    <row r="62" spans="1:40">
+    <row r="62" spans="1:41">
       <c r="A62" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B62" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C62" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -8442,16 +8628,19 @@
       <c r="AN62">
         <v>0</v>
       </c>
+      <c r="AO62">
+        <v>28</v>
+      </c>
     </row>
-    <row r="63" spans="1:40">
+    <row r="63" spans="1:41">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B63" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C63" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -8564,16 +8753,19 @@
       <c r="AN63">
         <v>0</v>
       </c>
+      <c r="AO63">
+        <v>26</v>
+      </c>
     </row>
-    <row r="64" spans="1:40">
+    <row r="64" spans="1:41">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B64" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C64" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -8686,16 +8878,19 @@
       <c r="AN64">
         <v>0</v>
       </c>
+      <c r="AO64">
+        <v>25</v>
+      </c>
     </row>
-    <row r="65" spans="1:40">
+    <row r="65" spans="1:41">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B65" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C65" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -8808,16 +9003,19 @@
       <c r="AN65">
         <v>0</v>
       </c>
+      <c r="AO65">
+        <v>26</v>
+      </c>
     </row>
-    <row r="66" spans="1:40">
+    <row r="66" spans="1:41">
       <c r="A66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B66" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C66" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -8930,260 +9128,269 @@
       <c r="AN66">
         <v>0</v>
       </c>
+      <c r="AO66">
+        <v>26</v>
+      </c>
     </row>
-    <row r="67" spans="1:40">
+    <row r="67" spans="1:41">
       <c r="A67" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B67" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C67" t="s">
+        <v>177</v>
+      </c>
+      <c r="D67">
+        <v>1</v>
+      </c>
+      <c r="E67" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="H67" t="b">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>2</v>
+      </c>
+      <c r="J67">
+        <v>3</v>
+      </c>
+      <c r="K67" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>2</v>
+      </c>
+      <c r="N67" t="b">
+        <v>0</v>
+      </c>
+      <c r="O67">
+        <v>1</v>
+      </c>
+      <c r="P67">
+        <v>2</v>
+      </c>
+      <c r="Q67" t="b">
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <v>1</v>
+      </c>
+      <c r="S67">
+        <v>2</v>
+      </c>
+      <c r="T67" t="b">
+        <v>0</v>
+      </c>
+      <c r="U67">
+        <v>1</v>
+      </c>
+      <c r="V67">
+        <v>2</v>
+      </c>
+      <c r="W67" t="b">
+        <v>0</v>
+      </c>
+      <c r="X67">
+        <v>1</v>
+      </c>
+      <c r="Y67">
+        <v>2</v>
+      </c>
+      <c r="Z67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA67">
+        <v>1</v>
+      </c>
+      <c r="AB67">
+        <v>2</v>
+      </c>
+      <c r="AC67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD67">
+        <v>1</v>
+      </c>
+      <c r="AE67">
+        <v>2</v>
+      </c>
+      <c r="AF67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67">
+        <v>1</v>
+      </c>
+      <c r="AH67">
+        <v>2</v>
+      </c>
+      <c r="AI67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ67">
+        <v>2</v>
+      </c>
+      <c r="AK67">
+        <v>3</v>
+      </c>
+      <c r="AL67" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM67">
+        <v>0</v>
+      </c>
+      <c r="AN67">
+        <v>0</v>
+      </c>
+      <c r="AO67">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="1:41">
+      <c r="A68" t="s">
+        <v>107</v>
+      </c>
+      <c r="B68" t="s">
+        <v>175</v>
+      </c>
+      <c r="C68" t="s">
+        <v>177</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="E68" t="b">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+      <c r="H68" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>2</v>
+      </c>
+      <c r="J68">
+        <v>3</v>
+      </c>
+      <c r="K68" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <v>2</v>
+      </c>
+      <c r="N68" t="b">
+        <v>0</v>
+      </c>
+      <c r="O68">
+        <v>1</v>
+      </c>
+      <c r="P68">
+        <v>2</v>
+      </c>
+      <c r="Q68" t="b">
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <v>1</v>
+      </c>
+      <c r="S68">
+        <v>2</v>
+      </c>
+      <c r="T68" t="b">
+        <v>0</v>
+      </c>
+      <c r="U68">
+        <v>1</v>
+      </c>
+      <c r="V68">
+        <v>2</v>
+      </c>
+      <c r="W68" t="b">
+        <v>0</v>
+      </c>
+      <c r="X68">
+        <v>1</v>
+      </c>
+      <c r="Y68">
+        <v>2</v>
+      </c>
+      <c r="Z68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AA68">
+        <v>1</v>
+      </c>
+      <c r="AB68">
+        <v>2</v>
+      </c>
+      <c r="AC68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD68">
+        <v>1</v>
+      </c>
+      <c r="AE68">
+        <v>2</v>
+      </c>
+      <c r="AF68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68">
+        <v>1</v>
+      </c>
+      <c r="AH68">
+        <v>2</v>
+      </c>
+      <c r="AI68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ68">
+        <v>2</v>
+      </c>
+      <c r="AK68">
+        <v>3</v>
+      </c>
+      <c r="AL68" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM68">
+        <v>0</v>
+      </c>
+      <c r="AN68">
+        <v>0</v>
+      </c>
+      <c r="AO68">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:41">
+      <c r="A69" t="s">
+        <v>108</v>
+      </c>
+      <c r="B69" t="s">
         <v>176</v>
       </c>
-      <c r="D67">
-        <v>1</v>
-      </c>
-      <c r="E67" t="b">
-        <v>0</v>
-      </c>
-      <c r="F67">
-        <v>1</v>
-      </c>
-      <c r="G67">
-        <v>2</v>
-      </c>
-      <c r="H67" t="b">
-        <v>0</v>
-      </c>
-      <c r="I67">
-        <v>2</v>
-      </c>
-      <c r="J67">
-        <v>3</v>
-      </c>
-      <c r="K67" t="b">
-        <v>0</v>
-      </c>
-      <c r="L67">
-        <v>1</v>
-      </c>
-      <c r="M67">
-        <v>2</v>
-      </c>
-      <c r="N67" t="b">
-        <v>0</v>
-      </c>
-      <c r="O67">
-        <v>1</v>
-      </c>
-      <c r="P67">
-        <v>2</v>
-      </c>
-      <c r="Q67" t="b">
-        <v>0</v>
-      </c>
-      <c r="R67">
-        <v>1</v>
-      </c>
-      <c r="S67">
-        <v>2</v>
-      </c>
-      <c r="T67" t="b">
-        <v>0</v>
-      </c>
-      <c r="U67">
-        <v>1</v>
-      </c>
-      <c r="V67">
-        <v>2</v>
-      </c>
-      <c r="W67" t="b">
-        <v>0</v>
-      </c>
-      <c r="X67">
-        <v>1</v>
-      </c>
-      <c r="Y67">
-        <v>2</v>
-      </c>
-      <c r="Z67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA67">
-        <v>1</v>
-      </c>
-      <c r="AB67">
-        <v>2</v>
-      </c>
-      <c r="AC67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD67">
-        <v>1</v>
-      </c>
-      <c r="AE67">
-        <v>2</v>
-      </c>
-      <c r="AF67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG67">
-        <v>1</v>
-      </c>
-      <c r="AH67">
-        <v>2</v>
-      </c>
-      <c r="AI67" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ67">
-        <v>2</v>
-      </c>
-      <c r="AK67">
-        <v>3</v>
-      </c>
-      <c r="AL67" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM67">
-        <v>0</v>
-      </c>
-      <c r="AN67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:40">
-      <c r="A68" t="s">
-        <v>106</v>
-      </c>
-      <c r="B68" t="s">
-        <v>174</v>
-      </c>
-      <c r="C68" t="s">
-        <v>176</v>
-      </c>
-      <c r="D68">
-        <v>1</v>
-      </c>
-      <c r="E68" t="b">
-        <v>0</v>
-      </c>
-      <c r="F68">
-        <v>1</v>
-      </c>
-      <c r="G68">
-        <v>2</v>
-      </c>
-      <c r="H68" t="b">
-        <v>0</v>
-      </c>
-      <c r="I68">
-        <v>2</v>
-      </c>
-      <c r="J68">
-        <v>3</v>
-      </c>
-      <c r="K68" t="b">
-        <v>0</v>
-      </c>
-      <c r="L68">
-        <v>1</v>
-      </c>
-      <c r="M68">
-        <v>2</v>
-      </c>
-      <c r="N68" t="b">
-        <v>0</v>
-      </c>
-      <c r="O68">
-        <v>1</v>
-      </c>
-      <c r="P68">
-        <v>2</v>
-      </c>
-      <c r="Q68" t="b">
-        <v>0</v>
-      </c>
-      <c r="R68">
-        <v>1</v>
-      </c>
-      <c r="S68">
-        <v>2</v>
-      </c>
-      <c r="T68" t="b">
-        <v>0</v>
-      </c>
-      <c r="U68">
-        <v>1</v>
-      </c>
-      <c r="V68">
-        <v>2</v>
-      </c>
-      <c r="W68" t="b">
-        <v>0</v>
-      </c>
-      <c r="X68">
-        <v>1</v>
-      </c>
-      <c r="Y68">
-        <v>2</v>
-      </c>
-      <c r="Z68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AA68">
-        <v>1</v>
-      </c>
-      <c r="AB68">
-        <v>2</v>
-      </c>
-      <c r="AC68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD68">
-        <v>1</v>
-      </c>
-      <c r="AE68">
-        <v>2</v>
-      </c>
-      <c r="AF68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68">
-        <v>1</v>
-      </c>
-      <c r="AH68">
-        <v>2</v>
-      </c>
-      <c r="AI68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AJ68">
-        <v>2</v>
-      </c>
-      <c r="AK68">
-        <v>3</v>
-      </c>
-      <c r="AL68" t="b">
-        <v>1</v>
-      </c>
-      <c r="AM68">
-        <v>0</v>
-      </c>
-      <c r="AN68">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:40">
-      <c r="A69" t="s">
-        <v>107</v>
-      </c>
-      <c r="B69" t="s">
-        <v>175</v>
-      </c>
       <c r="C69" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -9294,6 +9501,9 @@
         <v>0</v>
       </c>
       <c r="AN69">
+        <v>0</v>
+      </c>
+      <c r="AO69">
         <v>0</v>
       </c>
     </row>
